--- a/其他楼交接班容量报表空模板.xlsx
+++ b/其他楼交接班容量报表空模板.xlsx
@@ -4500,7 +4500,10 @@
       <c r="AB29" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="AC29" s="83"/>
+      <c r="AC29" s="83">
+        <f>(AC26+AC28)*2.25*2.25*3.14</f>
+        <v>0</v>
+      </c>
       <c r="AD29" s="71"/>
       <c r="AE29" s="72"/>
     </row>
@@ -11083,7 +11086,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{27a2076e-51ec-4ada-a9a8-7649d0dbfc47}</x14:id>
+          <x14:id>{b5bdb37c-304d-45b0-9ead-82cf4b1e18ba}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11095,7 +11098,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2cd55699-38d2-4427-8f9d-ebbba0418e8c}</x14:id>
+          <x14:id>{70cac10c-c36d-4e1d-a2c5-c516e8f5755e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11107,7 +11110,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8208dc65-4d26-444a-87e7-f91fa2a760fe}</x14:id>
+          <x14:id>{b6af8c4e-13f2-4703-88dc-cfed550de9c5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11119,7 +11122,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{24c7773b-7f01-43a8-806e-0cd7aee61c7c}</x14:id>
+          <x14:id>{bee170fd-42b7-40df-9112-0529c3e8af7d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11131,7 +11134,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e9267cdf-8e2e-4dd7-9c8f-93e2ef9f45a2}</x14:id>
+          <x14:id>{c5a833c9-4ce5-4980-ae7e-c11d14bbdc15}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11143,7 +11146,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cb93ccb6-410b-43a7-b720-5a67bef0051a}</x14:id>
+          <x14:id>{0553788b-7da1-45bd-a985-958155d938e9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11155,7 +11158,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bc5c2782-0af9-4b6f-9d7d-528b4ec34f40}</x14:id>
+          <x14:id>{114fcd61-28dc-4a3d-8bf2-4982fdfb1546}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11167,7 +11170,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{20e6b1a4-36fb-4fda-a231-ff5e8f5ed1d0}</x14:id>
+          <x14:id>{2f292e0e-71a0-4d17-8db6-3ac6c57e5318}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11181,7 +11184,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3a5e319c-9346-4629-858c-067cec1080f9}</x14:id>
+          <x14:id>{f06b5711-00b8-49b1-b0c4-77c1220dd65f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11193,7 +11196,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8b96164f-63b1-40fa-ba31-e5243f6cc2ab}</x14:id>
+          <x14:id>{965cd7c9-04c7-4320-8637-ec70834fa997}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11205,7 +11208,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{235e71dd-2115-4c5a-be6b-4fc3034c36ec}</x14:id>
+          <x14:id>{1aa03129-594d-4d1c-b29b-cbe46ad0f321}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11217,7 +11220,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ac8f4302-bf77-44d8-910e-9507c7088a67}</x14:id>
+          <x14:id>{2f8f479c-fff7-4087-8ec2-684807409923}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11229,7 +11232,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{79eccbcb-085c-46ee-a629-480cc5ac652d}</x14:id>
+          <x14:id>{78278cfb-ca23-4344-b895-291410e6af17}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11241,7 +11244,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{22a4db15-2a95-4afe-a268-22a727e94d26}</x14:id>
+          <x14:id>{d01c4d01-5569-4c75-8d97-2c31d5f0cf4e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11253,7 +11256,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b9e6c776-67ba-44bf-af5b-24e34752ef51}</x14:id>
+          <x14:id>{c7b218de-9a6b-44e5-b631-73ec483f30c2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11265,7 +11268,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f96ba63a-35dd-4b0a-8aa1-e79f526f1342}</x14:id>
+          <x14:id>{8d693668-89f8-4e19-a75d-dd2b62168fc4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11279,7 +11282,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5d96fa7d-3c86-4919-9698-748a12ff42b4}</x14:id>
+          <x14:id>{0f6f1cfa-4622-4714-af9e-864554cb04fc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11291,7 +11294,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4651ecab-26b6-4eeb-82c1-ba48336a702c}</x14:id>
+          <x14:id>{a9913723-1643-4861-a19a-cec77ddaccfe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11303,7 +11306,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2b56a4cf-8fd8-45b4-a3e2-0a1efaac78da}</x14:id>
+          <x14:id>{bea9e6f5-ba8b-4f43-af62-21b318bab6e7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11315,7 +11318,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f63aa823-9865-48dc-9394-5e927fab843d}</x14:id>
+          <x14:id>{a4abb4c2-a7e7-41a6-8d65-f07f8b857fae}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11327,7 +11330,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1a56e43b-c44c-48a1-8730-bbe0f86158bc}</x14:id>
+          <x14:id>{0458a306-f0a9-4df4-a133-ac43f3ad062b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11339,7 +11342,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e2666ba1-614c-4fb7-bbc0-c6e415bcb179}</x14:id>
+          <x14:id>{eb4ea31a-4a31-4d6a-ac71-e23e06fb8e35}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11351,7 +11354,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{926b9aa9-5f4f-472c-b450-01f8dd536a30}</x14:id>
+          <x14:id>{285d110c-58bc-456b-824f-edb20d1032d6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11363,7 +11366,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9130bf04-8546-4dec-807e-f9618131eb06}</x14:id>
+          <x14:id>{219751a3-2ce5-4831-ab37-ff5e15317496}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11377,7 +11380,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{70f4b5aa-e064-485c-b5a2-74109b60be8d}</x14:id>
+          <x14:id>{5dfc36d9-ee4e-4022-8ef2-020b9c63c61d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11389,7 +11392,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{11c09cc5-f662-4d58-b985-f94885011f3e}</x14:id>
+          <x14:id>{4700a69f-9f02-419e-abac-bfd92861ca4d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11401,7 +11404,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3c258f1c-f43b-4190-81a9-31278ffa4c0b}</x14:id>
+          <x14:id>{a2fba1b3-9157-40d6-a81a-0028feb684e4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11413,7 +11416,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{460e833c-5fcc-43c8-a0de-b58531654cce}</x14:id>
+          <x14:id>{94817ea8-8a5b-4010-9977-c022e014e003}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11425,7 +11428,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{65896c6e-1f60-47b1-a6b2-ab0f0a83ff57}</x14:id>
+          <x14:id>{e57d1a90-9aaa-4c70-8e30-106d55c09713}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11437,7 +11440,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{225e6ae3-ffe4-4832-9d0e-64364bdca911}</x14:id>
+          <x14:id>{12179ac9-f647-4d9c-b9ae-4a1be66bf126}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11449,7 +11452,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3309748b-dfeb-4b59-9612-df0137523be2}</x14:id>
+          <x14:id>{de4caa06-4609-4439-9130-509dfe5a9dc5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11461,7 +11464,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{19899705-1c0f-4953-8a7c-9e0a84a6e6a7}</x14:id>
+          <x14:id>{765bddd9-3192-437e-9afb-27933e53a3f8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11475,7 +11478,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{52b4e27b-edbc-49ff-8d1f-30586f21005f}</x14:id>
+          <x14:id>{b291811a-dcea-4d64-b241-5d85a2500b9c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11487,7 +11490,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e606366b-a47d-4fce-af22-92822dee6d53}</x14:id>
+          <x14:id>{5df749e9-95a0-42d9-976c-ab5571580b11}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11499,7 +11502,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{10b36dcd-3ca9-4dc0-9d12-d446dfc15f63}</x14:id>
+          <x14:id>{9a431776-b765-4fc1-9f80-9fe681b7e805}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11511,7 +11514,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{83be260a-704c-4531-ad7b-fc74217964fd}</x14:id>
+          <x14:id>{a1fd002b-7e0a-4e52-9539-06961645664a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11523,7 +11526,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{484d040a-ca61-49e2-9820-284397b4e44f}</x14:id>
+          <x14:id>{7207f772-8522-4531-824a-e67beb258a74}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11535,7 +11538,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1fc26570-e7be-47d8-b206-b3cfb4e05980}</x14:id>
+          <x14:id>{e475a319-fd6c-4759-8851-334b36e00a75}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11547,7 +11550,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ae4c0290-f9e0-4d44-9f2e-f1a06009f35a}</x14:id>
+          <x14:id>{ae775541-37ab-4200-87c7-76f0ea39bb1f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11559,7 +11562,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{953e9ecf-948b-4efd-a6bd-b145f027389c}</x14:id>
+          <x14:id>{28aea0bf-fcca-4cc0-8df3-9e74ea5f36ee}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11573,7 +11576,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{40a46591-af6c-48b5-a523-41b779c03c4c}</x14:id>
+          <x14:id>{17dce266-3284-4cb8-94c1-f36d85374b28}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11585,7 +11588,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ab2e7f69-c50d-487f-878a-650ceb659327}</x14:id>
+          <x14:id>{34c6179b-6b7f-42dc-8b61-49591e1fc02c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11597,7 +11600,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eafa1ab2-3847-4276-9d38-f3db5203b754}</x14:id>
+          <x14:id>{37418d0b-11ad-4b43-89cc-9c372b3c1143}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11609,7 +11612,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{efd478b7-3c2b-4255-8961-890b0e99464c}</x14:id>
+          <x14:id>{075dbdca-8b4d-4d31-8253-2482efffd198}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11621,7 +11624,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{715e64d3-d146-4087-893f-82dfa2b68ba0}</x14:id>
+          <x14:id>{14335229-59b5-4440-9262-849cabff99ec}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11633,7 +11636,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d53ceb99-c113-40f0-82ef-a3efe9346adc}</x14:id>
+          <x14:id>{dadabee5-68bb-4c30-af48-157a83eff0f2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11645,7 +11648,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8540eb8a-fba1-4cb8-9fd3-a46b8855801b}</x14:id>
+          <x14:id>{e56e7f9a-caf4-477b-9d1f-8b9f411e3563}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11657,7 +11660,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3919367d-cf15-4098-b638-93ffbae2f3da}</x14:id>
+          <x14:id>{5cd39489-b0d7-4c27-bd74-55e9f86d60b0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11671,7 +11674,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eedf71da-8c0c-4e5a-9ef9-16f733f7bb2b}</x14:id>
+          <x14:id>{adcea6f6-a63f-438f-a7d5-06c178a3e3cf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11683,7 +11686,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a978706b-0df9-4145-8fa7-d0768703120b}</x14:id>
+          <x14:id>{25a027e5-9b5e-4eef-9bed-e86368ecd880}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11695,7 +11698,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4959ec2b-46c6-432a-901b-97b84d457f03}</x14:id>
+          <x14:id>{6b0a2beb-4643-4d8b-bbd2-13dd2d781aca}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11709,7 +11712,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5d736307-418c-4e7d-bc26-caa8b05007a7}</x14:id>
+          <x14:id>{ee7d6c52-3640-46e1-a24d-d40fbf16e8d9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11721,7 +11724,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6d2c1282-db22-49f0-8dff-91f161226190}</x14:id>
+          <x14:id>{4fad6bbd-e805-446d-ac9e-06593a0f925b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11733,7 +11736,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ad936aac-4ccc-4f23-ac11-efb0f3b9fa4d}</x14:id>
+          <x14:id>{56127cfd-c848-448f-9036-4cb856e63eee}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11747,7 +11750,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{911b66fc-e193-4eb8-855b-2e1368a22f74}</x14:id>
+          <x14:id>{f1198962-2654-4c94-8476-6e3b45cd451c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11759,7 +11762,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{713e74bd-566f-4382-ab6a-0e12f5e9c9d4}</x14:id>
+          <x14:id>{b0e3e4d8-9fea-4b16-bf73-a9b23d92ad38}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11773,7 +11776,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{edc6ce1e-0125-4b80-b12f-e906a2280a49}</x14:id>
+          <x14:id>{66b29c32-8cf3-4277-82d6-ba95161c5981}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11785,7 +11788,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ae80fc1e-f4ea-4dd8-a4d1-aa035adf65f7}</x14:id>
+          <x14:id>{f506ca46-8425-4c07-a8da-13727ef585c8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11797,7 +11800,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3867c719-2c5b-4c3b-a150-dafbd9f21e1d}</x14:id>
+          <x14:id>{30ef224e-fe6c-4b32-b953-937fb224c6f2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11811,7 +11814,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2c9582b8-8ee0-452b-9775-a3ee918f6f65}</x14:id>
+          <x14:id>{ea6cb50c-aac6-4be2-8eb0-196601b5940a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11823,7 +11826,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8c7c7f6a-c55f-4169-aa65-df483e1622fb}</x14:id>
+          <x14:id>{c34ba798-a809-4db0-aa17-fa446710e270}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11835,7 +11838,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cc60f8c6-7ab5-4f08-925b-2ba2d1347e06}</x14:id>
+          <x14:id>{4bd76677-8845-4c64-acfb-b6a557ead14e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11849,7 +11852,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{989c5a77-120e-4ef7-9401-0b4dd828d508}</x14:id>
+          <x14:id>{8fe7ba6b-37bd-4793-9560-3f7fb8fef8a7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11861,7 +11864,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cae0d366-93a6-4f0a-87f7-97e6f0e2992a}</x14:id>
+          <x14:id>{152d7522-c7ca-49a0-b114-a5b724a1f774}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11873,7 +11876,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2eb1fc4a-5d93-4a60-b0db-d1ee26943dac}</x14:id>
+          <x14:id>{130ca20e-fec8-4d00-8c53-292224148420}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11887,7 +11890,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cbb04cc1-473f-4d2b-a284-8b1f1e5806b4}</x14:id>
+          <x14:id>{d6931269-8022-4805-a10b-f685ee134c25}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11899,7 +11902,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3217b1c4-012a-43b7-abe5-cc2d9315a9c7}</x14:id>
+          <x14:id>{c6989c46-adfc-4013-b430-805b1c371b96}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11911,7 +11914,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3ae7b952-7515-4592-b63e-e447079a52f1}</x14:id>
+          <x14:id>{8ac1dcf1-5a08-4401-907d-98676ac0adc6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11925,7 +11928,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{48cdd583-f439-4118-a7eb-adc8a5c616fe}</x14:id>
+          <x14:id>{c914cfa2-4f39-449f-b9fe-931802c70420}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11937,7 +11940,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d3055f7e-f86a-438c-82f7-d2a033cad152}</x14:id>
+          <x14:id>{b32f1855-e93c-44f4-9a79-e6b80394f85c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11949,7 +11952,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a91314e6-a3cc-49f9-8fb6-1a1b91c361a7}</x14:id>
+          <x14:id>{b78adf73-c8f4-487a-8e7d-bcff748e7667}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11963,7 +11966,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4ebc1d00-4ee2-40a0-9939-9da9667cd3a9}</x14:id>
+          <x14:id>{86dd25d1-7c19-4d66-b61b-9852ae60cbf0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11975,7 +11978,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8d732b5e-bc14-4282-8e71-87bd255ba434}</x14:id>
+          <x14:id>{adfd9c4f-6b88-44a4-b255-16336ff6d4f6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11987,7 +11990,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{da16034a-58d6-4ee3-879f-998fe9262ba9}</x14:id>
+          <x14:id>{ab6efa9f-6f94-4293-8f44-388673ea190d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11999,7 +12002,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cfa76ac8-3850-4818-9e3a-f9bdbb56b741}</x14:id>
+          <x14:id>{62e892dc-3651-4ea0-9ebf-4e11e1936ed2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12011,7 +12014,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9ec8e3d1-84ab-40bc-8a89-192b514cc0d3}</x14:id>
+          <x14:id>{dadba715-1311-4b2c-81a9-1a0e0cc11ac7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12023,7 +12026,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f30bfd8d-ed71-4c6f-b3a0-76679c60c84b}</x14:id>
+          <x14:id>{67bc41c7-064d-4f54-8835-8b4bbcab6d95}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12035,7 +12038,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{315c8095-5310-4eaa-a869-8f9449157ff3}</x14:id>
+          <x14:id>{edb8592f-6483-4caa-8b83-d9c2ac690782}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12047,7 +12050,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f17ffa41-bedc-48e1-b23f-1bb4c30a26b9}</x14:id>
+          <x14:id>{d043a9cb-21e5-4ec2-b058-a4ea811c027e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12061,7 +12064,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9a22b9cf-7e89-4d67-8eba-aba49a51ba58}</x14:id>
+          <x14:id>{c9313cad-6624-4e0f-ae7d-7f037f9f250f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12073,7 +12076,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1244d046-cc21-4fda-b571-a7d362d41cde}</x14:id>
+          <x14:id>{68fa76f4-0799-4cbc-8303-65ed6c0ca6d9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12087,7 +12090,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d1e99945-ac53-4dc1-8da3-679850d6effe}</x14:id>
+          <x14:id>{5b7c410c-f518-4d51-9341-9efd74373b22}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12101,7 +12104,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e3138be4-72d6-4e3a-b7c7-66d5c29bf4ea}</x14:id>
+          <x14:id>{899b5e31-c46a-49b8-95f6-2baf42f6a076}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12115,7 +12118,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9f273491-a02a-4cd7-bfcd-2952a53ad6af}</x14:id>
+          <x14:id>{f1a4b3e3-fef8-49a8-8bc7-2e173d78582e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12129,7 +12132,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{22a23e53-6edc-4b7a-a7dc-611f981fdf1d}</x14:id>
+          <x14:id>{8362e5b2-406f-470b-9f71-6247ab730169}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12143,7 +12146,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{967e3a25-e4aa-4369-90fc-9cc22cd8648c}</x14:id>
+          <x14:id>{03f8dc56-1d28-40fd-9ea3-a61cdeef71e8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12155,7 +12158,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{183064af-aa97-44c2-8498-af7ab78e04b9}</x14:id>
+          <x14:id>{5d7c33c2-0703-4e16-8173-894538552e82}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12167,7 +12170,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{63dc0918-9e24-415e-8733-b93562ce53e5}</x14:id>
+          <x14:id>{a876de58-0e26-4b09-b6ed-bb9db6bd7eb5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12181,7 +12184,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{96d3de2d-b870-49ab-b136-e3181c0b6834}</x14:id>
+          <x14:id>{7a74caab-7c50-49c3-b25c-0be646ed47b7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12193,7 +12196,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c084a419-1ec3-4567-9e21-dcd7b209b1b5}</x14:id>
+          <x14:id>{3f2352c3-6ec6-4fc9-9b24-f41eadfbc60f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12205,7 +12208,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1fc1936e-e5cf-4e9c-9475-f450178b8875}</x14:id>
+          <x14:id>{5f8b9665-7e50-4bb3-9c94-e00344d7b40f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12219,7 +12222,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4de21f80-ab6a-4c92-a437-40190f95548e}</x14:id>
+          <x14:id>{67e86ebc-2a6d-41a6-aa7a-48a719c20d65}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12231,7 +12234,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2b964334-fe11-4aa8-8f0d-1022d2912d48}</x14:id>
+          <x14:id>{c3b5085b-5262-45b8-90e4-b5b4fab31cbc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12243,7 +12246,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d77a807a-eb05-4acc-b17f-4375d79cf593}</x14:id>
+          <x14:id>{be17578d-f265-4070-a364-1ba6ef976da4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12257,7 +12260,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{976b1155-83b3-4bbf-8409-8486be5b93e2}</x14:id>
+          <x14:id>{a2c91264-2f52-467c-95b1-3b0d15e451da}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12269,7 +12272,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0fe2ae0e-7314-4267-ac36-914a2bfa672b}</x14:id>
+          <x14:id>{f7f8b401-6248-419b-b500-eaf3502d38d5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12281,7 +12284,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{20f85bdb-025c-442a-94c8-836f14a7c265}</x14:id>
+          <x14:id>{49416b94-fd26-4d9d-994f-6df1882ca6e9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12295,7 +12298,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{49159c48-6ed2-443c-be55-4eb502bef441}</x14:id>
+          <x14:id>{b15f3b6d-6758-45ff-abbc-36130e6136a0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12307,7 +12310,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8220679b-09a8-47a1-8447-204f78068b0d}</x14:id>
+          <x14:id>{37d9cf3b-6aa4-468e-a81f-876467b1e332}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12321,7 +12324,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a3a14427-3f06-445f-acf1-e471e49b6059}</x14:id>
+          <x14:id>{e249975f-305c-4e94-9257-91fd1a6d53e8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12333,7 +12336,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c200053b-da06-4955-a4d5-ce67ce21ef45}</x14:id>
+          <x14:id>{b240a561-ec3e-406b-8750-8614b86aed19}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12345,7 +12348,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{42032116-b0b6-42d8-a5be-a5656a9f6de8}</x14:id>
+          <x14:id>{b27629ea-eb70-4edc-8f10-b9a81b9d8624}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12359,7 +12362,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{22bd0596-7e92-407c-add9-0198101164b2}</x14:id>
+          <x14:id>{4fd8c3ad-57f4-4b82-9b33-3d148fd0137e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12371,7 +12374,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{03ad4fb0-7094-4b16-9fb2-5560e45de73e}</x14:id>
+          <x14:id>{5433f30b-40b0-4f97-80a1-b3af0999a273}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12383,7 +12386,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fce6e24a-7487-4151-87d4-701cb4b17b59}</x14:id>
+          <x14:id>{ed943de3-3d56-464c-856a-33d969cf3a04}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12397,7 +12400,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{30281817-6aff-4384-b9cc-2041747aa4fa}</x14:id>
+          <x14:id>{55abfbfa-66ed-4cfd-a1a3-2b07625cfb9d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12409,7 +12412,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{438d1385-a242-49fd-8383-ff26e11f080c}</x14:id>
+          <x14:id>{e9de3cd7-e3ff-4b26-8af4-d46824f7900e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12443,7 +12446,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{27a2076e-51ec-4ada-a9a8-7649d0dbfc47}">
+          <x14:cfRule type="dataBar" id="{b5bdb37c-304d-45b0-9ead-82cf4b1e18ba}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12454,7 +12457,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2cd55699-38d2-4427-8f9d-ebbba0418e8c}">
+          <x14:cfRule type="dataBar" id="{70cac10c-c36d-4e1d-a2c5-c516e8f5755e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12465,14 +12468,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8208dc65-4d26-444a-87e7-f91fa2a760fe}">
+          <x14:cfRule type="dataBar" id="{b6af8c4e-13f2-4703-88dc-cfed550de9c5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{24c7773b-7f01-43a8-806e-0cd7aee61c7c}">
+          <x14:cfRule type="dataBar" id="{bee170fd-42b7-40df-9112-0529c3e8af7d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12483,7 +12486,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e9267cdf-8e2e-4dd7-9c8f-93e2ef9f45a2}">
+          <x14:cfRule type="dataBar" id="{c5a833c9-4ce5-4980-ae7e-c11d14bbdc15}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12494,7 +12497,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{cb93ccb6-410b-43a7-b720-5a67bef0051a}">
+          <x14:cfRule type="dataBar" id="{0553788b-7da1-45bd-a985-958155d938e9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12505,7 +12508,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{bc5c2782-0af9-4b6f-9d7d-528b4ec34f40}">
+          <x14:cfRule type="dataBar" id="{114fcd61-28dc-4a3d-8bf2-4982fdfb1546}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12514,7 +12517,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{20e6b1a4-36fb-4fda-a231-ff5e8f5ed1d0}">
+          <x14:cfRule type="dataBar" id="{2f292e0e-71a0-4d17-8db6-3ac6c57e5318}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12526,7 +12529,7 @@
           <xm:sqref>AD56</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3a5e319c-9346-4629-858c-067cec1080f9}">
+          <x14:cfRule type="dataBar" id="{f06b5711-00b8-49b1-b0c4-77c1220dd65f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12537,7 +12540,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8b96164f-63b1-40fa-ba31-e5243f6cc2ab}">
+          <x14:cfRule type="dataBar" id="{965cd7c9-04c7-4320-8637-ec70834fa997}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12548,14 +12551,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{235e71dd-2115-4c5a-be6b-4fc3034c36ec}">
+          <x14:cfRule type="dataBar" id="{1aa03129-594d-4d1c-b29b-cbe46ad0f321}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ac8f4302-bf77-44d8-910e-9507c7088a67}">
+          <x14:cfRule type="dataBar" id="{2f8f479c-fff7-4087-8ec2-684807409923}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12566,7 +12569,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{79eccbcb-085c-46ee-a629-480cc5ac652d}">
+          <x14:cfRule type="dataBar" id="{78278cfb-ca23-4344-b895-291410e6af17}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12577,7 +12580,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{22a4db15-2a95-4afe-a268-22a727e94d26}">
+          <x14:cfRule type="dataBar" id="{d01c4d01-5569-4c75-8d97-2c31d5f0cf4e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12588,7 +12591,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b9e6c776-67ba-44bf-af5b-24e34752ef51}">
+          <x14:cfRule type="dataBar" id="{c7b218de-9a6b-44e5-b631-73ec483f30c2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12597,7 +12600,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f96ba63a-35dd-4b0a-8aa1-e79f526f1342}">
+          <x14:cfRule type="dataBar" id="{8d693668-89f8-4e19-a75d-dd2b62168fc4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12609,7 +12612,7 @@
           <xm:sqref>K60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5d96fa7d-3c86-4919-9698-748a12ff42b4}">
+          <x14:cfRule type="dataBar" id="{0f6f1cfa-4622-4714-af9e-864554cb04fc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12620,7 +12623,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4651ecab-26b6-4eeb-82c1-ba48336a702c}">
+          <x14:cfRule type="dataBar" id="{a9913723-1643-4861-a19a-cec77ddaccfe}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12631,14 +12634,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2b56a4cf-8fd8-45b4-a3e2-0a1efaac78da}">
+          <x14:cfRule type="dataBar" id="{bea9e6f5-ba8b-4f43-af62-21b318bab6e7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f63aa823-9865-48dc-9394-5e927fab843d}">
+          <x14:cfRule type="dataBar" id="{a4abb4c2-a7e7-41a6-8d65-f07f8b857fae}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12649,7 +12652,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1a56e43b-c44c-48a1-8730-bbe0f86158bc}">
+          <x14:cfRule type="dataBar" id="{0458a306-f0a9-4df4-a133-ac43f3ad062b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12660,7 +12663,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e2666ba1-614c-4fb7-bbc0-c6e415bcb179}">
+          <x14:cfRule type="dataBar" id="{eb4ea31a-4a31-4d6a-ac71-e23e06fb8e35}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12671,7 +12674,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{926b9aa9-5f4f-472c-b450-01f8dd536a30}">
+          <x14:cfRule type="dataBar" id="{285d110c-58bc-456b-824f-edb20d1032d6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12680,7 +12683,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9130bf04-8546-4dec-807e-f9618131eb06}">
+          <x14:cfRule type="dataBar" id="{219751a3-2ce5-4831-ab37-ff5e15317496}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12692,7 +12695,7 @@
           <xm:sqref>AD60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{70f4b5aa-e064-485c-b5a2-74109b60be8d}">
+          <x14:cfRule type="dataBar" id="{5dfc36d9-ee4e-4022-8ef2-020b9c63c61d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12703,7 +12706,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{11c09cc5-f662-4d58-b985-f94885011f3e}">
+          <x14:cfRule type="dataBar" id="{4700a69f-9f02-419e-abac-bfd92861ca4d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12714,14 +12717,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3c258f1c-f43b-4190-81a9-31278ffa4c0b}">
+          <x14:cfRule type="dataBar" id="{a2fba1b3-9157-40d6-a81a-0028feb684e4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{460e833c-5fcc-43c8-a0de-b58531654cce}">
+          <x14:cfRule type="dataBar" id="{94817ea8-8a5b-4010-9977-c022e014e003}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12732,7 +12735,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{65896c6e-1f60-47b1-a6b2-ab0f0a83ff57}">
+          <x14:cfRule type="dataBar" id="{e57d1a90-9aaa-4c70-8e30-106d55c09713}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12743,7 +12746,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{225e6ae3-ffe4-4832-9d0e-64364bdca911}">
+          <x14:cfRule type="dataBar" id="{12179ac9-f647-4d9c-b9ae-4a1be66bf126}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12754,7 +12757,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3309748b-dfeb-4b59-9612-df0137523be2}">
+          <x14:cfRule type="dataBar" id="{de4caa06-4609-4439-9130-509dfe5a9dc5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12763,7 +12766,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{19899705-1c0f-4953-8a7c-9e0a84a6e6a7}">
+          <x14:cfRule type="dataBar" id="{765bddd9-3192-437e-9afb-27933e53a3f8}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12775,7 +12778,7 @@
           <xm:sqref>K61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{52b4e27b-edbc-49ff-8d1f-30586f21005f}">
+          <x14:cfRule type="dataBar" id="{b291811a-dcea-4d64-b241-5d85a2500b9c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12786,7 +12789,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e606366b-a47d-4fce-af22-92822dee6d53}">
+          <x14:cfRule type="dataBar" id="{5df749e9-95a0-42d9-976c-ab5571580b11}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12797,14 +12800,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{10b36dcd-3ca9-4dc0-9d12-d446dfc15f63}">
+          <x14:cfRule type="dataBar" id="{9a431776-b765-4fc1-9f80-9fe681b7e805}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{83be260a-704c-4531-ad7b-fc74217964fd}">
+          <x14:cfRule type="dataBar" id="{a1fd002b-7e0a-4e52-9539-06961645664a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12815,7 +12818,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{484d040a-ca61-49e2-9820-284397b4e44f}">
+          <x14:cfRule type="dataBar" id="{7207f772-8522-4531-824a-e67beb258a74}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12826,7 +12829,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1fc26570-e7be-47d8-b206-b3cfb4e05980}">
+          <x14:cfRule type="dataBar" id="{e475a319-fd6c-4759-8851-334b36e00a75}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12837,7 +12840,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ae4c0290-f9e0-4d44-9f2e-f1a06009f35a}">
+          <x14:cfRule type="dataBar" id="{ae775541-37ab-4200-87c7-76f0ea39bb1f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12846,7 +12849,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{953e9ecf-948b-4efd-a6bd-b145f027389c}">
+          <x14:cfRule type="dataBar" id="{28aea0bf-fcca-4cc0-8df3-9e74ea5f36ee}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12858,7 +12861,7 @@
           <xm:sqref>K62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{40a46591-af6c-48b5-a523-41b779c03c4c}">
+          <x14:cfRule type="dataBar" id="{17dce266-3284-4cb8-94c1-f36d85374b28}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12869,7 +12872,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ab2e7f69-c50d-487f-878a-650ceb659327}">
+          <x14:cfRule type="dataBar" id="{34c6179b-6b7f-42dc-8b61-49591e1fc02c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12880,14 +12883,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{eafa1ab2-3847-4276-9d38-f3db5203b754}">
+          <x14:cfRule type="dataBar" id="{37418d0b-11ad-4b43-89cc-9c372b3c1143}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{efd478b7-3c2b-4255-8961-890b0e99464c}">
+          <x14:cfRule type="dataBar" id="{075dbdca-8b4d-4d31-8253-2482efffd198}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12898,7 +12901,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{715e64d3-d146-4087-893f-82dfa2b68ba0}">
+          <x14:cfRule type="dataBar" id="{14335229-59b5-4440-9262-849cabff99ec}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12909,7 +12912,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d53ceb99-c113-40f0-82ef-a3efe9346adc}">
+          <x14:cfRule type="dataBar" id="{dadabee5-68bb-4c30-af48-157a83eff0f2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12920,7 +12923,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8540eb8a-fba1-4cb8-9fd3-a46b8855801b}">
+          <x14:cfRule type="dataBar" id="{e56e7f9a-caf4-477b-9d1f-8b9f411e3563}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12929,7 +12932,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3919367d-cf15-4098-b638-93ffbae2f3da}">
+          <x14:cfRule type="dataBar" id="{5cd39489-b0d7-4c27-bd74-55e9f86d60b0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12941,7 +12944,7 @@
           <xm:sqref>K63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{eedf71da-8c0c-4e5a-9ef9-16f733f7bb2b}">
+          <x14:cfRule type="dataBar" id="{adcea6f6-a63f-438f-a7d5-06c178a3e3cf}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12950,7 +12953,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a978706b-0df9-4145-8fa7-d0768703120b}">
+          <x14:cfRule type="dataBar" id="{25a027e5-9b5e-4eef-9bed-e86368ecd880}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12959,7 +12962,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4959ec2b-46c6-432a-901b-97b84d457f03}">
+          <x14:cfRule type="dataBar" id="{6b0a2beb-4643-4d8b-bbd2-13dd2d781aca}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -12972,7 +12975,7 @@
           <xm:sqref>AB67</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5d736307-418c-4e7d-bc26-caa8b05007a7}">
+          <x14:cfRule type="dataBar" id="{ee7d6c52-3640-46e1-a24d-d40fbf16e8d9}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12981,7 +12984,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6d2c1282-db22-49f0-8dff-91f161226190}">
+          <x14:cfRule type="dataBar" id="{4fad6bbd-e805-446d-ac9e-06593a0f925b}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12990,7 +12993,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ad936aac-4ccc-4f23-ac11-efb0f3b9fa4d}">
+          <x14:cfRule type="dataBar" id="{56127cfd-c848-448f-9036-4cb856e63eee}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13003,7 +13006,7 @@
           <xm:sqref>AB101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{911b66fc-e193-4eb8-855b-2e1368a22f74}">
+          <x14:cfRule type="dataBar" id="{f1198962-2654-4c94-8476-6e3b45cd451c}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13012,7 +13015,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{713e74bd-566f-4382-ab6a-0e12f5e9c9d4}">
+          <x14:cfRule type="dataBar" id="{b0e3e4d8-9fea-4b16-bf73-a9b23d92ad38}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13024,7 +13027,7 @@
           <xm:sqref>AB115</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{edc6ce1e-0125-4b80-b12f-e906a2280a49}">
+          <x14:cfRule type="dataBar" id="{66b29c32-8cf3-4277-82d6-ba95161c5981}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13033,7 +13036,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ae80fc1e-f4ea-4dd8-a4d1-aa035adf65f7}">
+          <x14:cfRule type="dataBar" id="{f506ca46-8425-4c07-a8da-13727ef585c8}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13042,7 +13045,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3867c719-2c5b-4c3b-a150-dafbd9f21e1d}">
+          <x14:cfRule type="dataBar" id="{30ef224e-fe6c-4b32-b953-937fb224c6f2}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13055,7 +13058,7 @@
           <xm:sqref>AB125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2c9582b8-8ee0-452b-9775-a3ee918f6f65}">
+          <x14:cfRule type="dataBar" id="{ea6cb50c-aac6-4be2-8eb0-196601b5940a}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13064,7 +13067,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8c7c7f6a-c55f-4169-aa65-df483e1622fb}">
+          <x14:cfRule type="dataBar" id="{c34ba798-a809-4db0-aa17-fa446710e270}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13073,7 +13076,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{cc60f8c6-7ab5-4f08-925b-2ba2d1347e06}">
+          <x14:cfRule type="dataBar" id="{4bd76677-8845-4c64-acfb-b6a557ead14e}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13086,7 +13089,7 @@
           <xm:sqref>K135</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{989c5a77-120e-4ef7-9401-0b4dd828d508}">
+          <x14:cfRule type="dataBar" id="{8fe7ba6b-37bd-4793-9560-3f7fb8fef8a7}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13095,7 +13098,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{cae0d366-93a6-4f0a-87f7-97e6f0e2992a}">
+          <x14:cfRule type="dataBar" id="{152d7522-c7ca-49a0-b114-a5b724a1f774}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13104,7 +13107,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2eb1fc4a-5d93-4a60-b0db-d1ee26943dac}">
+          <x14:cfRule type="dataBar" id="{130ca20e-fec8-4d00-8c53-292224148420}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13117,7 +13120,7 @@
           <xm:sqref>K140</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cbb04cc1-473f-4d2b-a284-8b1f1e5806b4}">
+          <x14:cfRule type="dataBar" id="{d6931269-8022-4805-a10b-f685ee134c25}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13126,7 +13129,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3217b1c4-012a-43b7-abe5-cc2d9315a9c7}">
+          <x14:cfRule type="dataBar" id="{c6989c46-adfc-4013-b430-805b1c371b96}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13135,7 +13138,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3ae7b952-7515-4592-b63e-e447079a52f1}">
+          <x14:cfRule type="dataBar" id="{8ac1dcf1-5a08-4401-907d-98676ac0adc6}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13148,7 +13151,7 @@
           <xm:sqref>K145</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{48cdd583-f439-4118-a7eb-adc8a5c616fe}">
+          <x14:cfRule type="dataBar" id="{c914cfa2-4f39-449f-b9fe-931802c70420}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13157,7 +13160,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d3055f7e-f86a-438c-82f7-d2a033cad152}">
+          <x14:cfRule type="dataBar" id="{b32f1855-e93c-44f4-9a79-e6b80394f85c}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13166,7 +13169,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a91314e6-a3cc-49f9-8fb6-1a1b91c361a7}">
+          <x14:cfRule type="dataBar" id="{b78adf73-c8f4-487a-8e7d-bcff748e7667}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13179,7 +13182,7 @@
           <xm:sqref>K150</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4ebc1d00-4ee2-40a0-9939-9da9667cd3a9}">
+          <x14:cfRule type="dataBar" id="{86dd25d1-7c19-4d66-b61b-9852ae60cbf0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -13190,7 +13193,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8d732b5e-bc14-4282-8e71-87bd255ba434}">
+          <x14:cfRule type="dataBar" id="{adfd9c4f-6b88-44a4-b255-16336ff6d4f6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13201,14 +13204,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{da16034a-58d6-4ee3-879f-998fe9262ba9}">
+          <x14:cfRule type="dataBar" id="{ab6efa9f-6f94-4293-8f44-388673ea190d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{cfa76ac8-3850-4818-9e3a-f9bdbb56b741}">
+          <x14:cfRule type="dataBar" id="{62e892dc-3651-4ea0-9ebf-4e11e1936ed2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -13219,7 +13222,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9ec8e3d1-84ab-40bc-8a89-192b514cc0d3}">
+          <x14:cfRule type="dataBar" id="{dadba715-1311-4b2c-81a9-1a0e0cc11ac7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -13230,7 +13233,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f30bfd8d-ed71-4c6f-b3a0-76679c60c84b}">
+          <x14:cfRule type="dataBar" id="{67bc41c7-064d-4f54-8835-8b4bbcab6d95}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13241,7 +13244,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{315c8095-5310-4eaa-a869-8f9449157ff3}">
+          <x14:cfRule type="dataBar" id="{edb8592f-6483-4caa-8b83-d9c2ac690782}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13250,7 +13253,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f17ffa41-bedc-48e1-b23f-1bb4c30a26b9}">
+          <x14:cfRule type="dataBar" id="{d043a9cb-21e5-4ec2-b058-a4ea811c027e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13262,7 +13265,7 @@
           <xm:sqref>K57:K58</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9a22b9cf-7e89-4d67-8eba-aba49a51ba58}">
+          <x14:cfRule type="dataBar" id="{c9313cad-6624-4e0f-ae7d-7f037f9f250f}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13271,7 +13274,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1244d046-cc21-4fda-b571-a7d362d41cde}">
+          <x14:cfRule type="dataBar" id="{68fa76f4-0799-4cbc-8303-65ed6c0ca6d9}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13284,7 +13287,7 @@
           <xm:sqref>Y67:Y86</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d1e99945-ac53-4dc1-8da3-679850d6effe}">
+          <x14:cfRule type="dataBar" id="{5b7c410c-f518-4d51-9341-9efd74373b22}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13297,7 +13300,7 @@
           <xm:sqref>Y77:Y86</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e3138be4-72d6-4e3a-b7c7-66d5c29bf4ea}">
+          <x14:cfRule type="dataBar" id="{899b5e31-c46a-49b8-95f6-2baf42f6a076}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13310,7 +13313,7 @@
           <xm:sqref>AB115:AB124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9f273491-a02a-4cd7-bfcd-2952a53ad6af}">
+          <x14:cfRule type="dataBar" id="{f1a4b3e3-fef8-49a8-8bc7-2e173d78582e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13322,7 +13325,7 @@
           <xm:sqref>AD56:AE57</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{22a23e53-6edc-4b7a-a7dc-611f981fdf1d}">
+          <x14:cfRule type="dataBar" id="{8362e5b2-406f-470b-9f71-6247ab730169}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13334,7 +13337,7 @@
           <xm:sqref>AD60:AE63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{967e3a25-e4aa-4369-90fc-9cc22cd8648c}">
+          <x14:cfRule type="dataBar" id="{03f8dc56-1d28-40fd-9ea3-a61cdeef71e8}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13343,7 +13346,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{183064af-aa97-44c2-8498-af7ab78e04b9}">
+          <x14:cfRule type="dataBar" id="{5d7c33c2-0703-4e16-8173-894538552e82}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13352,7 +13355,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{63dc0918-9e24-415e-8733-b93562ce53e5}">
+          <x14:cfRule type="dataBar" id="{a876de58-0e26-4b09-b6ed-bb9db6bd7eb5}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13365,7 +13368,7 @@
           <xm:sqref>F67 F72 F77 F82</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{96d3de2d-b870-49ab-b136-e3181c0b6834}">
+          <x14:cfRule type="dataBar" id="{7a74caab-7c50-49c3-b25c-0be646ed47b7}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13374,7 +13377,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c084a419-1ec3-4567-9e21-dcd7b209b1b5}">
+          <x14:cfRule type="dataBar" id="{3f2352c3-6ec6-4fc9-9b24-f41eadfbc60f}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13383,7 +13386,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1fc1936e-e5cf-4e9c-9475-f450178b8875}">
+          <x14:cfRule type="dataBar" id="{5f8b9665-7e50-4bb3-9c94-e00344d7b40f}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13396,7 +13399,7 @@
           <xm:sqref>K67 K77 K87 K101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4de21f80-ab6a-4c92-a437-40190f95548e}">
+          <x14:cfRule type="dataBar" id="{67e86ebc-2a6d-41a6-aa7a-48a719c20d65}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13405,7 +13408,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2b964334-fe11-4aa8-8f0d-1022d2912d48}">
+          <x14:cfRule type="dataBar" id="{c3b5085b-5262-45b8-90e4-b5b4fab31cbc}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13414,7 +13417,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d77a807a-eb05-4acc-b17f-4375d79cf593}">
+          <x14:cfRule type="dataBar" id="{be17578d-f265-4070-a364-1ba6ef976da4}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13427,7 +13430,7 @@
           <xm:sqref>AB77 AB87</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{976b1155-83b3-4bbf-8409-8486be5b93e2}">
+          <x14:cfRule type="dataBar" id="{a2c91264-2f52-467c-95b1-3b0d15e451da}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13436,7 +13439,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0fe2ae0e-7314-4267-ac36-914a2bfa672b}">
+          <x14:cfRule type="dataBar" id="{f7f8b401-6248-419b-b500-eaf3502d38d5}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13445,7 +13448,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{20f85bdb-025c-442a-94c8-836f14a7c265}">
+          <x14:cfRule type="dataBar" id="{49416b94-fd26-4d9d-994f-6df1882ca6e9}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13458,7 +13461,7 @@
           <xm:sqref>F87 F94 F101 F108</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{49159c48-6ed2-443c-be55-4eb502bef441}">
+          <x14:cfRule type="dataBar" id="{b15f3b6d-6758-45ff-abbc-36130e6136a0}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13467,7 +13470,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8220679b-09a8-47a1-8447-204f78068b0d}">
+          <x14:cfRule type="dataBar" id="{37d9cf3b-6aa4-468e-a81f-876467b1e332}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13480,7 +13483,7 @@
           <xm:sqref>Y87 Y101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a3a14427-3f06-445f-acf1-e471e49b6059}">
+          <x14:cfRule type="dataBar" id="{e249975f-305c-4e94-9257-91fd1a6d53e8}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13489,7 +13492,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c200053b-da06-4955-a4d5-ce67ce21ef45}">
+          <x14:cfRule type="dataBar" id="{b240a561-ec3e-406b-8750-8614b86aed19}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13498,7 +13501,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{42032116-b0b6-42d8-a5be-a5656a9f6de8}">
+          <x14:cfRule type="dataBar" id="{b27629ea-eb70-4edc-8f10-b9a81b9d8624}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13511,7 +13514,7 @@
           <xm:sqref>F115 F120 F125 F130 F135 F140 F145 F150</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{22bd0596-7e92-407c-add9-0198101164b2}">
+          <x14:cfRule type="dataBar" id="{4fd8c3ad-57f4-4b82-9b33-3d148fd0137e}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13520,7 +13523,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{03ad4fb0-7094-4b16-9fb2-5560e45de73e}">
+          <x14:cfRule type="dataBar" id="{5433f30b-40b0-4f97-80a1-b3af0999a273}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13529,7 +13532,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fce6e24a-7487-4151-87d4-701cb4b17b59}">
+          <x14:cfRule type="dataBar" id="{ed943de3-3d56-464c-856a-33d969cf3a04}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13542,7 +13545,7 @@
           <xm:sqref>K115 K125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{30281817-6aff-4384-b9cc-2041747aa4fa}">
+          <x14:cfRule type="dataBar" id="{55abfbfa-66ed-4cfd-a1a3-2b07625cfb9d}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13551,7 +13554,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{438d1385-a242-49fd-8383-ff26e11f080c}">
+          <x14:cfRule type="dataBar" id="{e9de3cd7-e3ff-4b26-8af4-d46824f7900e}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">

--- a/其他楼交接班容量报表空模板.xlsx
+++ b/其他楼交接班容量报表空模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowHeight="22020"/>
   </bookViews>
   <sheets>
     <sheet name="本班组" sheetId="1" r:id="rId1"/>
@@ -1250,7 +1250,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
@@ -1259,6 +1259,7 @@
     <numFmt numFmtId="177" formatCode="0.00;[Red]0.00"/>
     <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="179" formatCode="0.0_ "/>
+    <numFmt numFmtId="180" formatCode="0.0%"/>
   </numFmts>
   <fonts count="43">
     <font>
@@ -2429,7 +2430,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="155">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2801,6 +2802,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3189,28 +3193,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AF154"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="18.1818181818182" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1851851851852" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.9363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.9351851851852" style="1" customWidth="1"/>
     <col min="7" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.4090909090909" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.4074074074074" style="1" customWidth="1"/>
     <col min="10" max="11" width="9" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.9363636363636" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.9351851851852" style="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1" customWidth="1"/>
-    <col min="14" max="14" width="8.74545454545455" style="1" customWidth="1"/>
-    <col min="15" max="15" width="38.1818181818182" style="1" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="1" customWidth="1"/>
+    <col min="15" max="15" width="38.1851851851852" style="1" customWidth="1"/>
     <col min="16" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="12.5909090909091" style="1" customWidth="1"/>
-    <col min="20" max="20" width="16.5090909090909" style="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5925925925926" style="1" customWidth="1"/>
+    <col min="20" max="20" width="16.5092592592593" style="1" customWidth="1"/>
     <col min="21" max="21" width="9" style="1" customWidth="1"/>
-    <col min="22" max="22" width="14.1545454545455" style="1" customWidth="1"/>
+    <col min="22" max="22" width="14.1574074074074" style="1" customWidth="1"/>
     <col min="23" max="24" width="9" style="1" customWidth="1"/>
-    <col min="25" max="25" width="10.2545454545455" style="1" customWidth="1"/>
+    <col min="25" max="25" width="10.25" style="1" customWidth="1"/>
     <col min="26" max="27" width="9" style="1" customWidth="1"/>
-    <col min="28" max="28" width="17.4181818181818" style="1" customWidth="1"/>
+    <col min="28" max="28" width="17.4166666666667" style="1" customWidth="1"/>
     <col min="31" max="31" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6238,7 +6242,7 @@
       <c r="AD64" s="62"/>
       <c r="AE64" s="62"/>
     </row>
-    <row r="65" s="10" customFormat="1" ht="17.5" spans="1:32">
+    <row r="65" s="10" customFormat="1" ht="17.4" spans="1:32">
       <c r="A65" s="134"/>
       <c r="B65" s="135"/>
       <c r="C65" s="135"/>
@@ -6374,19 +6378,19 @@
       </c>
       <c r="D67" s="141"/>
       <c r="E67" s="141"/>
-      <c r="F67" s="141">
+      <c r="F67" s="142">
         <f>E67/2500</f>
         <v>0</v>
       </c>
-      <c r="G67" s="141"/>
-      <c r="H67" s="142" t="s">
+      <c r="G67" s="142"/>
+      <c r="H67" s="143" t="s">
         <v>194</v>
       </c>
-      <c r="I67" s="142" t="s">
+      <c r="I67" s="143" t="s">
         <v>195</v>
       </c>
       <c r="J67" s="141"/>
-      <c r="K67" s="141">
+      <c r="K67" s="142">
         <f>J67/300</f>
         <v>0</v>
       </c>
@@ -6395,16 +6399,16 @@
       </c>
       <c r="M67" s="141"/>
       <c r="N67" s="141"/>
-      <c r="O67" s="143" t="s">
+      <c r="O67" s="144" t="s">
         <v>196</v>
       </c>
       <c r="P67" s="141"/>
       <c r="Q67" s="141"/>
-      <c r="R67" s="144"/>
-      <c r="S67" s="145" t="s">
+      <c r="R67" s="145"/>
+      <c r="S67" s="146" t="s">
         <v>197</v>
       </c>
-      <c r="T67" s="145"/>
+      <c r="T67" s="146"/>
       <c r="U67" s="141">
         <f t="shared" ref="U67:U130" si="0">R67*0.935</f>
         <v>0</v>
@@ -6413,24 +6417,24 @@
         <f t="shared" ref="V67:V130" si="1">U67/215</f>
         <v>0</v>
       </c>
-      <c r="W67" s="142">
+      <c r="W67" s="143">
         <v>202</v>
       </c>
       <c r="X67" s="141">
         <f>SUM(U67:U76)</f>
         <v>0</v>
       </c>
-      <c r="Y67" s="141">
+      <c r="Y67" s="142">
         <f>X67/2150</f>
         <v>0</v>
       </c>
       <c r="Z67" s="141">
         <v>170</v>
       </c>
-      <c r="AA67" s="146">
+      <c r="AA67" s="147">
         <v>168</v>
       </c>
-      <c r="AB67" s="141">
+      <c r="AB67" s="142">
         <f>67/Z67</f>
         <v>0.394117647058824</v>
       </c>
@@ -6440,10 +6444,10 @@
       <c r="AD67" s="141">
         <v>0</v>
       </c>
-      <c r="AE67" s="147" t="s">
+      <c r="AE67" s="148" t="s">
         <v>198</v>
       </c>
-      <c r="AF67" s="148"/>
+      <c r="AF67" s="149"/>
     </row>
     <row r="68" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A68" s="141"/>
@@ -6451,25 +6455,25 @@
       <c r="C68" s="141"/>
       <c r="D68" s="141"/>
       <c r="E68" s="141"/>
-      <c r="F68" s="141"/>
-      <c r="G68" s="141"/>
-      <c r="H68" s="142"/>
-      <c r="I68" s="142"/>
+      <c r="F68" s="142"/>
+      <c r="G68" s="142"/>
+      <c r="H68" s="143"/>
+      <c r="I68" s="143"/>
       <c r="J68" s="141"/>
-      <c r="K68" s="141"/>
+      <c r="K68" s="142"/>
       <c r="L68" s="141"/>
       <c r="M68" s="141"/>
       <c r="N68" s="141"/>
-      <c r="O68" s="143" t="s">
+      <c r="O68" s="144" t="s">
         <v>199</v>
       </c>
       <c r="P68" s="141"/>
       <c r="Q68" s="141"/>
-      <c r="R68" s="144"/>
-      <c r="S68" s="145" t="s">
+      <c r="R68" s="145"/>
+      <c r="S68" s="146" t="s">
         <v>200</v>
       </c>
-      <c r="T68" s="145"/>
+      <c r="T68" s="146"/>
       <c r="U68" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6478,16 +6482,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W68" s="142"/>
+      <c r="W68" s="143"/>
       <c r="X68" s="141"/>
-      <c r="Y68" s="141"/>
+      <c r="Y68" s="142"/>
       <c r="Z68" s="141"/>
-      <c r="AA68" s="146"/>
-      <c r="AB68" s="141"/>
+      <c r="AA68" s="147"/>
+      <c r="AB68" s="142"/>
       <c r="AC68" s="141"/>
       <c r="AD68" s="141"/>
-      <c r="AE68" s="149"/>
-      <c r="AF68" s="148"/>
+      <c r="AE68" s="150"/>
+      <c r="AF68" s="149"/>
     </row>
     <row r="69" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A69" s="141"/>
@@ -6495,25 +6499,25 @@
       <c r="C69" s="141"/>
       <c r="D69" s="141"/>
       <c r="E69" s="141"/>
-      <c r="F69" s="141"/>
-      <c r="G69" s="141"/>
-      <c r="H69" s="142"/>
-      <c r="I69" s="142"/>
+      <c r="F69" s="142"/>
+      <c r="G69" s="142"/>
+      <c r="H69" s="143"/>
+      <c r="I69" s="143"/>
       <c r="J69" s="141"/>
-      <c r="K69" s="141"/>
+      <c r="K69" s="142"/>
       <c r="L69" s="141"/>
       <c r="M69" s="141"/>
       <c r="N69" s="141"/>
-      <c r="O69" s="143" t="s">
+      <c r="O69" s="144" t="s">
         <v>201</v>
       </c>
       <c r="P69" s="141"/>
       <c r="Q69" s="141"/>
-      <c r="R69" s="144"/>
-      <c r="S69" s="145" t="s">
+      <c r="R69" s="145"/>
+      <c r="S69" s="146" t="s">
         <v>202</v>
       </c>
-      <c r="T69" s="145"/>
+      <c r="T69" s="146"/>
       <c r="U69" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6522,16 +6526,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W69" s="142"/>
+      <c r="W69" s="143"/>
       <c r="X69" s="141"/>
-      <c r="Y69" s="141"/>
+      <c r="Y69" s="142"/>
       <c r="Z69" s="141"/>
-      <c r="AA69" s="146"/>
-      <c r="AB69" s="141"/>
+      <c r="AA69" s="147"/>
+      <c r="AB69" s="142"/>
       <c r="AC69" s="141"/>
       <c r="AD69" s="141"/>
-      <c r="AE69" s="150"/>
-      <c r="AF69" s="148"/>
+      <c r="AE69" s="151"/>
+      <c r="AF69" s="149"/>
     </row>
     <row r="70" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A70" s="141"/>
@@ -6539,25 +6543,25 @@
       <c r="C70" s="141"/>
       <c r="D70" s="141"/>
       <c r="E70" s="141"/>
-      <c r="F70" s="141"/>
-      <c r="G70" s="141"/>
-      <c r="H70" s="142"/>
-      <c r="I70" s="142"/>
+      <c r="F70" s="142"/>
+      <c r="G70" s="142"/>
+      <c r="H70" s="143"/>
+      <c r="I70" s="143"/>
       <c r="J70" s="141"/>
-      <c r="K70" s="141"/>
+      <c r="K70" s="142"/>
       <c r="L70" s="141"/>
       <c r="M70" s="141"/>
       <c r="N70" s="141"/>
-      <c r="O70" s="143" t="s">
+      <c r="O70" s="144" t="s">
         <v>203</v>
       </c>
       <c r="P70" s="141"/>
       <c r="Q70" s="141"/>
-      <c r="R70" s="144"/>
-      <c r="S70" s="145" t="s">
+      <c r="R70" s="145"/>
+      <c r="S70" s="146" t="s">
         <v>204</v>
       </c>
-      <c r="T70" s="145"/>
+      <c r="T70" s="146"/>
       <c r="U70" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6566,16 +6570,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W70" s="142"/>
+      <c r="W70" s="143"/>
       <c r="X70" s="141"/>
-      <c r="Y70" s="141"/>
+      <c r="Y70" s="142"/>
       <c r="Z70" s="141"/>
-      <c r="AA70" s="146"/>
-      <c r="AB70" s="141"/>
+      <c r="AA70" s="147"/>
+      <c r="AB70" s="142"/>
       <c r="AC70" s="141"/>
       <c r="AD70" s="141"/>
-      <c r="AE70" s="147"/>
-      <c r="AF70" s="148"/>
+      <c r="AE70" s="148"/>
+      <c r="AF70" s="149"/>
     </row>
     <row r="71" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A71" s="141"/>
@@ -6583,25 +6587,25 @@
       <c r="C71" s="141"/>
       <c r="D71" s="141"/>
       <c r="E71" s="141"/>
-      <c r="F71" s="141"/>
-      <c r="G71" s="141"/>
-      <c r="H71" s="142"/>
-      <c r="I71" s="142"/>
+      <c r="F71" s="142"/>
+      <c r="G71" s="142"/>
+      <c r="H71" s="143"/>
+      <c r="I71" s="143"/>
       <c r="J71" s="141"/>
-      <c r="K71" s="141"/>
+      <c r="K71" s="142"/>
       <c r="L71" s="141"/>
       <c r="M71" s="141"/>
       <c r="N71" s="141"/>
-      <c r="O71" s="143" t="s">
+      <c r="O71" s="144" t="s">
         <v>205</v>
       </c>
       <c r="P71" s="141"/>
       <c r="Q71" s="141"/>
-      <c r="R71" s="144"/>
-      <c r="S71" s="145" t="s">
+      <c r="R71" s="145"/>
+      <c r="S71" s="146" t="s">
         <v>206</v>
       </c>
-      <c r="T71" s="145"/>
+      <c r="T71" s="146"/>
       <c r="U71" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6610,16 +6614,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W71" s="142"/>
+      <c r="W71" s="143"/>
       <c r="X71" s="141"/>
-      <c r="Y71" s="141"/>
+      <c r="Y71" s="142"/>
       <c r="Z71" s="141"/>
-      <c r="AA71" s="146"/>
-      <c r="AB71" s="141"/>
+      <c r="AA71" s="147"/>
+      <c r="AB71" s="142"/>
       <c r="AC71" s="141"/>
       <c r="AD71" s="141"/>
-      <c r="AE71" s="150"/>
-      <c r="AF71" s="148"/>
+      <c r="AE71" s="151"/>
+      <c r="AF71" s="149"/>
     </row>
     <row r="72" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A72" s="141"/>
@@ -6631,30 +6635,30 @@
       </c>
       <c r="D72" s="141"/>
       <c r="E72" s="141"/>
-      <c r="F72" s="141">
+      <c r="F72" s="142">
         <f>E72/2500</f>
         <v>0</v>
       </c>
-      <c r="G72" s="141"/>
-      <c r="H72" s="142" t="s">
+      <c r="G72" s="142"/>
+      <c r="H72" s="143" t="s">
         <v>194</v>
       </c>
-      <c r="I72" s="142"/>
+      <c r="I72" s="143"/>
       <c r="J72" s="141"/>
-      <c r="K72" s="141"/>
+      <c r="K72" s="142"/>
       <c r="L72" s="141"/>
       <c r="M72" s="141"/>
       <c r="N72" s="141"/>
-      <c r="O72" s="143" t="s">
+      <c r="O72" s="144" t="s">
         <v>208</v>
       </c>
       <c r="P72" s="141"/>
       <c r="Q72" s="141"/>
-      <c r="R72" s="144"/>
-      <c r="S72" s="145" t="s">
+      <c r="R72" s="145"/>
+      <c r="S72" s="146" t="s">
         <v>209</v>
       </c>
-      <c r="T72" s="145"/>
+      <c r="T72" s="146"/>
       <c r="U72" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6663,18 +6667,18 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W72" s="142"/>
+      <c r="W72" s="143"/>
       <c r="X72" s="141"/>
-      <c r="Y72" s="141"/>
+      <c r="Y72" s="142"/>
       <c r="Z72" s="141"/>
-      <c r="AA72" s="146"/>
-      <c r="AB72" s="141"/>
+      <c r="AA72" s="147"/>
+      <c r="AB72" s="142"/>
       <c r="AC72" s="141"/>
       <c r="AD72" s="141"/>
-      <c r="AE72" s="147" t="s">
+      <c r="AE72" s="148" t="s">
         <v>210</v>
       </c>
-      <c r="AF72" s="148"/>
+      <c r="AF72" s="149"/>
     </row>
     <row r="73" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A73" s="141"/>
@@ -6682,25 +6686,25 @@
       <c r="C73" s="141"/>
       <c r="D73" s="141"/>
       <c r="E73" s="141"/>
-      <c r="F73" s="141"/>
-      <c r="G73" s="141"/>
-      <c r="H73" s="142"/>
-      <c r="I73" s="142"/>
+      <c r="F73" s="142"/>
+      <c r="G73" s="142"/>
+      <c r="H73" s="143"/>
+      <c r="I73" s="143"/>
       <c r="J73" s="141"/>
-      <c r="K73" s="141"/>
+      <c r="K73" s="142"/>
       <c r="L73" s="141"/>
       <c r="M73" s="141"/>
       <c r="N73" s="141"/>
-      <c r="O73" s="143" t="s">
+      <c r="O73" s="144" t="s">
         <v>211</v>
       </c>
       <c r="P73" s="141"/>
       <c r="Q73" s="141"/>
-      <c r="R73" s="144"/>
-      <c r="S73" s="145" t="s">
+      <c r="R73" s="145"/>
+      <c r="S73" s="146" t="s">
         <v>212</v>
       </c>
-      <c r="T73" s="145"/>
+      <c r="T73" s="146"/>
       <c r="U73" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6709,16 +6713,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W73" s="142"/>
+      <c r="W73" s="143"/>
       <c r="X73" s="141"/>
-      <c r="Y73" s="141"/>
+      <c r="Y73" s="142"/>
       <c r="Z73" s="141"/>
-      <c r="AA73" s="146"/>
-      <c r="AB73" s="141"/>
+      <c r="AA73" s="147"/>
+      <c r="AB73" s="142"/>
       <c r="AC73" s="141"/>
       <c r="AD73" s="141"/>
-      <c r="AE73" s="149"/>
-      <c r="AF73" s="148"/>
+      <c r="AE73" s="150"/>
+      <c r="AF73" s="149"/>
     </row>
     <row r="74" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A74" s="141"/>
@@ -6726,25 +6730,25 @@
       <c r="C74" s="141"/>
       <c r="D74" s="141"/>
       <c r="E74" s="141"/>
-      <c r="F74" s="141"/>
-      <c r="G74" s="141"/>
-      <c r="H74" s="142"/>
-      <c r="I74" s="142"/>
+      <c r="F74" s="142"/>
+      <c r="G74" s="142"/>
+      <c r="H74" s="143"/>
+      <c r="I74" s="143"/>
       <c r="J74" s="141"/>
-      <c r="K74" s="141"/>
+      <c r="K74" s="142"/>
       <c r="L74" s="141"/>
       <c r="M74" s="141"/>
       <c r="N74" s="141"/>
-      <c r="O74" s="143" t="s">
+      <c r="O74" s="144" t="s">
         <v>213</v>
       </c>
       <c r="P74" s="141"/>
       <c r="Q74" s="141"/>
-      <c r="R74" s="144"/>
-      <c r="S74" s="145" t="s">
+      <c r="R74" s="145"/>
+      <c r="S74" s="146" t="s">
         <v>214</v>
       </c>
-      <c r="T74" s="145"/>
+      <c r="T74" s="146"/>
       <c r="U74" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6753,16 +6757,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W74" s="142"/>
+      <c r="W74" s="143"/>
       <c r="X74" s="141"/>
-      <c r="Y74" s="141"/>
+      <c r="Y74" s="142"/>
       <c r="Z74" s="141"/>
-      <c r="AA74" s="146"/>
-      <c r="AB74" s="141"/>
+      <c r="AA74" s="147"/>
+      <c r="AB74" s="142"/>
       <c r="AC74" s="141"/>
       <c r="AD74" s="141"/>
-      <c r="AE74" s="150"/>
-      <c r="AF74" s="148"/>
+      <c r="AE74" s="151"/>
+      <c r="AF74" s="149"/>
     </row>
     <row r="75" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A75" s="141"/>
@@ -6770,25 +6774,25 @@
       <c r="C75" s="141"/>
       <c r="D75" s="141"/>
       <c r="E75" s="141"/>
-      <c r="F75" s="141"/>
-      <c r="G75" s="141"/>
-      <c r="H75" s="142"/>
-      <c r="I75" s="142"/>
+      <c r="F75" s="142"/>
+      <c r="G75" s="142"/>
+      <c r="H75" s="143"/>
+      <c r="I75" s="143"/>
       <c r="J75" s="141"/>
-      <c r="K75" s="141"/>
+      <c r="K75" s="142"/>
       <c r="L75" s="141"/>
       <c r="M75" s="141"/>
       <c r="N75" s="141"/>
-      <c r="O75" s="143" t="s">
+      <c r="O75" s="144" t="s">
         <v>215</v>
       </c>
       <c r="P75" s="141"/>
       <c r="Q75" s="141"/>
-      <c r="R75" s="144"/>
-      <c r="S75" s="145" t="s">
+      <c r="R75" s="145"/>
+      <c r="S75" s="146" t="s">
         <v>216</v>
       </c>
-      <c r="T75" s="145"/>
+      <c r="T75" s="146"/>
       <c r="U75" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6797,16 +6801,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W75" s="142"/>
+      <c r="W75" s="143"/>
       <c r="X75" s="141"/>
-      <c r="Y75" s="141"/>
+      <c r="Y75" s="142"/>
       <c r="Z75" s="141"/>
-      <c r="AA75" s="146"/>
-      <c r="AB75" s="141"/>
+      <c r="AA75" s="147"/>
+      <c r="AB75" s="142"/>
       <c r="AC75" s="141"/>
       <c r="AD75" s="141"/>
-      <c r="AE75" s="147"/>
-      <c r="AF75" s="148"/>
+      <c r="AE75" s="148"/>
+      <c r="AF75" s="149"/>
     </row>
     <row r="76" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A76" s="141"/>
@@ -6814,25 +6818,25 @@
       <c r="C76" s="141"/>
       <c r="D76" s="141"/>
       <c r="E76" s="141"/>
-      <c r="F76" s="141"/>
-      <c r="G76" s="141"/>
-      <c r="H76" s="142"/>
-      <c r="I76" s="142"/>
+      <c r="F76" s="142"/>
+      <c r="G76" s="142"/>
+      <c r="H76" s="143"/>
+      <c r="I76" s="143"/>
       <c r="J76" s="141"/>
-      <c r="K76" s="141"/>
+      <c r="K76" s="142"/>
       <c r="L76" s="141"/>
       <c r="M76" s="141"/>
       <c r="N76" s="141"/>
-      <c r="O76" s="143" t="s">
+      <c r="O76" s="144" t="s">
         <v>217</v>
       </c>
       <c r="P76" s="141"/>
       <c r="Q76" s="141"/>
-      <c r="R76" s="144"/>
-      <c r="S76" s="145" t="s">
+      <c r="R76" s="145"/>
+      <c r="S76" s="146" t="s">
         <v>218</v>
       </c>
-      <c r="T76" s="145"/>
+      <c r="T76" s="146"/>
       <c r="U76" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6841,16 +6845,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W76" s="142"/>
+      <c r="W76" s="143"/>
       <c r="X76" s="141"/>
-      <c r="Y76" s="141"/>
+      <c r="Y76" s="142"/>
       <c r="Z76" s="141"/>
-      <c r="AA76" s="146"/>
-      <c r="AB76" s="141"/>
+      <c r="AA76" s="147"/>
+      <c r="AB76" s="142"/>
       <c r="AC76" s="141"/>
       <c r="AD76" s="141"/>
-      <c r="AE76" s="150"/>
-      <c r="AF76" s="148"/>
+      <c r="AE76" s="151"/>
+      <c r="AF76" s="149"/>
     </row>
     <row r="77" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A77" s="141" t="s">
@@ -6864,19 +6868,19 @@
       </c>
       <c r="D77" s="141"/>
       <c r="E77" s="141"/>
-      <c r="F77" s="141">
+      <c r="F77" s="142">
         <f>E77/2500</f>
         <v>0</v>
       </c>
-      <c r="G77" s="141"/>
-      <c r="H77" s="142" t="s">
+      <c r="G77" s="142"/>
+      <c r="H77" s="143" t="s">
         <v>194</v>
       </c>
-      <c r="I77" s="151" t="s">
+      <c r="I77" s="152" t="s">
         <v>221</v>
       </c>
       <c r="J77" s="141"/>
-      <c r="K77" s="141">
+      <c r="K77" s="142">
         <f>J77/300</f>
         <v>0</v>
       </c>
@@ -6885,16 +6889,16 @@
       </c>
       <c r="M77" s="141"/>
       <c r="N77" s="141"/>
-      <c r="O77" s="143" t="s">
+      <c r="O77" s="144" t="s">
         <v>222</v>
       </c>
       <c r="P77" s="141"/>
       <c r="Q77" s="141"/>
-      <c r="R77" s="144"/>
-      <c r="S77" s="145" t="s">
+      <c r="R77" s="145"/>
+      <c r="S77" s="146" t="s">
         <v>223</v>
       </c>
-      <c r="T77" s="145"/>
+      <c r="T77" s="146"/>
       <c r="U77" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6903,24 +6907,24 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W77" s="142">
+      <c r="W77" s="143">
         <v>201</v>
       </c>
       <c r="X77" s="141">
         <f>SUM(U77:U86)</f>
         <v>0</v>
       </c>
-      <c r="Y77" s="141">
+      <c r="Y77" s="142">
         <f>X77/2150</f>
         <v>0</v>
       </c>
       <c r="Z77" s="141">
         <v>170</v>
       </c>
-      <c r="AA77" s="146">
+      <c r="AA77" s="147">
         <v>170</v>
       </c>
-      <c r="AB77" s="141">
+      <c r="AB77" s="142">
         <f>77/Z77</f>
         <v>0.452941176470588</v>
       </c>
@@ -6930,10 +6934,10 @@
       <c r="AD77" s="141">
         <v>0</v>
       </c>
-      <c r="AE77" s="147" t="s">
+      <c r="AE77" s="148" t="s">
         <v>198</v>
       </c>
-      <c r="AF77" s="148"/>
+      <c r="AF77" s="149"/>
     </row>
     <row r="78" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A78" s="141"/>
@@ -6941,25 +6945,25 @@
       <c r="C78" s="141"/>
       <c r="D78" s="141"/>
       <c r="E78" s="141"/>
-      <c r="F78" s="141"/>
-      <c r="G78" s="141"/>
-      <c r="H78" s="142"/>
-      <c r="I78" s="151"/>
+      <c r="F78" s="142"/>
+      <c r="G78" s="142"/>
+      <c r="H78" s="143"/>
+      <c r="I78" s="152"/>
       <c r="J78" s="141"/>
-      <c r="K78" s="141"/>
+      <c r="K78" s="142"/>
       <c r="L78" s="141"/>
       <c r="M78" s="141"/>
       <c r="N78" s="141"/>
-      <c r="O78" s="143" t="s">
+      <c r="O78" s="144" t="s">
         <v>224</v>
       </c>
       <c r="P78" s="141"/>
       <c r="Q78" s="141"/>
-      <c r="R78" s="144"/>
-      <c r="S78" s="145" t="s">
+      <c r="R78" s="145"/>
+      <c r="S78" s="146" t="s">
         <v>225</v>
       </c>
-      <c r="T78" s="145"/>
+      <c r="T78" s="146"/>
       <c r="U78" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6968,16 +6972,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W78" s="142"/>
+      <c r="W78" s="143"/>
       <c r="X78" s="141"/>
-      <c r="Y78" s="141"/>
+      <c r="Y78" s="142"/>
       <c r="Z78" s="141"/>
-      <c r="AA78" s="146"/>
-      <c r="AB78" s="141"/>
+      <c r="AA78" s="147"/>
+      <c r="AB78" s="142"/>
       <c r="AC78" s="141"/>
       <c r="AD78" s="141"/>
-      <c r="AE78" s="149"/>
-      <c r="AF78" s="148"/>
+      <c r="AE78" s="150"/>
+      <c r="AF78" s="149"/>
     </row>
     <row r="79" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A79" s="141"/>
@@ -6985,25 +6989,25 @@
       <c r="C79" s="141"/>
       <c r="D79" s="141"/>
       <c r="E79" s="141"/>
-      <c r="F79" s="141"/>
-      <c r="G79" s="141"/>
-      <c r="H79" s="142"/>
-      <c r="I79" s="151"/>
+      <c r="F79" s="142"/>
+      <c r="G79" s="142"/>
+      <c r="H79" s="143"/>
+      <c r="I79" s="152"/>
       <c r="J79" s="141"/>
-      <c r="K79" s="141"/>
+      <c r="K79" s="142"/>
       <c r="L79" s="141"/>
       <c r="M79" s="141"/>
       <c r="N79" s="141"/>
-      <c r="O79" s="143" t="s">
+      <c r="O79" s="144" t="s">
         <v>226</v>
       </c>
       <c r="P79" s="141"/>
       <c r="Q79" s="141"/>
-      <c r="R79" s="144"/>
-      <c r="S79" s="145" t="s">
+      <c r="R79" s="145"/>
+      <c r="S79" s="146" t="s">
         <v>227</v>
       </c>
-      <c r="T79" s="145"/>
+      <c r="T79" s="146"/>
       <c r="U79" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7012,16 +7016,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W79" s="142"/>
+      <c r="W79" s="143"/>
       <c r="X79" s="141"/>
-      <c r="Y79" s="141"/>
+      <c r="Y79" s="142"/>
       <c r="Z79" s="141"/>
-      <c r="AA79" s="146"/>
-      <c r="AB79" s="141"/>
+      <c r="AA79" s="147"/>
+      <c r="AB79" s="142"/>
       <c r="AC79" s="141"/>
       <c r="AD79" s="141"/>
-      <c r="AE79" s="150"/>
-      <c r="AF79" s="148"/>
+      <c r="AE79" s="151"/>
+      <c r="AF79" s="149"/>
     </row>
     <row r="80" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A80" s="141"/>
@@ -7029,25 +7033,25 @@
       <c r="C80" s="141"/>
       <c r="D80" s="141"/>
       <c r="E80" s="141"/>
-      <c r="F80" s="141"/>
-      <c r="G80" s="141"/>
-      <c r="H80" s="142"/>
-      <c r="I80" s="151"/>
+      <c r="F80" s="142"/>
+      <c r="G80" s="142"/>
+      <c r="H80" s="143"/>
+      <c r="I80" s="152"/>
       <c r="J80" s="141"/>
-      <c r="K80" s="141"/>
+      <c r="K80" s="142"/>
       <c r="L80" s="141"/>
       <c r="M80" s="141"/>
       <c r="N80" s="141"/>
-      <c r="O80" s="143" t="s">
+      <c r="O80" s="144" t="s">
         <v>228</v>
       </c>
       <c r="P80" s="141"/>
       <c r="Q80" s="141"/>
-      <c r="R80" s="144"/>
-      <c r="S80" s="145" t="s">
+      <c r="R80" s="145"/>
+      <c r="S80" s="146" t="s">
         <v>229</v>
       </c>
-      <c r="T80" s="145"/>
+      <c r="T80" s="146"/>
       <c r="U80" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7056,16 +7060,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W80" s="142"/>
+      <c r="W80" s="143"/>
       <c r="X80" s="141"/>
-      <c r="Y80" s="141"/>
+      <c r="Y80" s="142"/>
       <c r="Z80" s="141"/>
-      <c r="AA80" s="146"/>
-      <c r="AB80" s="141"/>
+      <c r="AA80" s="147"/>
+      <c r="AB80" s="142"/>
       <c r="AC80" s="141"/>
       <c r="AD80" s="141"/>
-      <c r="AE80" s="147"/>
-      <c r="AF80" s="148"/>
+      <c r="AE80" s="148"/>
+      <c r="AF80" s="149"/>
     </row>
     <row r="81" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A81" s="141"/>
@@ -7073,25 +7077,25 @@
       <c r="C81" s="141"/>
       <c r="D81" s="141"/>
       <c r="E81" s="141"/>
-      <c r="F81" s="141"/>
-      <c r="G81" s="141"/>
-      <c r="H81" s="142"/>
-      <c r="I81" s="151"/>
+      <c r="F81" s="142"/>
+      <c r="G81" s="142"/>
+      <c r="H81" s="143"/>
+      <c r="I81" s="152"/>
       <c r="J81" s="141"/>
-      <c r="K81" s="141"/>
+      <c r="K81" s="142"/>
       <c r="L81" s="141"/>
       <c r="M81" s="141"/>
       <c r="N81" s="141"/>
-      <c r="O81" s="143" t="s">
+      <c r="O81" s="144" t="s">
         <v>230</v>
       </c>
       <c r="P81" s="141"/>
       <c r="Q81" s="141"/>
-      <c r="R81" s="144"/>
-      <c r="S81" s="145" t="s">
+      <c r="R81" s="145"/>
+      <c r="S81" s="146" t="s">
         <v>231</v>
       </c>
-      <c r="T81" s="145"/>
+      <c r="T81" s="146"/>
       <c r="U81" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7100,16 +7104,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W81" s="142"/>
+      <c r="W81" s="143"/>
       <c r="X81" s="141"/>
-      <c r="Y81" s="141"/>
+      <c r="Y81" s="142"/>
       <c r="Z81" s="141"/>
-      <c r="AA81" s="146"/>
-      <c r="AB81" s="141"/>
+      <c r="AA81" s="147"/>
+      <c r="AB81" s="142"/>
       <c r="AC81" s="141"/>
       <c r="AD81" s="141"/>
-      <c r="AE81" s="150"/>
-      <c r="AF81" s="148"/>
+      <c r="AE81" s="151"/>
+      <c r="AF81" s="149"/>
     </row>
     <row r="82" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A82" s="141"/>
@@ -7121,30 +7125,30 @@
       </c>
       <c r="D82" s="141"/>
       <c r="E82" s="141"/>
-      <c r="F82" s="141">
+      <c r="F82" s="142">
         <f>E82/2500</f>
         <v>0</v>
       </c>
-      <c r="G82" s="141"/>
-      <c r="H82" s="142" t="s">
+      <c r="G82" s="142"/>
+      <c r="H82" s="143" t="s">
         <v>194</v>
       </c>
-      <c r="I82" s="151"/>
+      <c r="I82" s="152"/>
       <c r="J82" s="141"/>
-      <c r="K82" s="141"/>
+      <c r="K82" s="142"/>
       <c r="L82" s="141"/>
       <c r="M82" s="141"/>
       <c r="N82" s="141"/>
-      <c r="O82" s="143" t="s">
+      <c r="O82" s="144" t="s">
         <v>233</v>
       </c>
       <c r="P82" s="141"/>
       <c r="Q82" s="141"/>
-      <c r="R82" s="144"/>
-      <c r="S82" s="145" t="s">
+      <c r="R82" s="145"/>
+      <c r="S82" s="146" t="s">
         <v>234</v>
       </c>
-      <c r="T82" s="145"/>
+      <c r="T82" s="146"/>
       <c r="U82" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7153,18 +7157,18 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W82" s="142"/>
+      <c r="W82" s="143"/>
       <c r="X82" s="141"/>
-      <c r="Y82" s="141"/>
+      <c r="Y82" s="142"/>
       <c r="Z82" s="141"/>
-      <c r="AA82" s="146"/>
-      <c r="AB82" s="141"/>
+      <c r="AA82" s="147"/>
+      <c r="AB82" s="142"/>
       <c r="AC82" s="141"/>
       <c r="AD82" s="141"/>
-      <c r="AE82" s="147" t="s">
+      <c r="AE82" s="148" t="s">
         <v>210</v>
       </c>
-      <c r="AF82" s="148"/>
+      <c r="AF82" s="149"/>
     </row>
     <row r="83" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A83" s="141"/>
@@ -7172,25 +7176,25 @@
       <c r="C83" s="141"/>
       <c r="D83" s="141"/>
       <c r="E83" s="141"/>
-      <c r="F83" s="141"/>
-      <c r="G83" s="141"/>
-      <c r="H83" s="142"/>
-      <c r="I83" s="151"/>
+      <c r="F83" s="142"/>
+      <c r="G83" s="142"/>
+      <c r="H83" s="143"/>
+      <c r="I83" s="152"/>
       <c r="J83" s="141"/>
-      <c r="K83" s="141"/>
+      <c r="K83" s="142"/>
       <c r="L83" s="141"/>
       <c r="M83" s="141"/>
       <c r="N83" s="141"/>
-      <c r="O83" s="143" t="s">
+      <c r="O83" s="144" t="s">
         <v>235</v>
       </c>
       <c r="P83" s="141"/>
       <c r="Q83" s="141"/>
-      <c r="R83" s="144"/>
-      <c r="S83" s="145" t="s">
+      <c r="R83" s="145"/>
+      <c r="S83" s="146" t="s">
         <v>236</v>
       </c>
-      <c r="T83" s="145"/>
+      <c r="T83" s="146"/>
       <c r="U83" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7199,16 +7203,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W83" s="142"/>
+      <c r="W83" s="143"/>
       <c r="X83" s="141"/>
-      <c r="Y83" s="141"/>
+      <c r="Y83" s="142"/>
       <c r="Z83" s="141"/>
-      <c r="AA83" s="146"/>
-      <c r="AB83" s="141"/>
+      <c r="AA83" s="147"/>
+      <c r="AB83" s="142"/>
       <c r="AC83" s="141"/>
       <c r="AD83" s="141"/>
-      <c r="AE83" s="149"/>
-      <c r="AF83" s="148"/>
+      <c r="AE83" s="150"/>
+      <c r="AF83" s="149"/>
     </row>
     <row r="84" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A84" s="141"/>
@@ -7216,25 +7220,25 @@
       <c r="C84" s="141"/>
       <c r="D84" s="141"/>
       <c r="E84" s="141"/>
-      <c r="F84" s="141"/>
-      <c r="G84" s="141"/>
-      <c r="H84" s="142"/>
-      <c r="I84" s="151"/>
+      <c r="F84" s="142"/>
+      <c r="G84" s="142"/>
+      <c r="H84" s="143"/>
+      <c r="I84" s="152"/>
       <c r="J84" s="141"/>
-      <c r="K84" s="141"/>
+      <c r="K84" s="142"/>
       <c r="L84" s="141"/>
       <c r="M84" s="141"/>
       <c r="N84" s="141"/>
-      <c r="O84" s="143" t="s">
+      <c r="O84" s="144" t="s">
         <v>237</v>
       </c>
       <c r="P84" s="141"/>
       <c r="Q84" s="141"/>
-      <c r="R84" s="144"/>
-      <c r="S84" s="145" t="s">
+      <c r="R84" s="145"/>
+      <c r="S84" s="146" t="s">
         <v>238</v>
       </c>
-      <c r="T84" s="145"/>
+      <c r="T84" s="146"/>
       <c r="U84" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7243,16 +7247,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W84" s="142"/>
+      <c r="W84" s="143"/>
       <c r="X84" s="141"/>
-      <c r="Y84" s="141"/>
+      <c r="Y84" s="142"/>
       <c r="Z84" s="141"/>
-      <c r="AA84" s="146"/>
-      <c r="AB84" s="141"/>
+      <c r="AA84" s="147"/>
+      <c r="AB84" s="142"/>
       <c r="AC84" s="141"/>
       <c r="AD84" s="141"/>
-      <c r="AE84" s="150"/>
-      <c r="AF84" s="148"/>
+      <c r="AE84" s="151"/>
+      <c r="AF84" s="149"/>
     </row>
     <row r="85" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A85" s="141"/>
@@ -7260,25 +7264,25 @@
       <c r="C85" s="141"/>
       <c r="D85" s="141"/>
       <c r="E85" s="141"/>
-      <c r="F85" s="141"/>
-      <c r="G85" s="141"/>
-      <c r="H85" s="142"/>
-      <c r="I85" s="151"/>
+      <c r="F85" s="142"/>
+      <c r="G85" s="142"/>
+      <c r="H85" s="143"/>
+      <c r="I85" s="152"/>
       <c r="J85" s="141"/>
-      <c r="K85" s="141"/>
+      <c r="K85" s="142"/>
       <c r="L85" s="141"/>
       <c r="M85" s="141"/>
       <c r="N85" s="141"/>
-      <c r="O85" s="143" t="s">
+      <c r="O85" s="144" t="s">
         <v>239</v>
       </c>
       <c r="P85" s="141"/>
       <c r="Q85" s="141"/>
-      <c r="R85" s="144"/>
-      <c r="S85" s="145" t="s">
+      <c r="R85" s="145"/>
+      <c r="S85" s="146" t="s">
         <v>240</v>
       </c>
-      <c r="T85" s="145"/>
+      <c r="T85" s="146"/>
       <c r="U85" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7287,16 +7291,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W85" s="142"/>
+      <c r="W85" s="143"/>
       <c r="X85" s="141"/>
-      <c r="Y85" s="141"/>
+      <c r="Y85" s="142"/>
       <c r="Z85" s="141"/>
-      <c r="AA85" s="146"/>
-      <c r="AB85" s="141"/>
+      <c r="AA85" s="147"/>
+      <c r="AB85" s="142"/>
       <c r="AC85" s="141"/>
       <c r="AD85" s="141"/>
-      <c r="AE85" s="147"/>
-      <c r="AF85" s="148"/>
+      <c r="AE85" s="148"/>
+      <c r="AF85" s="149"/>
     </row>
     <row r="86" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A86" s="141"/>
@@ -7304,25 +7308,25 @@
       <c r="C86" s="141"/>
       <c r="D86" s="141"/>
       <c r="E86" s="141"/>
-      <c r="F86" s="141"/>
-      <c r="G86" s="141"/>
-      <c r="H86" s="142"/>
-      <c r="I86" s="151"/>
+      <c r="F86" s="142"/>
+      <c r="G86" s="142"/>
+      <c r="H86" s="143"/>
+      <c r="I86" s="152"/>
       <c r="J86" s="141"/>
-      <c r="K86" s="141"/>
+      <c r="K86" s="142"/>
       <c r="L86" s="141"/>
       <c r="M86" s="141"/>
       <c r="N86" s="141"/>
-      <c r="O86" s="143" t="s">
+      <c r="O86" s="144" t="s">
         <v>241</v>
       </c>
       <c r="P86" s="141"/>
       <c r="Q86" s="141"/>
-      <c r="R86" s="144"/>
-      <c r="S86" s="145" t="s">
+      <c r="R86" s="145"/>
+      <c r="S86" s="146" t="s">
         <v>242</v>
       </c>
-      <c r="T86" s="145"/>
+      <c r="T86" s="146"/>
       <c r="U86" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7331,16 +7335,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W86" s="142"/>
+      <c r="W86" s="143"/>
       <c r="X86" s="141"/>
-      <c r="Y86" s="141"/>
+      <c r="Y86" s="142"/>
       <c r="Z86" s="141"/>
-      <c r="AA86" s="146"/>
-      <c r="AB86" s="141"/>
+      <c r="AA86" s="147"/>
+      <c r="AB86" s="142"/>
       <c r="AC86" s="141"/>
       <c r="AD86" s="141"/>
-      <c r="AE86" s="150"/>
-      <c r="AF86" s="148"/>
+      <c r="AE86" s="151"/>
+      <c r="AF86" s="149"/>
     </row>
     <row r="87" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A87" s="141" t="s">
@@ -7354,19 +7358,19 @@
       </c>
       <c r="D87" s="141"/>
       <c r="E87" s="141"/>
-      <c r="F87" s="141">
+      <c r="F87" s="142">
         <f>E87/2500</f>
         <v>0</v>
       </c>
-      <c r="G87" s="141"/>
-      <c r="H87" s="142" t="s">
+      <c r="G87" s="142"/>
+      <c r="H87" s="143" t="s">
         <v>194</v>
       </c>
-      <c r="I87" s="142" t="s">
+      <c r="I87" s="143" t="s">
         <v>245</v>
       </c>
       <c r="J87" s="141"/>
-      <c r="K87" s="141">
+      <c r="K87" s="142">
         <f>J87/300</f>
         <v>0</v>
       </c>
@@ -7375,16 +7379,16 @@
       </c>
       <c r="M87" s="141"/>
       <c r="N87" s="141"/>
-      <c r="O87" s="152" t="s">
+      <c r="O87" s="153" t="s">
         <v>246</v>
       </c>
       <c r="P87" s="141"/>
       <c r="Q87" s="141"/>
-      <c r="R87" s="144"/>
-      <c r="S87" s="145" t="s">
+      <c r="R87" s="145"/>
+      <c r="S87" s="146" t="s">
         <v>247</v>
       </c>
-      <c r="T87" s="145"/>
+      <c r="T87" s="146"/>
       <c r="U87" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7393,24 +7397,24 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W87" s="142">
+      <c r="W87" s="143">
         <v>302</v>
       </c>
       <c r="X87" s="141">
         <f>SUM(U87:U100)</f>
         <v>0</v>
       </c>
-      <c r="Y87" s="141">
+      <c r="Y87" s="142">
         <f>X87/2150</f>
         <v>0</v>
       </c>
       <c r="Z87" s="141">
         <v>154</v>
       </c>
-      <c r="AA87" s="146">
+      <c r="AA87" s="147">
         <v>140</v>
       </c>
-      <c r="AB87" s="141">
+      <c r="AB87" s="142">
         <f>87/Z87</f>
         <v>0.564935064935065</v>
       </c>
@@ -7420,10 +7424,10 @@
       <c r="AD87" s="141">
         <v>8</v>
       </c>
-      <c r="AE87" s="147" t="s">
+      <c r="AE87" s="148" t="s">
         <v>198</v>
       </c>
-      <c r="AF87" s="148"/>
+      <c r="AF87" s="149"/>
     </row>
     <row r="88" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A88" s="141"/>
@@ -7431,25 +7435,25 @@
       <c r="C88" s="141"/>
       <c r="D88" s="141"/>
       <c r="E88" s="141"/>
-      <c r="F88" s="141"/>
-      <c r="G88" s="141"/>
-      <c r="H88" s="142"/>
-      <c r="I88" s="142"/>
+      <c r="F88" s="142"/>
+      <c r="G88" s="142"/>
+      <c r="H88" s="143"/>
+      <c r="I88" s="143"/>
       <c r="J88" s="141"/>
-      <c r="K88" s="141"/>
+      <c r="K88" s="142"/>
       <c r="L88" s="141"/>
       <c r="M88" s="141"/>
       <c r="N88" s="141"/>
-      <c r="O88" s="152" t="s">
+      <c r="O88" s="153" t="s">
         <v>248</v>
       </c>
       <c r="P88" s="141"/>
       <c r="Q88" s="141"/>
-      <c r="R88" s="144"/>
-      <c r="S88" s="145" t="s">
+      <c r="R88" s="145"/>
+      <c r="S88" s="146" t="s">
         <v>249</v>
       </c>
-      <c r="T88" s="145"/>
+      <c r="T88" s="146"/>
       <c r="U88" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7458,16 +7462,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W88" s="142"/>
+      <c r="W88" s="143"/>
       <c r="X88" s="141"/>
-      <c r="Y88" s="141"/>
+      <c r="Y88" s="142"/>
       <c r="Z88" s="141"/>
-      <c r="AA88" s="146"/>
-      <c r="AB88" s="141"/>
+      <c r="AA88" s="147"/>
+      <c r="AB88" s="142"/>
       <c r="AC88" s="141"/>
       <c r="AD88" s="141"/>
-      <c r="AE88" s="149"/>
-      <c r="AF88" s="148"/>
+      <c r="AE88" s="150"/>
+      <c r="AF88" s="149"/>
     </row>
     <row r="89" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A89" s="141"/>
@@ -7475,25 +7479,25 @@
       <c r="C89" s="141"/>
       <c r="D89" s="141"/>
       <c r="E89" s="141"/>
-      <c r="F89" s="141"/>
-      <c r="G89" s="141"/>
-      <c r="H89" s="142"/>
-      <c r="I89" s="142"/>
+      <c r="F89" s="142"/>
+      <c r="G89" s="142"/>
+      <c r="H89" s="143"/>
+      <c r="I89" s="143"/>
       <c r="J89" s="141"/>
-      <c r="K89" s="141"/>
+      <c r="K89" s="142"/>
       <c r="L89" s="141"/>
       <c r="M89" s="141"/>
       <c r="N89" s="141"/>
-      <c r="O89" s="152" t="s">
+      <c r="O89" s="153" t="s">
         <v>250</v>
       </c>
       <c r="P89" s="141"/>
       <c r="Q89" s="141"/>
-      <c r="R89" s="144"/>
-      <c r="S89" s="145" t="s">
+      <c r="R89" s="145"/>
+      <c r="S89" s="146" t="s">
         <v>251</v>
       </c>
-      <c r="T89" s="145"/>
+      <c r="T89" s="146"/>
       <c r="U89" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7502,16 +7506,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W89" s="142"/>
+      <c r="W89" s="143"/>
       <c r="X89" s="141"/>
-      <c r="Y89" s="141"/>
+      <c r="Y89" s="142"/>
       <c r="Z89" s="141"/>
-      <c r="AA89" s="146"/>
-      <c r="AB89" s="141"/>
+      <c r="AA89" s="147"/>
+      <c r="AB89" s="142"/>
       <c r="AC89" s="141"/>
       <c r="AD89" s="141"/>
-      <c r="AE89" s="149"/>
-      <c r="AF89" s="148"/>
+      <c r="AE89" s="150"/>
+      <c r="AF89" s="149"/>
     </row>
     <row r="90" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A90" s="141"/>
@@ -7519,25 +7523,25 @@
       <c r="C90" s="141"/>
       <c r="D90" s="141"/>
       <c r="E90" s="141"/>
-      <c r="F90" s="141"/>
-      <c r="G90" s="141"/>
-      <c r="H90" s="142"/>
-      <c r="I90" s="142"/>
+      <c r="F90" s="142"/>
+      <c r="G90" s="142"/>
+      <c r="H90" s="143"/>
+      <c r="I90" s="143"/>
       <c r="J90" s="141"/>
-      <c r="K90" s="141"/>
+      <c r="K90" s="142"/>
       <c r="L90" s="141"/>
       <c r="M90" s="141"/>
       <c r="N90" s="141"/>
-      <c r="O90" s="152" t="s">
+      <c r="O90" s="153" t="s">
         <v>252</v>
       </c>
       <c r="P90" s="141"/>
       <c r="Q90" s="141"/>
-      <c r="R90" s="144"/>
-      <c r="S90" s="145" t="s">
+      <c r="R90" s="145"/>
+      <c r="S90" s="146" t="s">
         <v>253</v>
       </c>
-      <c r="T90" s="145"/>
+      <c r="T90" s="146"/>
       <c r="U90" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7546,16 +7550,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W90" s="142"/>
+      <c r="W90" s="143"/>
       <c r="X90" s="141"/>
-      <c r="Y90" s="141"/>
+      <c r="Y90" s="142"/>
       <c r="Z90" s="141"/>
-      <c r="AA90" s="146"/>
-      <c r="AB90" s="141"/>
+      <c r="AA90" s="147"/>
+      <c r="AB90" s="142"/>
       <c r="AC90" s="141"/>
       <c r="AD90" s="141"/>
-      <c r="AE90" s="150"/>
-      <c r="AF90" s="148"/>
+      <c r="AE90" s="151"/>
+      <c r="AF90" s="149"/>
     </row>
     <row r="91" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A91" s="141"/>
@@ -7563,25 +7567,25 @@
       <c r="C91" s="141"/>
       <c r="D91" s="141"/>
       <c r="E91" s="141"/>
-      <c r="F91" s="141"/>
-      <c r="G91" s="141"/>
-      <c r="H91" s="142"/>
-      <c r="I91" s="142"/>
+      <c r="F91" s="142"/>
+      <c r="G91" s="142"/>
+      <c r="H91" s="143"/>
+      <c r="I91" s="143"/>
       <c r="J91" s="141"/>
-      <c r="K91" s="141"/>
+      <c r="K91" s="142"/>
       <c r="L91" s="141"/>
       <c r="M91" s="141"/>
       <c r="N91" s="141"/>
-      <c r="O91" s="152" t="s">
+      <c r="O91" s="153" t="s">
         <v>254</v>
       </c>
       <c r="P91" s="141"/>
       <c r="Q91" s="141"/>
-      <c r="R91" s="144"/>
-      <c r="S91" s="145" t="s">
+      <c r="R91" s="145"/>
+      <c r="S91" s="146" t="s">
         <v>255</v>
       </c>
-      <c r="T91" s="145"/>
+      <c r="T91" s="146"/>
       <c r="U91" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7590,16 +7594,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W91" s="142"/>
+      <c r="W91" s="143"/>
       <c r="X91" s="141"/>
-      <c r="Y91" s="141"/>
+      <c r="Y91" s="142"/>
       <c r="Z91" s="141"/>
-      <c r="AA91" s="146"/>
-      <c r="AB91" s="141"/>
+      <c r="AA91" s="147"/>
+      <c r="AB91" s="142"/>
       <c r="AC91" s="141"/>
       <c r="AD91" s="141"/>
-      <c r="AE91" s="147"/>
-      <c r="AF91" s="148"/>
+      <c r="AE91" s="148"/>
+      <c r="AF91" s="149"/>
     </row>
     <row r="92" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A92" s="141"/>
@@ -7607,25 +7611,25 @@
       <c r="C92" s="141"/>
       <c r="D92" s="141"/>
       <c r="E92" s="141"/>
-      <c r="F92" s="141"/>
-      <c r="G92" s="141"/>
-      <c r="H92" s="142"/>
-      <c r="I92" s="142"/>
+      <c r="F92" s="142"/>
+      <c r="G92" s="142"/>
+      <c r="H92" s="143"/>
+      <c r="I92" s="143"/>
       <c r="J92" s="141"/>
-      <c r="K92" s="141"/>
+      <c r="K92" s="142"/>
       <c r="L92" s="141"/>
       <c r="M92" s="141"/>
       <c r="N92" s="141"/>
-      <c r="O92" s="152" t="s">
+      <c r="O92" s="153" t="s">
         <v>256</v>
       </c>
       <c r="P92" s="141"/>
       <c r="Q92" s="141"/>
-      <c r="R92" s="144"/>
-      <c r="S92" s="145" t="s">
+      <c r="R92" s="145"/>
+      <c r="S92" s="146" t="s">
         <v>257</v>
       </c>
-      <c r="T92" s="145"/>
+      <c r="T92" s="146"/>
       <c r="U92" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7634,16 +7638,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W92" s="142"/>
+      <c r="W92" s="143"/>
       <c r="X92" s="141"/>
-      <c r="Y92" s="141"/>
+      <c r="Y92" s="142"/>
       <c r="Z92" s="141"/>
-      <c r="AA92" s="146"/>
-      <c r="AB92" s="141"/>
+      <c r="AA92" s="147"/>
+      <c r="AB92" s="142"/>
       <c r="AC92" s="141"/>
       <c r="AD92" s="141"/>
-      <c r="AE92" s="149"/>
-      <c r="AF92" s="148"/>
+      <c r="AE92" s="150"/>
+      <c r="AF92" s="149"/>
     </row>
     <row r="93" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A93" s="141"/>
@@ -7651,25 +7655,25 @@
       <c r="C93" s="141"/>
       <c r="D93" s="141"/>
       <c r="E93" s="141"/>
-      <c r="F93" s="141"/>
-      <c r="G93" s="141"/>
-      <c r="H93" s="142"/>
-      <c r="I93" s="142"/>
+      <c r="F93" s="142"/>
+      <c r="G93" s="142"/>
+      <c r="H93" s="143"/>
+      <c r="I93" s="143"/>
       <c r="J93" s="141"/>
-      <c r="K93" s="141"/>
+      <c r="K93" s="142"/>
       <c r="L93" s="141"/>
       <c r="M93" s="141"/>
       <c r="N93" s="141"/>
-      <c r="O93" s="152" t="s">
+      <c r="O93" s="153" t="s">
         <v>258</v>
       </c>
       <c r="P93" s="141"/>
       <c r="Q93" s="141"/>
-      <c r="R93" s="144"/>
-      <c r="S93" s="145" t="s">
+      <c r="R93" s="145"/>
+      <c r="S93" s="146" t="s">
         <v>259</v>
       </c>
-      <c r="T93" s="145"/>
+      <c r="T93" s="146"/>
       <c r="U93" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7678,16 +7682,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W93" s="142"/>
+      <c r="W93" s="143"/>
       <c r="X93" s="141"/>
-      <c r="Y93" s="141"/>
+      <c r="Y93" s="142"/>
       <c r="Z93" s="141"/>
-      <c r="AA93" s="146"/>
-      <c r="AB93" s="141"/>
+      <c r="AA93" s="147"/>
+      <c r="AB93" s="142"/>
       <c r="AC93" s="141"/>
       <c r="AD93" s="141"/>
-      <c r="AE93" s="150"/>
-      <c r="AF93" s="148"/>
+      <c r="AE93" s="151"/>
+      <c r="AF93" s="149"/>
     </row>
     <row r="94" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A94" s="141"/>
@@ -7699,30 +7703,30 @@
       </c>
       <c r="D94" s="141"/>
       <c r="E94" s="141"/>
-      <c r="F94" s="141">
+      <c r="F94" s="142">
         <f>E94/2500</f>
         <v>0</v>
       </c>
-      <c r="G94" s="141"/>
-      <c r="H94" s="142" t="s">
+      <c r="G94" s="142"/>
+      <c r="H94" s="143" t="s">
         <v>194</v>
       </c>
-      <c r="I94" s="142"/>
+      <c r="I94" s="143"/>
       <c r="J94" s="141"/>
-      <c r="K94" s="141"/>
+      <c r="K94" s="142"/>
       <c r="L94" s="141"/>
       <c r="M94" s="141"/>
       <c r="N94" s="141"/>
-      <c r="O94" s="152" t="s">
+      <c r="O94" s="153" t="s">
         <v>261</v>
       </c>
       <c r="P94" s="141"/>
       <c r="Q94" s="141"/>
-      <c r="R94" s="144"/>
-      <c r="S94" s="145" t="s">
+      <c r="R94" s="145"/>
+      <c r="S94" s="146" t="s">
         <v>262</v>
       </c>
-      <c r="T94" s="145"/>
+      <c r="T94" s="146"/>
       <c r="U94" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7731,18 +7735,18 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W94" s="142"/>
+      <c r="W94" s="143"/>
       <c r="X94" s="141"/>
-      <c r="Y94" s="141"/>
+      <c r="Y94" s="142"/>
       <c r="Z94" s="141"/>
-      <c r="AA94" s="146"/>
-      <c r="AB94" s="141"/>
+      <c r="AA94" s="147"/>
+      <c r="AB94" s="142"/>
       <c r="AC94" s="141"/>
       <c r="AD94" s="141"/>
-      <c r="AE94" s="147" t="s">
+      <c r="AE94" s="148" t="s">
         <v>210</v>
       </c>
-      <c r="AF94" s="148"/>
+      <c r="AF94" s="149"/>
     </row>
     <row r="95" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A95" s="141"/>
@@ -7750,25 +7754,25 @@
       <c r="C95" s="141"/>
       <c r="D95" s="141"/>
       <c r="E95" s="141"/>
-      <c r="F95" s="141"/>
-      <c r="G95" s="141"/>
-      <c r="H95" s="142"/>
-      <c r="I95" s="142"/>
+      <c r="F95" s="142"/>
+      <c r="G95" s="142"/>
+      <c r="H95" s="143"/>
+      <c r="I95" s="143"/>
       <c r="J95" s="141"/>
-      <c r="K95" s="141"/>
+      <c r="K95" s="142"/>
       <c r="L95" s="141"/>
       <c r="M95" s="141"/>
       <c r="N95" s="141"/>
-      <c r="O95" s="152" t="s">
+      <c r="O95" s="153" t="s">
         <v>263</v>
       </c>
       <c r="P95" s="141"/>
       <c r="Q95" s="141"/>
-      <c r="R95" s="144"/>
-      <c r="S95" s="145" t="s">
+      <c r="R95" s="145"/>
+      <c r="S95" s="146" t="s">
         <v>264</v>
       </c>
-      <c r="T95" s="145"/>
+      <c r="T95" s="146"/>
       <c r="U95" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7777,16 +7781,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W95" s="142"/>
+      <c r="W95" s="143"/>
       <c r="X95" s="141"/>
-      <c r="Y95" s="141"/>
+      <c r="Y95" s="142"/>
       <c r="Z95" s="141"/>
-      <c r="AA95" s="146"/>
-      <c r="AB95" s="141"/>
+      <c r="AA95" s="147"/>
+      <c r="AB95" s="142"/>
       <c r="AC95" s="141"/>
       <c r="AD95" s="141"/>
-      <c r="AE95" s="149"/>
-      <c r="AF95" s="148"/>
+      <c r="AE95" s="150"/>
+      <c r="AF95" s="149"/>
     </row>
     <row r="96" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A96" s="141"/>
@@ -7794,25 +7798,25 @@
       <c r="C96" s="141"/>
       <c r="D96" s="141"/>
       <c r="E96" s="141"/>
-      <c r="F96" s="141"/>
-      <c r="G96" s="141"/>
-      <c r="H96" s="142"/>
-      <c r="I96" s="142"/>
+      <c r="F96" s="142"/>
+      <c r="G96" s="142"/>
+      <c r="H96" s="143"/>
+      <c r="I96" s="143"/>
       <c r="J96" s="141"/>
-      <c r="K96" s="141"/>
+      <c r="K96" s="142"/>
       <c r="L96" s="141"/>
       <c r="M96" s="141"/>
       <c r="N96" s="141"/>
-      <c r="O96" s="152" t="s">
+      <c r="O96" s="153" t="s">
         <v>265</v>
       </c>
       <c r="P96" s="141"/>
       <c r="Q96" s="141"/>
-      <c r="R96" s="144"/>
-      <c r="S96" s="145" t="s">
+      <c r="R96" s="145"/>
+      <c r="S96" s="146" t="s">
         <v>266</v>
       </c>
-      <c r="T96" s="145"/>
+      <c r="T96" s="146"/>
       <c r="U96" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7821,16 +7825,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W96" s="142"/>
+      <c r="W96" s="143"/>
       <c r="X96" s="141"/>
-      <c r="Y96" s="141"/>
+      <c r="Y96" s="142"/>
       <c r="Z96" s="141"/>
-      <c r="AA96" s="146"/>
-      <c r="AB96" s="141"/>
+      <c r="AA96" s="147"/>
+      <c r="AB96" s="142"/>
       <c r="AC96" s="141"/>
       <c r="AD96" s="141"/>
-      <c r="AE96" s="149"/>
-      <c r="AF96" s="148"/>
+      <c r="AE96" s="150"/>
+      <c r="AF96" s="149"/>
     </row>
     <row r="97" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A97" s="141"/>
@@ -7838,25 +7842,25 @@
       <c r="C97" s="141"/>
       <c r="D97" s="141"/>
       <c r="E97" s="141"/>
-      <c r="F97" s="141"/>
-      <c r="G97" s="141"/>
-      <c r="H97" s="142"/>
-      <c r="I97" s="142"/>
+      <c r="F97" s="142"/>
+      <c r="G97" s="142"/>
+      <c r="H97" s="143"/>
+      <c r="I97" s="143"/>
       <c r="J97" s="141"/>
-      <c r="K97" s="141"/>
+      <c r="K97" s="142"/>
       <c r="L97" s="141"/>
       <c r="M97" s="141"/>
       <c r="N97" s="141"/>
-      <c r="O97" s="152" t="s">
+      <c r="O97" s="153" t="s">
         <v>267</v>
       </c>
       <c r="P97" s="141"/>
       <c r="Q97" s="141"/>
-      <c r="R97" s="144"/>
-      <c r="S97" s="145" t="s">
+      <c r="R97" s="145"/>
+      <c r="S97" s="146" t="s">
         <v>268</v>
       </c>
-      <c r="T97" s="145"/>
+      <c r="T97" s="146"/>
       <c r="U97" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7865,16 +7869,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W97" s="142"/>
+      <c r="W97" s="143"/>
       <c r="X97" s="141"/>
-      <c r="Y97" s="141"/>
+      <c r="Y97" s="142"/>
       <c r="Z97" s="141"/>
-      <c r="AA97" s="146"/>
-      <c r="AB97" s="141"/>
+      <c r="AA97" s="147"/>
+      <c r="AB97" s="142"/>
       <c r="AC97" s="141"/>
       <c r="AD97" s="141"/>
-      <c r="AE97" s="150"/>
-      <c r="AF97" s="148"/>
+      <c r="AE97" s="151"/>
+      <c r="AF97" s="149"/>
     </row>
     <row r="98" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A98" s="141"/>
@@ -7882,25 +7886,25 @@
       <c r="C98" s="141"/>
       <c r="D98" s="141"/>
       <c r="E98" s="141"/>
-      <c r="F98" s="141"/>
-      <c r="G98" s="141"/>
-      <c r="H98" s="142"/>
-      <c r="I98" s="142"/>
+      <c r="F98" s="142"/>
+      <c r="G98" s="142"/>
+      <c r="H98" s="143"/>
+      <c r="I98" s="143"/>
       <c r="J98" s="141"/>
-      <c r="K98" s="141"/>
+      <c r="K98" s="142"/>
       <c r="L98" s="141"/>
       <c r="M98" s="141"/>
       <c r="N98" s="141"/>
-      <c r="O98" s="152" t="s">
+      <c r="O98" s="153" t="s">
         <v>269</v>
       </c>
       <c r="P98" s="141"/>
       <c r="Q98" s="141"/>
-      <c r="R98" s="144"/>
-      <c r="S98" s="145" t="s">
+      <c r="R98" s="145"/>
+      <c r="S98" s="146" t="s">
         <v>270</v>
       </c>
-      <c r="T98" s="145"/>
+      <c r="T98" s="146"/>
       <c r="U98" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7909,16 +7913,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W98" s="142"/>
+      <c r="W98" s="143"/>
       <c r="X98" s="141"/>
-      <c r="Y98" s="141"/>
+      <c r="Y98" s="142"/>
       <c r="Z98" s="141"/>
-      <c r="AA98" s="146"/>
-      <c r="AB98" s="141"/>
+      <c r="AA98" s="147"/>
+      <c r="AB98" s="142"/>
       <c r="AC98" s="141"/>
       <c r="AD98" s="141"/>
-      <c r="AE98" s="147"/>
-      <c r="AF98" s="148"/>
+      <c r="AE98" s="148"/>
+      <c r="AF98" s="149"/>
     </row>
     <row r="99" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A99" s="141"/>
@@ -7926,25 +7930,25 @@
       <c r="C99" s="141"/>
       <c r="D99" s="141"/>
       <c r="E99" s="141"/>
-      <c r="F99" s="141"/>
-      <c r="G99" s="141"/>
-      <c r="H99" s="142"/>
-      <c r="I99" s="142"/>
+      <c r="F99" s="142"/>
+      <c r="G99" s="142"/>
+      <c r="H99" s="143"/>
+      <c r="I99" s="143"/>
       <c r="J99" s="141"/>
-      <c r="K99" s="141"/>
+      <c r="K99" s="142"/>
       <c r="L99" s="141"/>
       <c r="M99" s="141"/>
       <c r="N99" s="141"/>
-      <c r="O99" s="152" t="s">
+      <c r="O99" s="153" t="s">
         <v>271</v>
       </c>
       <c r="P99" s="141"/>
       <c r="Q99" s="141"/>
-      <c r="R99" s="144"/>
-      <c r="S99" s="145" t="s">
+      <c r="R99" s="145"/>
+      <c r="S99" s="146" t="s">
         <v>272</v>
       </c>
-      <c r="T99" s="145"/>
+      <c r="T99" s="146"/>
       <c r="U99" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7953,16 +7957,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W99" s="142"/>
+      <c r="W99" s="143"/>
       <c r="X99" s="141"/>
-      <c r="Y99" s="141"/>
+      <c r="Y99" s="142"/>
       <c r="Z99" s="141"/>
-      <c r="AA99" s="146"/>
-      <c r="AB99" s="141"/>
+      <c r="AA99" s="147"/>
+      <c r="AB99" s="142"/>
       <c r="AC99" s="141"/>
       <c r="AD99" s="141"/>
-      <c r="AE99" s="149"/>
-      <c r="AF99" s="148"/>
+      <c r="AE99" s="150"/>
+      <c r="AF99" s="149"/>
     </row>
     <row r="100" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A100" s="141"/>
@@ -7970,25 +7974,25 @@
       <c r="C100" s="141"/>
       <c r="D100" s="141"/>
       <c r="E100" s="141"/>
-      <c r="F100" s="141"/>
-      <c r="G100" s="141"/>
-      <c r="H100" s="142"/>
-      <c r="I100" s="142"/>
+      <c r="F100" s="142"/>
+      <c r="G100" s="142"/>
+      <c r="H100" s="143"/>
+      <c r="I100" s="143"/>
       <c r="J100" s="141"/>
-      <c r="K100" s="141"/>
+      <c r="K100" s="142"/>
       <c r="L100" s="141"/>
       <c r="M100" s="141"/>
       <c r="N100" s="141"/>
-      <c r="O100" s="152" t="s">
+      <c r="O100" s="153" t="s">
         <v>273</v>
       </c>
       <c r="P100" s="141"/>
       <c r="Q100" s="141"/>
-      <c r="R100" s="144"/>
-      <c r="S100" s="145" t="s">
+      <c r="R100" s="145"/>
+      <c r="S100" s="146" t="s">
         <v>274</v>
       </c>
-      <c r="T100" s="145"/>
+      <c r="T100" s="146"/>
       <c r="U100" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7997,16 +8001,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W100" s="142"/>
+      <c r="W100" s="143"/>
       <c r="X100" s="141"/>
-      <c r="Y100" s="141"/>
+      <c r="Y100" s="142"/>
       <c r="Z100" s="141"/>
-      <c r="AA100" s="146"/>
-      <c r="AB100" s="141"/>
+      <c r="AA100" s="147"/>
+      <c r="AB100" s="142"/>
       <c r="AC100" s="141"/>
       <c r="AD100" s="141"/>
-      <c r="AE100" s="150"/>
-      <c r="AF100" s="148"/>
+      <c r="AE100" s="151"/>
+      <c r="AF100" s="149"/>
     </row>
     <row r="101" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A101" s="141" t="s">
@@ -8020,19 +8024,19 @@
       </c>
       <c r="D101" s="141"/>
       <c r="E101" s="141"/>
-      <c r="F101" s="141">
+      <c r="F101" s="142">
         <f>E101/2500</f>
         <v>0</v>
       </c>
-      <c r="G101" s="141"/>
-      <c r="H101" s="142" t="s">
+      <c r="G101" s="142"/>
+      <c r="H101" s="143" t="s">
         <v>194</v>
       </c>
-      <c r="I101" s="142" t="s">
+      <c r="I101" s="143" t="s">
         <v>277</v>
       </c>
       <c r="J101" s="141"/>
-      <c r="K101" s="141">
+      <c r="K101" s="142">
         <f>J101/300</f>
         <v>0</v>
       </c>
@@ -8041,16 +8045,16 @@
       </c>
       <c r="M101" s="141"/>
       <c r="N101" s="141"/>
-      <c r="O101" s="152" t="s">
+      <c r="O101" s="153" t="s">
         <v>278</v>
       </c>
       <c r="P101" s="141"/>
       <c r="Q101" s="141"/>
-      <c r="R101" s="144"/>
-      <c r="S101" s="145" t="s">
+      <c r="R101" s="145"/>
+      <c r="S101" s="146" t="s">
         <v>279</v>
       </c>
-      <c r="T101" s="145"/>
+      <c r="T101" s="146"/>
       <c r="U101" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8059,24 +8063,24 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W101" s="142">
+      <c r="W101" s="143">
         <v>301</v>
       </c>
       <c r="X101" s="141">
         <f>SUM(U101:U114)</f>
         <v>0</v>
       </c>
-      <c r="Y101" s="141">
+      <c r="Y101" s="142">
         <f>X101/2150</f>
         <v>0</v>
       </c>
       <c r="Z101" s="141">
         <v>154</v>
       </c>
-      <c r="AA101" s="146">
+      <c r="AA101" s="147">
         <v>152</v>
       </c>
-      <c r="AB101" s="141">
+      <c r="AB101" s="142">
         <f>101/Z101</f>
         <v>0.655844155844156</v>
       </c>
@@ -8086,10 +8090,10 @@
       <c r="AD101" s="141">
         <v>8</v>
       </c>
-      <c r="AE101" s="147" t="s">
+      <c r="AE101" s="148" t="s">
         <v>198</v>
       </c>
-      <c r="AF101" s="148"/>
+      <c r="AF101" s="149"/>
     </row>
     <row r="102" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A102" s="141"/>
@@ -8097,25 +8101,25 @@
       <c r="C102" s="141"/>
       <c r="D102" s="141"/>
       <c r="E102" s="141"/>
-      <c r="F102" s="141"/>
-      <c r="G102" s="141"/>
-      <c r="H102" s="142"/>
-      <c r="I102" s="142"/>
+      <c r="F102" s="142"/>
+      <c r="G102" s="142"/>
+      <c r="H102" s="143"/>
+      <c r="I102" s="143"/>
       <c r="J102" s="141"/>
-      <c r="K102" s="141"/>
+      <c r="K102" s="142"/>
       <c r="L102" s="141"/>
       <c r="M102" s="141"/>
       <c r="N102" s="141"/>
-      <c r="O102" s="143" t="s">
+      <c r="O102" s="144" t="s">
         <v>280</v>
       </c>
       <c r="P102" s="141"/>
       <c r="Q102" s="141"/>
-      <c r="R102" s="144"/>
-      <c r="S102" s="145" t="s">
+      <c r="R102" s="145"/>
+      <c r="S102" s="146" t="s">
         <v>281</v>
       </c>
-      <c r="T102" s="145"/>
+      <c r="T102" s="146"/>
       <c r="U102" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8124,16 +8128,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W102" s="142"/>
+      <c r="W102" s="143"/>
       <c r="X102" s="141"/>
-      <c r="Y102" s="141"/>
+      <c r="Y102" s="142"/>
       <c r="Z102" s="141"/>
-      <c r="AA102" s="146"/>
-      <c r="AB102" s="141"/>
+      <c r="AA102" s="147"/>
+      <c r="AB102" s="142"/>
       <c r="AC102" s="141"/>
       <c r="AD102" s="141"/>
-      <c r="AE102" s="149"/>
-      <c r="AF102" s="148"/>
+      <c r="AE102" s="150"/>
+      <c r="AF102" s="149"/>
     </row>
     <row r="103" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A103" s="141"/>
@@ -8141,25 +8145,25 @@
       <c r="C103" s="141"/>
       <c r="D103" s="141"/>
       <c r="E103" s="141"/>
-      <c r="F103" s="141"/>
-      <c r="G103" s="141"/>
-      <c r="H103" s="142"/>
-      <c r="I103" s="142"/>
+      <c r="F103" s="142"/>
+      <c r="G103" s="142"/>
+      <c r="H103" s="143"/>
+      <c r="I103" s="143"/>
       <c r="J103" s="141"/>
-      <c r="K103" s="141"/>
+      <c r="K103" s="142"/>
       <c r="L103" s="141"/>
       <c r="M103" s="141"/>
       <c r="N103" s="141"/>
-      <c r="O103" s="152" t="s">
+      <c r="O103" s="153" t="s">
         <v>282</v>
       </c>
       <c r="P103" s="141"/>
       <c r="Q103" s="141"/>
-      <c r="R103" s="144"/>
-      <c r="S103" s="145" t="s">
+      <c r="R103" s="145"/>
+      <c r="S103" s="146" t="s">
         <v>283</v>
       </c>
-      <c r="T103" s="145"/>
+      <c r="T103" s="146"/>
       <c r="U103" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8168,16 +8172,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W103" s="142"/>
+      <c r="W103" s="143"/>
       <c r="X103" s="141"/>
-      <c r="Y103" s="141"/>
+      <c r="Y103" s="142"/>
       <c r="Z103" s="141"/>
-      <c r="AA103" s="146"/>
-      <c r="AB103" s="141"/>
+      <c r="AA103" s="147"/>
+      <c r="AB103" s="142"/>
       <c r="AC103" s="141"/>
       <c r="AD103" s="141"/>
-      <c r="AE103" s="149"/>
-      <c r="AF103" s="148"/>
+      <c r="AE103" s="150"/>
+      <c r="AF103" s="149"/>
     </row>
     <row r="104" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A104" s="141"/>
@@ -8185,25 +8189,25 @@
       <c r="C104" s="141"/>
       <c r="D104" s="141"/>
       <c r="E104" s="141"/>
-      <c r="F104" s="141"/>
-      <c r="G104" s="141"/>
-      <c r="H104" s="142"/>
-      <c r="I104" s="142"/>
+      <c r="F104" s="142"/>
+      <c r="G104" s="142"/>
+      <c r="H104" s="143"/>
+      <c r="I104" s="143"/>
       <c r="J104" s="141"/>
-      <c r="K104" s="141"/>
+      <c r="K104" s="142"/>
       <c r="L104" s="141"/>
       <c r="M104" s="141"/>
       <c r="N104" s="141"/>
-      <c r="O104" s="143" t="s">
+      <c r="O104" s="144" t="s">
         <v>284</v>
       </c>
       <c r="P104" s="141"/>
       <c r="Q104" s="141"/>
-      <c r="R104" s="144"/>
-      <c r="S104" s="145" t="s">
+      <c r="R104" s="145"/>
+      <c r="S104" s="146" t="s">
         <v>285</v>
       </c>
-      <c r="T104" s="145"/>
+      <c r="T104" s="146"/>
       <c r="U104" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8212,16 +8216,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W104" s="142"/>
+      <c r="W104" s="143"/>
       <c r="X104" s="141"/>
-      <c r="Y104" s="141"/>
+      <c r="Y104" s="142"/>
       <c r="Z104" s="141"/>
-      <c r="AA104" s="146"/>
-      <c r="AB104" s="141"/>
+      <c r="AA104" s="147"/>
+      <c r="AB104" s="142"/>
       <c r="AC104" s="141"/>
       <c r="AD104" s="141"/>
-      <c r="AE104" s="150"/>
-      <c r="AF104" s="148"/>
+      <c r="AE104" s="151"/>
+      <c r="AF104" s="149"/>
     </row>
     <row r="105" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A105" s="141"/>
@@ -8229,25 +8233,25 @@
       <c r="C105" s="141"/>
       <c r="D105" s="141"/>
       <c r="E105" s="141"/>
-      <c r="F105" s="141"/>
-      <c r="G105" s="141"/>
-      <c r="H105" s="142"/>
-      <c r="I105" s="142"/>
+      <c r="F105" s="142"/>
+      <c r="G105" s="142"/>
+      <c r="H105" s="143"/>
+      <c r="I105" s="143"/>
       <c r="J105" s="141"/>
-      <c r="K105" s="141"/>
+      <c r="K105" s="142"/>
       <c r="L105" s="141"/>
       <c r="M105" s="141"/>
       <c r="N105" s="141"/>
-      <c r="O105" s="152" t="s">
+      <c r="O105" s="153" t="s">
         <v>286</v>
       </c>
       <c r="P105" s="141"/>
       <c r="Q105" s="141"/>
-      <c r="R105" s="144"/>
-      <c r="S105" s="145" t="s">
+      <c r="R105" s="145"/>
+      <c r="S105" s="146" t="s">
         <v>287</v>
       </c>
-      <c r="T105" s="145"/>
+      <c r="T105" s="146"/>
       <c r="U105" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8256,16 +8260,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W105" s="142"/>
+      <c r="W105" s="143"/>
       <c r="X105" s="141"/>
-      <c r="Y105" s="141"/>
+      <c r="Y105" s="142"/>
       <c r="Z105" s="141"/>
-      <c r="AA105" s="146"/>
-      <c r="AB105" s="141"/>
+      <c r="AA105" s="147"/>
+      <c r="AB105" s="142"/>
       <c r="AC105" s="141"/>
       <c r="AD105" s="141"/>
-      <c r="AE105" s="147"/>
-      <c r="AF105" s="148"/>
+      <c r="AE105" s="148"/>
+      <c r="AF105" s="149"/>
     </row>
     <row r="106" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A106" s="141"/>
@@ -8273,25 +8277,25 @@
       <c r="C106" s="141"/>
       <c r="D106" s="141"/>
       <c r="E106" s="141"/>
-      <c r="F106" s="141"/>
-      <c r="G106" s="141"/>
-      <c r="H106" s="142"/>
-      <c r="I106" s="142"/>
+      <c r="F106" s="142"/>
+      <c r="G106" s="142"/>
+      <c r="H106" s="143"/>
+      <c r="I106" s="143"/>
       <c r="J106" s="141"/>
-      <c r="K106" s="141"/>
+      <c r="K106" s="142"/>
       <c r="L106" s="141"/>
       <c r="M106" s="141"/>
       <c r="N106" s="141"/>
-      <c r="O106" s="143" t="s">
+      <c r="O106" s="144" t="s">
         <v>288</v>
       </c>
       <c r="P106" s="141"/>
       <c r="Q106" s="141"/>
-      <c r="R106" s="144"/>
-      <c r="S106" s="145" t="s">
+      <c r="R106" s="145"/>
+      <c r="S106" s="146" t="s">
         <v>289</v>
       </c>
-      <c r="T106" s="145"/>
+      <c r="T106" s="146"/>
       <c r="U106" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8300,16 +8304,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W106" s="142"/>
+      <c r="W106" s="143"/>
       <c r="X106" s="141"/>
-      <c r="Y106" s="141"/>
+      <c r="Y106" s="142"/>
       <c r="Z106" s="141"/>
-      <c r="AA106" s="146"/>
-      <c r="AB106" s="141"/>
+      <c r="AA106" s="147"/>
+      <c r="AB106" s="142"/>
       <c r="AC106" s="141"/>
       <c r="AD106" s="141"/>
-      <c r="AE106" s="149"/>
-      <c r="AF106" s="148"/>
+      <c r="AE106" s="150"/>
+      <c r="AF106" s="149"/>
     </row>
     <row r="107" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A107" s="141"/>
@@ -8317,25 +8321,25 @@
       <c r="C107" s="141"/>
       <c r="D107" s="141"/>
       <c r="E107" s="141"/>
-      <c r="F107" s="141"/>
-      <c r="G107" s="141"/>
-      <c r="H107" s="142"/>
-      <c r="I107" s="142"/>
+      <c r="F107" s="142"/>
+      <c r="G107" s="142"/>
+      <c r="H107" s="143"/>
+      <c r="I107" s="143"/>
       <c r="J107" s="141"/>
-      <c r="K107" s="141"/>
+      <c r="K107" s="142"/>
       <c r="L107" s="141"/>
       <c r="M107" s="141"/>
       <c r="N107" s="141"/>
-      <c r="O107" s="152" t="s">
+      <c r="O107" s="153" t="s">
         <v>290</v>
       </c>
       <c r="P107" s="141"/>
       <c r="Q107" s="141"/>
-      <c r="R107" s="144"/>
-      <c r="S107" s="145" t="s">
+      <c r="R107" s="145"/>
+      <c r="S107" s="146" t="s">
         <v>291</v>
       </c>
-      <c r="T107" s="145"/>
+      <c r="T107" s="146"/>
       <c r="U107" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8344,16 +8348,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W107" s="142"/>
+      <c r="W107" s="143"/>
       <c r="X107" s="141"/>
-      <c r="Y107" s="141"/>
+      <c r="Y107" s="142"/>
       <c r="Z107" s="141"/>
-      <c r="AA107" s="146"/>
-      <c r="AB107" s="141"/>
+      <c r="AA107" s="147"/>
+      <c r="AB107" s="142"/>
       <c r="AC107" s="141"/>
       <c r="AD107" s="141"/>
-      <c r="AE107" s="150"/>
-      <c r="AF107" s="148"/>
+      <c r="AE107" s="151"/>
+      <c r="AF107" s="149"/>
     </row>
     <row r="108" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A108" s="141"/>
@@ -8365,30 +8369,30 @@
       </c>
       <c r="D108" s="141"/>
       <c r="E108" s="141"/>
-      <c r="F108" s="141">
+      <c r="F108" s="142">
         <f>E108/2500</f>
         <v>0</v>
       </c>
-      <c r="G108" s="141"/>
-      <c r="H108" s="142" t="s">
+      <c r="G108" s="142"/>
+      <c r="H108" s="143" t="s">
         <v>194</v>
       </c>
-      <c r="I108" s="142"/>
+      <c r="I108" s="143"/>
       <c r="J108" s="141"/>
-      <c r="K108" s="141"/>
+      <c r="K108" s="142"/>
       <c r="L108" s="141"/>
       <c r="M108" s="141"/>
       <c r="N108" s="141"/>
-      <c r="O108" s="143" t="s">
+      <c r="O108" s="144" t="s">
         <v>293</v>
       </c>
       <c r="P108" s="141"/>
       <c r="Q108" s="141"/>
-      <c r="R108" s="144"/>
-      <c r="S108" s="145" t="s">
+      <c r="R108" s="145"/>
+      <c r="S108" s="146" t="s">
         <v>294</v>
       </c>
-      <c r="T108" s="145"/>
+      <c r="T108" s="146"/>
       <c r="U108" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8397,18 +8401,18 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W108" s="142"/>
+      <c r="W108" s="143"/>
       <c r="X108" s="141"/>
-      <c r="Y108" s="141"/>
+      <c r="Y108" s="142"/>
       <c r="Z108" s="141"/>
-      <c r="AA108" s="146"/>
-      <c r="AB108" s="141"/>
+      <c r="AA108" s="147"/>
+      <c r="AB108" s="142"/>
       <c r="AC108" s="141"/>
       <c r="AD108" s="141"/>
-      <c r="AE108" s="147" t="s">
+      <c r="AE108" s="148" t="s">
         <v>210</v>
       </c>
-      <c r="AF108" s="148"/>
+      <c r="AF108" s="149"/>
     </row>
     <row r="109" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A109" s="141"/>
@@ -8416,25 +8420,25 @@
       <c r="C109" s="141"/>
       <c r="D109" s="141"/>
       <c r="E109" s="141"/>
-      <c r="F109" s="141"/>
-      <c r="G109" s="141"/>
-      <c r="H109" s="142"/>
-      <c r="I109" s="142"/>
+      <c r="F109" s="142"/>
+      <c r="G109" s="142"/>
+      <c r="H109" s="143"/>
+      <c r="I109" s="143"/>
       <c r="J109" s="141"/>
-      <c r="K109" s="141"/>
+      <c r="K109" s="142"/>
       <c r="L109" s="141"/>
       <c r="M109" s="141"/>
       <c r="N109" s="141"/>
-      <c r="O109" s="143" t="s">
+      <c r="O109" s="144" t="s">
         <v>295</v>
       </c>
       <c r="P109" s="141"/>
       <c r="Q109" s="141"/>
-      <c r="R109" s="144"/>
-      <c r="S109" s="145" t="s">
+      <c r="R109" s="145"/>
+      <c r="S109" s="146" t="s">
         <v>296</v>
       </c>
-      <c r="T109" s="145"/>
+      <c r="T109" s="146"/>
       <c r="U109" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8443,16 +8447,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W109" s="142"/>
+      <c r="W109" s="143"/>
       <c r="X109" s="141"/>
-      <c r="Y109" s="141"/>
+      <c r="Y109" s="142"/>
       <c r="Z109" s="141"/>
-      <c r="AA109" s="146"/>
-      <c r="AB109" s="141"/>
+      <c r="AA109" s="147"/>
+      <c r="AB109" s="142"/>
       <c r="AC109" s="141"/>
       <c r="AD109" s="141"/>
-      <c r="AE109" s="149"/>
-      <c r="AF109" s="148"/>
+      <c r="AE109" s="150"/>
+      <c r="AF109" s="149"/>
     </row>
     <row r="110" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A110" s="141"/>
@@ -8460,25 +8464,25 @@
       <c r="C110" s="141"/>
       <c r="D110" s="141"/>
       <c r="E110" s="141"/>
-      <c r="F110" s="141"/>
-      <c r="G110" s="141"/>
-      <c r="H110" s="142"/>
-      <c r="I110" s="142"/>
+      <c r="F110" s="142"/>
+      <c r="G110" s="142"/>
+      <c r="H110" s="143"/>
+      <c r="I110" s="143"/>
       <c r="J110" s="141"/>
-      <c r="K110" s="141"/>
+      <c r="K110" s="142"/>
       <c r="L110" s="141"/>
       <c r="M110" s="141"/>
       <c r="N110" s="141"/>
-      <c r="O110" s="143" t="s">
+      <c r="O110" s="144" t="s">
         <v>297</v>
       </c>
       <c r="P110" s="141"/>
       <c r="Q110" s="141"/>
-      <c r="R110" s="144"/>
-      <c r="S110" s="145" t="s">
+      <c r="R110" s="145"/>
+      <c r="S110" s="146" t="s">
         <v>298</v>
       </c>
-      <c r="T110" s="145"/>
+      <c r="T110" s="146"/>
       <c r="U110" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8487,16 +8491,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W110" s="142"/>
+      <c r="W110" s="143"/>
       <c r="X110" s="141"/>
-      <c r="Y110" s="141"/>
+      <c r="Y110" s="142"/>
       <c r="Z110" s="141"/>
-      <c r="AA110" s="146"/>
-      <c r="AB110" s="141"/>
+      <c r="AA110" s="147"/>
+      <c r="AB110" s="142"/>
       <c r="AC110" s="141"/>
       <c r="AD110" s="141"/>
-      <c r="AE110" s="149"/>
-      <c r="AF110" s="148"/>
+      <c r="AE110" s="150"/>
+      <c r="AF110" s="149"/>
     </row>
     <row r="111" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A111" s="141"/>
@@ -8504,25 +8508,25 @@
       <c r="C111" s="141"/>
       <c r="D111" s="141"/>
       <c r="E111" s="141"/>
-      <c r="F111" s="141"/>
-      <c r="G111" s="141"/>
-      <c r="H111" s="142"/>
-      <c r="I111" s="142"/>
+      <c r="F111" s="142"/>
+      <c r="G111" s="142"/>
+      <c r="H111" s="143"/>
+      <c r="I111" s="143"/>
       <c r="J111" s="141"/>
-      <c r="K111" s="141"/>
+      <c r="K111" s="142"/>
       <c r="L111" s="141"/>
       <c r="M111" s="141"/>
       <c r="N111" s="141"/>
-      <c r="O111" s="143" t="s">
+      <c r="O111" s="144" t="s">
         <v>299</v>
       </c>
       <c r="P111" s="141"/>
       <c r="Q111" s="141"/>
-      <c r="R111" s="144"/>
-      <c r="S111" s="145" t="s">
+      <c r="R111" s="145"/>
+      <c r="S111" s="146" t="s">
         <v>300</v>
       </c>
-      <c r="T111" s="145"/>
+      <c r="T111" s="146"/>
       <c r="U111" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8531,16 +8535,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W111" s="142"/>
+      <c r="W111" s="143"/>
       <c r="X111" s="141"/>
-      <c r="Y111" s="141"/>
+      <c r="Y111" s="142"/>
       <c r="Z111" s="141"/>
-      <c r="AA111" s="146"/>
-      <c r="AB111" s="141"/>
+      <c r="AA111" s="147"/>
+      <c r="AB111" s="142"/>
       <c r="AC111" s="141"/>
       <c r="AD111" s="141"/>
-      <c r="AE111" s="150"/>
-      <c r="AF111" s="148"/>
+      <c r="AE111" s="151"/>
+      <c r="AF111" s="149"/>
     </row>
     <row r="112" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A112" s="141"/>
@@ -8548,25 +8552,25 @@
       <c r="C112" s="141"/>
       <c r="D112" s="141"/>
       <c r="E112" s="141"/>
-      <c r="F112" s="141"/>
-      <c r="G112" s="141"/>
-      <c r="H112" s="142"/>
-      <c r="I112" s="142"/>
+      <c r="F112" s="142"/>
+      <c r="G112" s="142"/>
+      <c r="H112" s="143"/>
+      <c r="I112" s="143"/>
       <c r="J112" s="141"/>
-      <c r="K112" s="141"/>
+      <c r="K112" s="142"/>
       <c r="L112" s="141"/>
       <c r="M112" s="141"/>
       <c r="N112" s="141"/>
-      <c r="O112" s="143" t="s">
+      <c r="O112" s="144" t="s">
         <v>301</v>
       </c>
       <c r="P112" s="141"/>
       <c r="Q112" s="141"/>
-      <c r="R112" s="144"/>
-      <c r="S112" s="145" t="s">
+      <c r="R112" s="145"/>
+      <c r="S112" s="146" t="s">
         <v>302</v>
       </c>
-      <c r="T112" s="145"/>
+      <c r="T112" s="146"/>
       <c r="U112" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8575,16 +8579,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W112" s="142"/>
+      <c r="W112" s="143"/>
       <c r="X112" s="141"/>
-      <c r="Y112" s="141"/>
+      <c r="Y112" s="142"/>
       <c r="Z112" s="141"/>
-      <c r="AA112" s="146"/>
-      <c r="AB112" s="141"/>
+      <c r="AA112" s="147"/>
+      <c r="AB112" s="142"/>
       <c r="AC112" s="141"/>
       <c r="AD112" s="141"/>
-      <c r="AE112" s="147"/>
-      <c r="AF112" s="148"/>
+      <c r="AE112" s="148"/>
+      <c r="AF112" s="149"/>
     </row>
     <row r="113" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A113" s="141"/>
@@ -8592,25 +8596,25 @@
       <c r="C113" s="141"/>
       <c r="D113" s="141"/>
       <c r="E113" s="141"/>
-      <c r="F113" s="141"/>
-      <c r="G113" s="141"/>
-      <c r="H113" s="142"/>
-      <c r="I113" s="142"/>
+      <c r="F113" s="142"/>
+      <c r="G113" s="142"/>
+      <c r="H113" s="143"/>
+      <c r="I113" s="143"/>
       <c r="J113" s="141"/>
-      <c r="K113" s="141"/>
+      <c r="K113" s="142"/>
       <c r="L113" s="141"/>
       <c r="M113" s="141"/>
       <c r="N113" s="141"/>
-      <c r="O113" s="143" t="s">
+      <c r="O113" s="144" t="s">
         <v>303</v>
       </c>
       <c r="P113" s="141"/>
       <c r="Q113" s="141"/>
-      <c r="R113" s="144"/>
-      <c r="S113" s="145" t="s">
+      <c r="R113" s="145"/>
+      <c r="S113" s="146" t="s">
         <v>304</v>
       </c>
-      <c r="T113" s="145"/>
+      <c r="T113" s="146"/>
       <c r="U113" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8619,16 +8623,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W113" s="142"/>
+      <c r="W113" s="143"/>
       <c r="X113" s="141"/>
-      <c r="Y113" s="141"/>
+      <c r="Y113" s="142"/>
       <c r="Z113" s="141"/>
-      <c r="AA113" s="146"/>
-      <c r="AB113" s="141"/>
+      <c r="AA113" s="147"/>
+      <c r="AB113" s="142"/>
       <c r="AC113" s="141"/>
       <c r="AD113" s="141"/>
-      <c r="AE113" s="149"/>
-      <c r="AF113" s="148"/>
+      <c r="AE113" s="150"/>
+      <c r="AF113" s="149"/>
     </row>
     <row r="114" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A114" s="141"/>
@@ -8636,25 +8640,25 @@
       <c r="C114" s="141"/>
       <c r="D114" s="141"/>
       <c r="E114" s="141"/>
-      <c r="F114" s="141"/>
-      <c r="G114" s="141"/>
-      <c r="H114" s="142"/>
-      <c r="I114" s="142"/>
+      <c r="F114" s="142"/>
+      <c r="G114" s="142"/>
+      <c r="H114" s="143"/>
+      <c r="I114" s="143"/>
       <c r="J114" s="141"/>
-      <c r="K114" s="141"/>
+      <c r="K114" s="142"/>
       <c r="L114" s="141"/>
       <c r="M114" s="141"/>
       <c r="N114" s="141"/>
-      <c r="O114" s="143" t="s">
+      <c r="O114" s="144" t="s">
         <v>305</v>
       </c>
       <c r="P114" s="141"/>
       <c r="Q114" s="141"/>
-      <c r="R114" s="144"/>
-      <c r="S114" s="145" t="s">
+      <c r="R114" s="145"/>
+      <c r="S114" s="146" t="s">
         <v>306</v>
       </c>
-      <c r="T114" s="145"/>
+      <c r="T114" s="146"/>
       <c r="U114" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8663,16 +8667,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W114" s="142"/>
+      <c r="W114" s="143"/>
       <c r="X114" s="141"/>
-      <c r="Y114" s="141"/>
+      <c r="Y114" s="142"/>
       <c r="Z114" s="141"/>
-      <c r="AA114" s="146"/>
-      <c r="AB114" s="141"/>
+      <c r="AA114" s="147"/>
+      <c r="AB114" s="142"/>
       <c r="AC114" s="141"/>
       <c r="AD114" s="141"/>
-      <c r="AE114" s="150"/>
-      <c r="AF114" s="148"/>
+      <c r="AE114" s="151"/>
+      <c r="AF114" s="149"/>
     </row>
     <row r="115" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A115" s="141" t="s">
@@ -8686,19 +8690,19 @@
       </c>
       <c r="D115" s="141"/>
       <c r="E115" s="141"/>
-      <c r="F115" s="141">
+      <c r="F115" s="142">
         <f>E115/2500</f>
         <v>0</v>
       </c>
-      <c r="G115" s="141"/>
-      <c r="H115" s="142" t="s">
+      <c r="G115" s="142"/>
+      <c r="H115" s="143" t="s">
         <v>194</v>
       </c>
-      <c r="I115" s="142" t="s">
+      <c r="I115" s="143" t="s">
         <v>309</v>
       </c>
       <c r="J115" s="141"/>
-      <c r="K115" s="141">
+      <c r="K115" s="142">
         <f>J115/300</f>
         <v>0</v>
       </c>
@@ -8707,16 +8711,16 @@
       </c>
       <c r="M115" s="141"/>
       <c r="N115" s="141"/>
-      <c r="O115" s="143" t="s">
+      <c r="O115" s="144" t="s">
         <v>310</v>
       </c>
       <c r="P115" s="141"/>
       <c r="Q115" s="141"/>
-      <c r="R115" s="144"/>
-      <c r="S115" s="145" t="s">
+      <c r="R115" s="145"/>
+      <c r="S115" s="146" t="s">
         <v>311</v>
       </c>
-      <c r="T115" s="145"/>
+      <c r="T115" s="146"/>
       <c r="U115" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8725,24 +8729,24 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W115" s="142">
+      <c r="W115" s="143">
         <v>402</v>
       </c>
       <c r="X115" s="141">
         <f>SUM(U115:U124)</f>
         <v>0</v>
       </c>
-      <c r="Y115" s="141">
+      <c r="Y115" s="142">
         <f>X115/2150</f>
         <v>0</v>
       </c>
       <c r="Z115" s="141">
         <v>170</v>
       </c>
-      <c r="AA115" s="146">
+      <c r="AA115" s="147">
         <v>170</v>
       </c>
-      <c r="AB115" s="141">
+      <c r="AB115" s="142">
         <f>115/Z115</f>
         <v>0.676470588235294</v>
       </c>
@@ -8752,10 +8756,10 @@
       <c r="AD115" s="141">
         <v>0</v>
       </c>
-      <c r="AE115" s="147" t="s">
+      <c r="AE115" s="148" t="s">
         <v>198</v>
       </c>
-      <c r="AF115" s="148"/>
+      <c r="AF115" s="149"/>
     </row>
     <row r="116" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A116" s="141"/>
@@ -8763,25 +8767,25 @@
       <c r="C116" s="141"/>
       <c r="D116" s="141"/>
       <c r="E116" s="141"/>
-      <c r="F116" s="141"/>
-      <c r="G116" s="141"/>
-      <c r="H116" s="142"/>
-      <c r="I116" s="142"/>
+      <c r="F116" s="142"/>
+      <c r="G116" s="142"/>
+      <c r="H116" s="143"/>
+      <c r="I116" s="143"/>
       <c r="J116" s="141"/>
-      <c r="K116" s="141"/>
+      <c r="K116" s="142"/>
       <c r="L116" s="141"/>
       <c r="M116" s="141"/>
       <c r="N116" s="141"/>
-      <c r="O116" s="143" t="s">
+      <c r="O116" s="144" t="s">
         <v>312</v>
       </c>
       <c r="P116" s="141"/>
       <c r="Q116" s="141"/>
-      <c r="R116" s="144"/>
-      <c r="S116" s="145" t="s">
+      <c r="R116" s="145"/>
+      <c r="S116" s="146" t="s">
         <v>313</v>
       </c>
-      <c r="T116" s="145"/>
+      <c r="T116" s="146"/>
       <c r="U116" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8790,16 +8794,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W116" s="142"/>
+      <c r="W116" s="143"/>
       <c r="X116" s="141"/>
-      <c r="Y116" s="141"/>
+      <c r="Y116" s="142"/>
       <c r="Z116" s="141"/>
-      <c r="AA116" s="146"/>
-      <c r="AB116" s="141"/>
+      <c r="AA116" s="147"/>
+      <c r="AB116" s="142"/>
       <c r="AC116" s="141"/>
       <c r="AD116" s="141"/>
-      <c r="AE116" s="149"/>
-      <c r="AF116" s="148"/>
+      <c r="AE116" s="150"/>
+      <c r="AF116" s="149"/>
     </row>
     <row r="117" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A117" s="141"/>
@@ -8807,25 +8811,25 @@
       <c r="C117" s="141"/>
       <c r="D117" s="141"/>
       <c r="E117" s="141"/>
-      <c r="F117" s="141"/>
-      <c r="G117" s="141"/>
-      <c r="H117" s="142"/>
-      <c r="I117" s="142"/>
+      <c r="F117" s="142"/>
+      <c r="G117" s="142"/>
+      <c r="H117" s="143"/>
+      <c r="I117" s="143"/>
       <c r="J117" s="141"/>
-      <c r="K117" s="141"/>
+      <c r="K117" s="142"/>
       <c r="L117" s="141"/>
       <c r="M117" s="141"/>
       <c r="N117" s="141"/>
-      <c r="O117" s="143" t="s">
+      <c r="O117" s="144" t="s">
         <v>314</v>
       </c>
       <c r="P117" s="141"/>
       <c r="Q117" s="141"/>
-      <c r="R117" s="144"/>
-      <c r="S117" s="145" t="s">
+      <c r="R117" s="145"/>
+      <c r="S117" s="146" t="s">
         <v>315</v>
       </c>
-      <c r="T117" s="145"/>
+      <c r="T117" s="146"/>
       <c r="U117" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8834,16 +8838,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W117" s="142"/>
+      <c r="W117" s="143"/>
       <c r="X117" s="141"/>
-      <c r="Y117" s="141"/>
+      <c r="Y117" s="142"/>
       <c r="Z117" s="141"/>
-      <c r="AA117" s="146"/>
-      <c r="AB117" s="141"/>
+      <c r="AA117" s="147"/>
+      <c r="AB117" s="142"/>
       <c r="AC117" s="141"/>
       <c r="AD117" s="141"/>
-      <c r="AE117" s="150"/>
-      <c r="AF117" s="148"/>
+      <c r="AE117" s="151"/>
+      <c r="AF117" s="149"/>
     </row>
     <row r="118" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A118" s="141"/>
@@ -8851,25 +8855,25 @@
       <c r="C118" s="141"/>
       <c r="D118" s="141"/>
       <c r="E118" s="141"/>
-      <c r="F118" s="141"/>
-      <c r="G118" s="141"/>
-      <c r="H118" s="142"/>
-      <c r="I118" s="142"/>
+      <c r="F118" s="142"/>
+      <c r="G118" s="142"/>
+      <c r="H118" s="143"/>
+      <c r="I118" s="143"/>
       <c r="J118" s="141"/>
-      <c r="K118" s="141"/>
+      <c r="K118" s="142"/>
       <c r="L118" s="141"/>
       <c r="M118" s="141"/>
       <c r="N118" s="141"/>
-      <c r="O118" s="143" t="s">
+      <c r="O118" s="144" t="s">
         <v>316</v>
       </c>
       <c r="P118" s="141"/>
       <c r="Q118" s="141"/>
-      <c r="R118" s="144"/>
-      <c r="S118" s="145" t="s">
+      <c r="R118" s="145"/>
+      <c r="S118" s="146" t="s">
         <v>317</v>
       </c>
-      <c r="T118" s="145"/>
+      <c r="T118" s="146"/>
       <c r="U118" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8878,16 +8882,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W118" s="142"/>
+      <c r="W118" s="143"/>
       <c r="X118" s="141"/>
-      <c r="Y118" s="141"/>
+      <c r="Y118" s="142"/>
       <c r="Z118" s="141"/>
-      <c r="AA118" s="146"/>
-      <c r="AB118" s="141"/>
+      <c r="AA118" s="147"/>
+      <c r="AB118" s="142"/>
       <c r="AC118" s="141"/>
       <c r="AD118" s="141"/>
-      <c r="AE118" s="147"/>
-      <c r="AF118" s="148"/>
+      <c r="AE118" s="148"/>
+      <c r="AF118" s="149"/>
     </row>
     <row r="119" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A119" s="141"/>
@@ -8895,25 +8899,25 @@
       <c r="C119" s="141"/>
       <c r="D119" s="141"/>
       <c r="E119" s="141"/>
-      <c r="F119" s="141"/>
-      <c r="G119" s="141"/>
-      <c r="H119" s="142"/>
-      <c r="I119" s="142"/>
+      <c r="F119" s="142"/>
+      <c r="G119" s="142"/>
+      <c r="H119" s="143"/>
+      <c r="I119" s="143"/>
       <c r="J119" s="141"/>
-      <c r="K119" s="141"/>
+      <c r="K119" s="142"/>
       <c r="L119" s="141"/>
       <c r="M119" s="141"/>
       <c r="N119" s="141"/>
-      <c r="O119" s="143" t="s">
+      <c r="O119" s="144" t="s">
         <v>318</v>
       </c>
       <c r="P119" s="141"/>
       <c r="Q119" s="141"/>
-      <c r="R119" s="144"/>
-      <c r="S119" s="145" t="s">
+      <c r="R119" s="145"/>
+      <c r="S119" s="146" t="s">
         <v>319</v>
       </c>
-      <c r="T119" s="145"/>
+      <c r="T119" s="146"/>
       <c r="U119" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8922,16 +8926,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W119" s="142"/>
+      <c r="W119" s="143"/>
       <c r="X119" s="141"/>
-      <c r="Y119" s="141"/>
+      <c r="Y119" s="142"/>
       <c r="Z119" s="141"/>
-      <c r="AA119" s="146"/>
-      <c r="AB119" s="141"/>
+      <c r="AA119" s="147"/>
+      <c r="AB119" s="142"/>
       <c r="AC119" s="141"/>
       <c r="AD119" s="141"/>
-      <c r="AE119" s="150"/>
-      <c r="AF119" s="148"/>
+      <c r="AE119" s="151"/>
+      <c r="AF119" s="149"/>
     </row>
     <row r="120" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A120" s="141"/>
@@ -8943,30 +8947,30 @@
       </c>
       <c r="D120" s="141"/>
       <c r="E120" s="141"/>
-      <c r="F120" s="141">
+      <c r="F120" s="142">
         <f>E120/2500</f>
         <v>0</v>
       </c>
-      <c r="G120" s="141"/>
-      <c r="H120" s="142" t="s">
+      <c r="G120" s="142"/>
+      <c r="H120" s="143" t="s">
         <v>194</v>
       </c>
-      <c r="I120" s="142"/>
+      <c r="I120" s="143"/>
       <c r="J120" s="141"/>
-      <c r="K120" s="141"/>
+      <c r="K120" s="142"/>
       <c r="L120" s="141"/>
       <c r="M120" s="141"/>
       <c r="N120" s="141"/>
-      <c r="O120" s="143" t="s">
+      <c r="O120" s="144" t="s">
         <v>321</v>
       </c>
       <c r="P120" s="141"/>
       <c r="Q120" s="141"/>
-      <c r="R120" s="144"/>
-      <c r="S120" s="145" t="s">
+      <c r="R120" s="145"/>
+      <c r="S120" s="146" t="s">
         <v>322</v>
       </c>
-      <c r="T120" s="145"/>
+      <c r="T120" s="146"/>
       <c r="U120" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8975,18 +8979,18 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W120" s="142"/>
+      <c r="W120" s="143"/>
       <c r="X120" s="141"/>
-      <c r="Y120" s="141"/>
+      <c r="Y120" s="142"/>
       <c r="Z120" s="141"/>
-      <c r="AA120" s="146"/>
-      <c r="AB120" s="141"/>
+      <c r="AA120" s="147"/>
+      <c r="AB120" s="142"/>
       <c r="AC120" s="141"/>
       <c r="AD120" s="141"/>
-      <c r="AE120" s="147" t="s">
+      <c r="AE120" s="148" t="s">
         <v>210</v>
       </c>
-      <c r="AF120" s="148"/>
+      <c r="AF120" s="149"/>
     </row>
     <row r="121" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A121" s="141"/>
@@ -8994,25 +8998,25 @@
       <c r="C121" s="141"/>
       <c r="D121" s="141"/>
       <c r="E121" s="141"/>
-      <c r="F121" s="141"/>
-      <c r="G121" s="141"/>
-      <c r="H121" s="142"/>
-      <c r="I121" s="142"/>
+      <c r="F121" s="142"/>
+      <c r="G121" s="142"/>
+      <c r="H121" s="143"/>
+      <c r="I121" s="143"/>
       <c r="J121" s="141"/>
-      <c r="K121" s="141"/>
+      <c r="K121" s="142"/>
       <c r="L121" s="141"/>
       <c r="M121" s="141"/>
       <c r="N121" s="141"/>
-      <c r="O121" s="143" t="s">
+      <c r="O121" s="144" t="s">
         <v>323</v>
       </c>
       <c r="P121" s="141"/>
       <c r="Q121" s="141"/>
-      <c r="R121" s="144"/>
-      <c r="S121" s="145" t="s">
+      <c r="R121" s="145"/>
+      <c r="S121" s="146" t="s">
         <v>324</v>
       </c>
-      <c r="T121" s="145"/>
+      <c r="T121" s="146"/>
       <c r="U121" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9021,16 +9025,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W121" s="142"/>
+      <c r="W121" s="143"/>
       <c r="X121" s="141"/>
-      <c r="Y121" s="141"/>
+      <c r="Y121" s="142"/>
       <c r="Z121" s="141"/>
-      <c r="AA121" s="146"/>
-      <c r="AB121" s="141"/>
+      <c r="AA121" s="147"/>
+      <c r="AB121" s="142"/>
       <c r="AC121" s="141"/>
       <c r="AD121" s="141"/>
-      <c r="AE121" s="149"/>
-      <c r="AF121" s="148"/>
+      <c r="AE121" s="150"/>
+      <c r="AF121" s="149"/>
     </row>
     <row r="122" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A122" s="141"/>
@@ -9038,25 +9042,25 @@
       <c r="C122" s="141"/>
       <c r="D122" s="141"/>
       <c r="E122" s="141"/>
-      <c r="F122" s="141"/>
-      <c r="G122" s="141"/>
-      <c r="H122" s="142"/>
-      <c r="I122" s="142"/>
+      <c r="F122" s="142"/>
+      <c r="G122" s="142"/>
+      <c r="H122" s="143"/>
+      <c r="I122" s="143"/>
       <c r="J122" s="141"/>
-      <c r="K122" s="141"/>
+      <c r="K122" s="142"/>
       <c r="L122" s="141"/>
       <c r="M122" s="141"/>
       <c r="N122" s="141"/>
-      <c r="O122" s="143" t="s">
+      <c r="O122" s="144" t="s">
         <v>325</v>
       </c>
       <c r="P122" s="141"/>
       <c r="Q122" s="141"/>
-      <c r="R122" s="144"/>
-      <c r="S122" s="145" t="s">
+      <c r="R122" s="145"/>
+      <c r="S122" s="146" t="s">
         <v>326</v>
       </c>
-      <c r="T122" s="145"/>
+      <c r="T122" s="146"/>
       <c r="U122" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9065,16 +9069,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W122" s="142"/>
+      <c r="W122" s="143"/>
       <c r="X122" s="141"/>
-      <c r="Y122" s="141"/>
+      <c r="Y122" s="142"/>
       <c r="Z122" s="141"/>
-      <c r="AA122" s="146"/>
-      <c r="AB122" s="141"/>
+      <c r="AA122" s="147"/>
+      <c r="AB122" s="142"/>
       <c r="AC122" s="141"/>
       <c r="AD122" s="141"/>
-      <c r="AE122" s="150"/>
-      <c r="AF122" s="148"/>
+      <c r="AE122" s="151"/>
+      <c r="AF122" s="149"/>
     </row>
     <row r="123" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A123" s="141"/>
@@ -9082,25 +9086,25 @@
       <c r="C123" s="141"/>
       <c r="D123" s="141"/>
       <c r="E123" s="141"/>
-      <c r="F123" s="141"/>
-      <c r="G123" s="141"/>
-      <c r="H123" s="142"/>
-      <c r="I123" s="142"/>
+      <c r="F123" s="142"/>
+      <c r="G123" s="142"/>
+      <c r="H123" s="143"/>
+      <c r="I123" s="143"/>
       <c r="J123" s="141"/>
-      <c r="K123" s="141"/>
+      <c r="K123" s="142"/>
       <c r="L123" s="141"/>
       <c r="M123" s="141"/>
       <c r="N123" s="141"/>
-      <c r="O123" s="143" t="s">
+      <c r="O123" s="144" t="s">
         <v>327</v>
       </c>
       <c r="P123" s="141"/>
       <c r="Q123" s="141"/>
-      <c r="R123" s="144"/>
-      <c r="S123" s="145" t="s">
+      <c r="R123" s="145"/>
+      <c r="S123" s="146" t="s">
         <v>328</v>
       </c>
-      <c r="T123" s="145"/>
+      <c r="T123" s="146"/>
       <c r="U123" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9109,16 +9113,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W123" s="142"/>
+      <c r="W123" s="143"/>
       <c r="X123" s="141"/>
-      <c r="Y123" s="141"/>
+      <c r="Y123" s="142"/>
       <c r="Z123" s="141"/>
-      <c r="AA123" s="146"/>
-      <c r="AB123" s="141"/>
+      <c r="AA123" s="147"/>
+      <c r="AB123" s="142"/>
       <c r="AC123" s="141"/>
       <c r="AD123" s="141"/>
-      <c r="AE123" s="147"/>
-      <c r="AF123" s="148"/>
+      <c r="AE123" s="148"/>
+      <c r="AF123" s="149"/>
     </row>
     <row r="124" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A124" s="141"/>
@@ -9126,25 +9130,25 @@
       <c r="C124" s="141"/>
       <c r="D124" s="141"/>
       <c r="E124" s="141"/>
-      <c r="F124" s="141"/>
-      <c r="G124" s="141"/>
-      <c r="H124" s="142"/>
-      <c r="I124" s="142"/>
+      <c r="F124" s="142"/>
+      <c r="G124" s="142"/>
+      <c r="H124" s="143"/>
+      <c r="I124" s="143"/>
       <c r="J124" s="141"/>
-      <c r="K124" s="141"/>
+      <c r="K124" s="142"/>
       <c r="L124" s="141"/>
       <c r="M124" s="141"/>
       <c r="N124" s="141"/>
-      <c r="O124" s="143" t="s">
+      <c r="O124" s="144" t="s">
         <v>329</v>
       </c>
       <c r="P124" s="141"/>
       <c r="Q124" s="141"/>
-      <c r="R124" s="144"/>
-      <c r="S124" s="145" t="s">
+      <c r="R124" s="145"/>
+      <c r="S124" s="146" t="s">
         <v>330</v>
       </c>
-      <c r="T124" s="145"/>
+      <c r="T124" s="146"/>
       <c r="U124" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9153,16 +9157,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W124" s="142"/>
+      <c r="W124" s="143"/>
       <c r="X124" s="141"/>
-      <c r="Y124" s="141"/>
+      <c r="Y124" s="142"/>
       <c r="Z124" s="141"/>
-      <c r="AA124" s="146"/>
-      <c r="AB124" s="141"/>
+      <c r="AA124" s="147"/>
+      <c r="AB124" s="142"/>
       <c r="AC124" s="141"/>
       <c r="AD124" s="141"/>
-      <c r="AE124" s="150"/>
-      <c r="AF124" s="148"/>
+      <c r="AE124" s="151"/>
+      <c r="AF124" s="149"/>
     </row>
     <row r="125" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A125" s="141" t="s">
@@ -9176,19 +9180,19 @@
       </c>
       <c r="D125" s="141"/>
       <c r="E125" s="141"/>
-      <c r="F125" s="141">
+      <c r="F125" s="142">
         <f>E125/2500</f>
         <v>0</v>
       </c>
-      <c r="G125" s="141"/>
-      <c r="H125" s="142" t="s">
+      <c r="G125" s="142"/>
+      <c r="H125" s="143" t="s">
         <v>194</v>
       </c>
-      <c r="I125" s="142" t="s">
+      <c r="I125" s="143" t="s">
         <v>333</v>
       </c>
       <c r="J125" s="141"/>
-      <c r="K125" s="141">
+      <c r="K125" s="142">
         <f>J125/300</f>
         <v>0</v>
       </c>
@@ -9197,16 +9201,16 @@
       </c>
       <c r="M125" s="141"/>
       <c r="N125" s="141"/>
-      <c r="O125" s="143" t="s">
+      <c r="O125" s="144" t="s">
         <v>334</v>
       </c>
       <c r="P125" s="141"/>
       <c r="Q125" s="141"/>
-      <c r="R125" s="144"/>
-      <c r="S125" s="145" t="s">
+      <c r="R125" s="145"/>
+      <c r="S125" s="146" t="s">
         <v>335</v>
       </c>
-      <c r="T125" s="145"/>
+      <c r="T125" s="146"/>
       <c r="U125" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9215,24 +9219,24 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W125" s="142">
+      <c r="W125" s="143">
         <v>401</v>
       </c>
       <c r="X125" s="141">
         <f>SUM(U125:U134)</f>
         <v>0</v>
       </c>
-      <c r="Y125" s="141">
+      <c r="Y125" s="142">
         <f>X125/2150</f>
         <v>0</v>
       </c>
       <c r="Z125" s="141">
         <v>170</v>
       </c>
-      <c r="AA125" s="146">
+      <c r="AA125" s="147">
         <v>170</v>
       </c>
-      <c r="AB125" s="141">
+      <c r="AB125" s="142">
         <f>125/Z125</f>
         <v>0.735294117647059</v>
       </c>
@@ -9242,10 +9246,10 @@
       <c r="AD125" s="141">
         <v>0</v>
       </c>
-      <c r="AE125" s="147" t="s">
+      <c r="AE125" s="148" t="s">
         <v>198</v>
       </c>
-      <c r="AF125" s="148"/>
+      <c r="AF125" s="149"/>
     </row>
     <row r="126" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A126" s="141"/>
@@ -9253,25 +9257,25 @@
       <c r="C126" s="141"/>
       <c r="D126" s="141"/>
       <c r="E126" s="141"/>
-      <c r="F126" s="141"/>
-      <c r="G126" s="141"/>
-      <c r="H126" s="142"/>
-      <c r="I126" s="142"/>
+      <c r="F126" s="142"/>
+      <c r="G126" s="142"/>
+      <c r="H126" s="143"/>
+      <c r="I126" s="143"/>
       <c r="J126" s="141"/>
-      <c r="K126" s="141"/>
+      <c r="K126" s="142"/>
       <c r="L126" s="141"/>
       <c r="M126" s="141"/>
       <c r="N126" s="141"/>
-      <c r="O126" s="143" t="s">
+      <c r="O126" s="144" t="s">
         <v>336</v>
       </c>
       <c r="P126" s="141"/>
       <c r="Q126" s="141"/>
-      <c r="R126" s="144"/>
-      <c r="S126" s="145" t="s">
+      <c r="R126" s="145"/>
+      <c r="S126" s="146" t="s">
         <v>337</v>
       </c>
-      <c r="T126" s="145"/>
+      <c r="T126" s="146"/>
       <c r="U126" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9280,16 +9284,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W126" s="142"/>
+      <c r="W126" s="143"/>
       <c r="X126" s="141"/>
-      <c r="Y126" s="141"/>
+      <c r="Y126" s="142"/>
       <c r="Z126" s="141"/>
-      <c r="AA126" s="146"/>
-      <c r="AB126" s="141"/>
+      <c r="AA126" s="147"/>
+      <c r="AB126" s="142"/>
       <c r="AC126" s="141"/>
       <c r="AD126" s="141"/>
-      <c r="AE126" s="149"/>
-      <c r="AF126" s="148"/>
+      <c r="AE126" s="150"/>
+      <c r="AF126" s="149"/>
     </row>
     <row r="127" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A127" s="141"/>
@@ -9297,25 +9301,25 @@
       <c r="C127" s="141"/>
       <c r="D127" s="141"/>
       <c r="E127" s="141"/>
-      <c r="F127" s="141"/>
-      <c r="G127" s="141"/>
-      <c r="H127" s="142"/>
-      <c r="I127" s="142"/>
+      <c r="F127" s="142"/>
+      <c r="G127" s="142"/>
+      <c r="H127" s="143"/>
+      <c r="I127" s="143"/>
       <c r="J127" s="141"/>
-      <c r="K127" s="141"/>
+      <c r="K127" s="142"/>
       <c r="L127" s="141"/>
       <c r="M127" s="141"/>
       <c r="N127" s="141"/>
-      <c r="O127" s="143" t="s">
+      <c r="O127" s="144" t="s">
         <v>338</v>
       </c>
       <c r="P127" s="141"/>
       <c r="Q127" s="141"/>
-      <c r="R127" s="144"/>
-      <c r="S127" s="145" t="s">
+      <c r="R127" s="145"/>
+      <c r="S127" s="146" t="s">
         <v>339</v>
       </c>
-      <c r="T127" s="145"/>
+      <c r="T127" s="146"/>
       <c r="U127" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9324,16 +9328,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W127" s="142"/>
+      <c r="W127" s="143"/>
       <c r="X127" s="141"/>
-      <c r="Y127" s="141"/>
+      <c r="Y127" s="142"/>
       <c r="Z127" s="141"/>
-      <c r="AA127" s="146"/>
-      <c r="AB127" s="141"/>
+      <c r="AA127" s="147"/>
+      <c r="AB127" s="142"/>
       <c r="AC127" s="141"/>
       <c r="AD127" s="141"/>
-      <c r="AE127" s="150"/>
-      <c r="AF127" s="148"/>
+      <c r="AE127" s="151"/>
+      <c r="AF127" s="149"/>
     </row>
     <row r="128" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A128" s="141"/>
@@ -9341,25 +9345,25 @@
       <c r="C128" s="141"/>
       <c r="D128" s="141"/>
       <c r="E128" s="141"/>
-      <c r="F128" s="141"/>
-      <c r="G128" s="141"/>
-      <c r="H128" s="142"/>
-      <c r="I128" s="142"/>
+      <c r="F128" s="142"/>
+      <c r="G128" s="142"/>
+      <c r="H128" s="143"/>
+      <c r="I128" s="143"/>
       <c r="J128" s="141"/>
-      <c r="K128" s="141"/>
+      <c r="K128" s="142"/>
       <c r="L128" s="141"/>
       <c r="M128" s="141"/>
       <c r="N128" s="141"/>
-      <c r="O128" s="143" t="s">
+      <c r="O128" s="144" t="s">
         <v>340</v>
       </c>
       <c r="P128" s="141"/>
       <c r="Q128" s="141"/>
-      <c r="R128" s="144"/>
-      <c r="S128" s="145" t="s">
+      <c r="R128" s="145"/>
+      <c r="S128" s="146" t="s">
         <v>341</v>
       </c>
-      <c r="T128" s="145"/>
+      <c r="T128" s="146"/>
       <c r="U128" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9368,16 +9372,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W128" s="142"/>
+      <c r="W128" s="143"/>
       <c r="X128" s="141"/>
-      <c r="Y128" s="141"/>
+      <c r="Y128" s="142"/>
       <c r="Z128" s="141"/>
-      <c r="AA128" s="146"/>
-      <c r="AB128" s="141"/>
+      <c r="AA128" s="147"/>
+      <c r="AB128" s="142"/>
       <c r="AC128" s="141"/>
       <c r="AD128" s="141"/>
-      <c r="AE128" s="147"/>
-      <c r="AF128" s="148"/>
+      <c r="AE128" s="148"/>
+      <c r="AF128" s="149"/>
     </row>
     <row r="129" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A129" s="141"/>
@@ -9385,25 +9389,25 @@
       <c r="C129" s="141"/>
       <c r="D129" s="141"/>
       <c r="E129" s="141"/>
-      <c r="F129" s="141"/>
-      <c r="G129" s="141"/>
-      <c r="H129" s="142"/>
-      <c r="I129" s="142"/>
+      <c r="F129" s="142"/>
+      <c r="G129" s="142"/>
+      <c r="H129" s="143"/>
+      <c r="I129" s="143"/>
       <c r="J129" s="141"/>
-      <c r="K129" s="141"/>
+      <c r="K129" s="142"/>
       <c r="L129" s="141"/>
       <c r="M129" s="141"/>
       <c r="N129" s="141"/>
-      <c r="O129" s="143" t="s">
+      <c r="O129" s="144" t="s">
         <v>342</v>
       </c>
       <c r="P129" s="141"/>
       <c r="Q129" s="141"/>
-      <c r="R129" s="144"/>
-      <c r="S129" s="145" t="s">
+      <c r="R129" s="145"/>
+      <c r="S129" s="146" t="s">
         <v>343</v>
       </c>
-      <c r="T129" s="145"/>
+      <c r="T129" s="146"/>
       <c r="U129" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9412,16 +9416,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W129" s="142"/>
+      <c r="W129" s="143"/>
       <c r="X129" s="141"/>
-      <c r="Y129" s="141"/>
+      <c r="Y129" s="142"/>
       <c r="Z129" s="141"/>
-      <c r="AA129" s="146"/>
-      <c r="AB129" s="141"/>
+      <c r="AA129" s="147"/>
+      <c r="AB129" s="142"/>
       <c r="AC129" s="141"/>
       <c r="AD129" s="141"/>
-      <c r="AE129" s="150"/>
-      <c r="AF129" s="148"/>
+      <c r="AE129" s="151"/>
+      <c r="AF129" s="149"/>
     </row>
     <row r="130" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A130" s="141"/>
@@ -9433,30 +9437,30 @@
       </c>
       <c r="D130" s="141"/>
       <c r="E130" s="141"/>
-      <c r="F130" s="141">
+      <c r="F130" s="142">
         <f>E130/2500</f>
         <v>0</v>
       </c>
-      <c r="G130" s="141"/>
-      <c r="H130" s="142" t="s">
+      <c r="G130" s="142"/>
+      <c r="H130" s="143" t="s">
         <v>194</v>
       </c>
-      <c r="I130" s="142"/>
+      <c r="I130" s="143"/>
       <c r="J130" s="141"/>
-      <c r="K130" s="141"/>
+      <c r="K130" s="142"/>
       <c r="L130" s="141"/>
       <c r="M130" s="141"/>
       <c r="N130" s="141"/>
-      <c r="O130" s="143" t="s">
+      <c r="O130" s="144" t="s">
         <v>345</v>
       </c>
       <c r="P130" s="141"/>
       <c r="Q130" s="141"/>
-      <c r="R130" s="144"/>
-      <c r="S130" s="145" t="s">
+      <c r="R130" s="145"/>
+      <c r="S130" s="146" t="s">
         <v>346</v>
       </c>
-      <c r="T130" s="145"/>
+      <c r="T130" s="146"/>
       <c r="U130" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9465,18 +9469,18 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W130" s="142"/>
+      <c r="W130" s="143"/>
       <c r="X130" s="141"/>
-      <c r="Y130" s="141"/>
+      <c r="Y130" s="142"/>
       <c r="Z130" s="141"/>
-      <c r="AA130" s="146"/>
-      <c r="AB130" s="141"/>
+      <c r="AA130" s="147"/>
+      <c r="AB130" s="142"/>
       <c r="AC130" s="141"/>
       <c r="AD130" s="141"/>
-      <c r="AE130" s="147" t="s">
+      <c r="AE130" s="148" t="s">
         <v>210</v>
       </c>
-      <c r="AF130" s="148"/>
+      <c r="AF130" s="149"/>
     </row>
     <row r="131" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A131" s="141"/>
@@ -9484,25 +9488,25 @@
       <c r="C131" s="141"/>
       <c r="D131" s="141"/>
       <c r="E131" s="141"/>
-      <c r="F131" s="141"/>
-      <c r="G131" s="141"/>
-      <c r="H131" s="142"/>
-      <c r="I131" s="142"/>
+      <c r="F131" s="142"/>
+      <c r="G131" s="142"/>
+      <c r="H131" s="143"/>
+      <c r="I131" s="143"/>
       <c r="J131" s="141"/>
-      <c r="K131" s="141"/>
+      <c r="K131" s="142"/>
       <c r="L131" s="141"/>
       <c r="M131" s="141"/>
       <c r="N131" s="141"/>
-      <c r="O131" s="143" t="s">
+      <c r="O131" s="144" t="s">
         <v>347</v>
       </c>
       <c r="P131" s="141"/>
       <c r="Q131" s="141"/>
-      <c r="R131" s="144"/>
-      <c r="S131" s="145" t="s">
+      <c r="R131" s="145"/>
+      <c r="S131" s="146" t="s">
         <v>348</v>
       </c>
-      <c r="T131" s="145"/>
+      <c r="T131" s="146"/>
       <c r="U131" s="141">
         <f t="shared" ref="U131:U134" si="2">R131*0.935</f>
         <v>0</v>
@@ -9511,16 +9515,16 @@
         <f t="shared" ref="V131:V134" si="3">U131/215</f>
         <v>0</v>
       </c>
-      <c r="W131" s="142"/>
+      <c r="W131" s="143"/>
       <c r="X131" s="141"/>
-      <c r="Y131" s="141"/>
+      <c r="Y131" s="142"/>
       <c r="Z131" s="141"/>
-      <c r="AA131" s="146"/>
-      <c r="AB131" s="141"/>
+      <c r="AA131" s="147"/>
+      <c r="AB131" s="142"/>
       <c r="AC131" s="141"/>
       <c r="AD131" s="141"/>
-      <c r="AE131" s="149"/>
-      <c r="AF131" s="148"/>
+      <c r="AE131" s="150"/>
+      <c r="AF131" s="149"/>
     </row>
     <row r="132" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A132" s="141"/>
@@ -9528,25 +9532,25 @@
       <c r="C132" s="141"/>
       <c r="D132" s="141"/>
       <c r="E132" s="141"/>
-      <c r="F132" s="141"/>
-      <c r="G132" s="141"/>
-      <c r="H132" s="142"/>
-      <c r="I132" s="142"/>
+      <c r="F132" s="142"/>
+      <c r="G132" s="142"/>
+      <c r="H132" s="143"/>
+      <c r="I132" s="143"/>
       <c r="J132" s="141"/>
-      <c r="K132" s="141"/>
+      <c r="K132" s="142"/>
       <c r="L132" s="141"/>
       <c r="M132" s="141"/>
       <c r="N132" s="141"/>
-      <c r="O132" s="143" t="s">
+      <c r="O132" s="144" t="s">
         <v>349</v>
       </c>
       <c r="P132" s="141"/>
       <c r="Q132" s="141"/>
-      <c r="R132" s="144"/>
-      <c r="S132" s="145" t="s">
+      <c r="R132" s="145"/>
+      <c r="S132" s="146" t="s">
         <v>350</v>
       </c>
-      <c r="T132" s="145"/>
+      <c r="T132" s="146"/>
       <c r="U132" s="141">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -9555,16 +9559,16 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W132" s="142"/>
+      <c r="W132" s="143"/>
       <c r="X132" s="141"/>
-      <c r="Y132" s="141"/>
+      <c r="Y132" s="142"/>
       <c r="Z132" s="141"/>
-      <c r="AA132" s="146"/>
-      <c r="AB132" s="141"/>
+      <c r="AA132" s="147"/>
+      <c r="AB132" s="142"/>
       <c r="AC132" s="141"/>
       <c r="AD132" s="141"/>
-      <c r="AE132" s="150"/>
-      <c r="AF132" s="148"/>
+      <c r="AE132" s="151"/>
+      <c r="AF132" s="149"/>
     </row>
     <row r="133" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A133" s="141"/>
@@ -9572,25 +9576,25 @@
       <c r="C133" s="141"/>
       <c r="D133" s="141"/>
       <c r="E133" s="141"/>
-      <c r="F133" s="141"/>
-      <c r="G133" s="141"/>
-      <c r="H133" s="142"/>
-      <c r="I133" s="142"/>
+      <c r="F133" s="142"/>
+      <c r="G133" s="142"/>
+      <c r="H133" s="143"/>
+      <c r="I133" s="143"/>
       <c r="J133" s="141"/>
-      <c r="K133" s="141"/>
+      <c r="K133" s="142"/>
       <c r="L133" s="141"/>
       <c r="M133" s="141"/>
       <c r="N133" s="141"/>
-      <c r="O133" s="143" t="s">
+      <c r="O133" s="144" t="s">
         <v>351</v>
       </c>
       <c r="P133" s="141"/>
       <c r="Q133" s="141"/>
-      <c r="R133" s="144"/>
-      <c r="S133" s="145" t="s">
+      <c r="R133" s="145"/>
+      <c r="S133" s="146" t="s">
         <v>352</v>
       </c>
-      <c r="T133" s="145"/>
+      <c r="T133" s="146"/>
       <c r="U133" s="141">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -9599,16 +9603,16 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W133" s="142"/>
+      <c r="W133" s="143"/>
       <c r="X133" s="141"/>
-      <c r="Y133" s="141"/>
+      <c r="Y133" s="142"/>
       <c r="Z133" s="141"/>
-      <c r="AA133" s="146"/>
-      <c r="AB133" s="141"/>
+      <c r="AA133" s="147"/>
+      <c r="AB133" s="142"/>
       <c r="AC133" s="141"/>
       <c r="AD133" s="141"/>
-      <c r="AE133" s="147"/>
-      <c r="AF133" s="148"/>
+      <c r="AE133" s="148"/>
+      <c r="AF133" s="149"/>
     </row>
     <row r="134" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A134" s="141"/>
@@ -9616,25 +9620,25 @@
       <c r="C134" s="141"/>
       <c r="D134" s="141"/>
       <c r="E134" s="141"/>
-      <c r="F134" s="141"/>
-      <c r="G134" s="141"/>
-      <c r="H134" s="142"/>
-      <c r="I134" s="142"/>
+      <c r="F134" s="142"/>
+      <c r="G134" s="142"/>
+      <c r="H134" s="143"/>
+      <c r="I134" s="143"/>
       <c r="J134" s="141"/>
-      <c r="K134" s="141"/>
+      <c r="K134" s="142"/>
       <c r="L134" s="141"/>
       <c r="M134" s="141"/>
       <c r="N134" s="141"/>
-      <c r="O134" s="143" t="s">
+      <c r="O134" s="144" t="s">
         <v>353</v>
       </c>
       <c r="P134" s="141"/>
       <c r="Q134" s="141"/>
-      <c r="R134" s="144"/>
-      <c r="S134" s="145" t="s">
+      <c r="R134" s="145"/>
+      <c r="S134" s="146" t="s">
         <v>354</v>
       </c>
-      <c r="T134" s="145"/>
+      <c r="T134" s="146"/>
       <c r="U134" s="141">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -9643,16 +9647,16 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W134" s="142"/>
+      <c r="W134" s="143"/>
       <c r="X134" s="141"/>
-      <c r="Y134" s="141"/>
+      <c r="Y134" s="142"/>
       <c r="Z134" s="141"/>
-      <c r="AA134" s="146"/>
-      <c r="AB134" s="141"/>
+      <c r="AA134" s="147"/>
+      <c r="AB134" s="142"/>
       <c r="AC134" s="141"/>
       <c r="AD134" s="141"/>
-      <c r="AE134" s="150"/>
-      <c r="AF134" s="148"/>
+      <c r="AE134" s="151"/>
+      <c r="AF134" s="149"/>
     </row>
     <row r="135" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A135" s="141" t="s">
@@ -9666,19 +9670,19 @@
       </c>
       <c r="D135" s="141"/>
       <c r="E135" s="141"/>
-      <c r="F135" s="141">
+      <c r="F135" s="142">
         <f>E135/2500</f>
         <v>0</v>
       </c>
-      <c r="G135" s="141"/>
-      <c r="H135" s="142" t="s">
+      <c r="G135" s="142"/>
+      <c r="H135" s="143" t="s">
         <v>194</v>
       </c>
-      <c r="I135" s="142" t="s">
+      <c r="I135" s="143" t="s">
         <v>357</v>
       </c>
-      <c r="J135" s="153"/>
-      <c r="K135" s="141">
+      <c r="J135" s="154"/>
+      <c r="K135" s="142">
         <f>J135/300</f>
         <v>0</v>
       </c>
@@ -9687,24 +9691,24 @@
       </c>
       <c r="M135" s="141"/>
       <c r="N135" s="141"/>
-      <c r="O135" s="148"/>
-      <c r="P135" s="148"/>
-      <c r="Q135" s="148"/>
-      <c r="R135" s="148"/>
-      <c r="S135" s="148"/>
-      <c r="T135" s="148"/>
-      <c r="U135" s="148"/>
-      <c r="V135" s="148"/>
-      <c r="W135" s="148"/>
-      <c r="X135" s="148"/>
-      <c r="Y135" s="148"/>
-      <c r="Z135" s="148"/>
-      <c r="AA135" s="148"/>
-      <c r="AB135" s="148"/>
-      <c r="AC135" s="148"/>
-      <c r="AD135" s="148"/>
-      <c r="AE135" s="148"/>
-      <c r="AF135" s="148"/>
+      <c r="O135" s="149"/>
+      <c r="P135" s="149"/>
+      <c r="Q135" s="149"/>
+      <c r="R135" s="149"/>
+      <c r="S135" s="149"/>
+      <c r="T135" s="149"/>
+      <c r="U135" s="149"/>
+      <c r="V135" s="149"/>
+      <c r="W135" s="149"/>
+      <c r="X135" s="149"/>
+      <c r="Y135" s="149"/>
+      <c r="Z135" s="149"/>
+      <c r="AA135" s="149"/>
+      <c r="AB135" s="149"/>
+      <c r="AC135" s="149"/>
+      <c r="AD135" s="149"/>
+      <c r="AE135" s="149"/>
+      <c r="AF135" s="149"/>
     </row>
     <row r="136" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A136" s="141"/>
@@ -9712,33 +9716,33 @@
       <c r="C136" s="141"/>
       <c r="D136" s="141"/>
       <c r="E136" s="141"/>
-      <c r="F136" s="141"/>
-      <c r="G136" s="141"/>
-      <c r="H136" s="142"/>
-      <c r="I136" s="142"/>
-      <c r="J136" s="153"/>
-      <c r="K136" s="141"/>
+      <c r="F136" s="142"/>
+      <c r="G136" s="142"/>
+      <c r="H136" s="143"/>
+      <c r="I136" s="143"/>
+      <c r="J136" s="154"/>
+      <c r="K136" s="142"/>
       <c r="L136" s="141"/>
       <c r="M136" s="141"/>
       <c r="N136" s="141"/>
-      <c r="O136" s="148"/>
-      <c r="P136" s="148"/>
-      <c r="Q136" s="148"/>
-      <c r="R136" s="148"/>
-      <c r="S136" s="148"/>
-      <c r="T136" s="148"/>
-      <c r="U136" s="148"/>
-      <c r="V136" s="148"/>
-      <c r="W136" s="148"/>
-      <c r="X136" s="148"/>
-      <c r="Y136" s="148"/>
-      <c r="Z136" s="148"/>
-      <c r="AA136" s="148"/>
-      <c r="AB136" s="148"/>
-      <c r="AC136" s="148"/>
-      <c r="AD136" s="148"/>
-      <c r="AE136" s="148"/>
-      <c r="AF136" s="148"/>
+      <c r="O136" s="149"/>
+      <c r="P136" s="149"/>
+      <c r="Q136" s="149"/>
+      <c r="R136" s="149"/>
+      <c r="S136" s="149"/>
+      <c r="T136" s="149"/>
+      <c r="U136" s="149"/>
+      <c r="V136" s="149"/>
+      <c r="W136" s="149"/>
+      <c r="X136" s="149"/>
+      <c r="Y136" s="149"/>
+      <c r="Z136" s="149"/>
+      <c r="AA136" s="149"/>
+      <c r="AB136" s="149"/>
+      <c r="AC136" s="149"/>
+      <c r="AD136" s="149"/>
+      <c r="AE136" s="149"/>
+      <c r="AF136" s="149"/>
     </row>
     <row r="137" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A137" s="141"/>
@@ -9746,33 +9750,33 @@
       <c r="C137" s="141"/>
       <c r="D137" s="141"/>
       <c r="E137" s="141"/>
-      <c r="F137" s="141"/>
-      <c r="G137" s="141"/>
-      <c r="H137" s="142"/>
-      <c r="I137" s="142"/>
-      <c r="J137" s="153"/>
-      <c r="K137" s="141"/>
+      <c r="F137" s="142"/>
+      <c r="G137" s="142"/>
+      <c r="H137" s="143"/>
+      <c r="I137" s="143"/>
+      <c r="J137" s="154"/>
+      <c r="K137" s="142"/>
       <c r="L137" s="141"/>
       <c r="M137" s="141"/>
       <c r="N137" s="141"/>
-      <c r="O137" s="148"/>
-      <c r="P137" s="148"/>
-      <c r="Q137" s="148"/>
-      <c r="R137" s="148"/>
-      <c r="S137" s="148"/>
-      <c r="T137" s="148"/>
-      <c r="U137" s="148"/>
-      <c r="V137" s="148"/>
-      <c r="W137" s="148"/>
-      <c r="X137" s="148"/>
-      <c r="Y137" s="148"/>
-      <c r="Z137" s="148"/>
-      <c r="AA137" s="148"/>
-      <c r="AB137" s="148"/>
-      <c r="AC137" s="148"/>
-      <c r="AD137" s="148"/>
-      <c r="AE137" s="148"/>
-      <c r="AF137" s="148"/>
+      <c r="O137" s="149"/>
+      <c r="P137" s="149"/>
+      <c r="Q137" s="149"/>
+      <c r="R137" s="149"/>
+      <c r="S137" s="149"/>
+      <c r="T137" s="149"/>
+      <c r="U137" s="149"/>
+      <c r="V137" s="149"/>
+      <c r="W137" s="149"/>
+      <c r="X137" s="149"/>
+      <c r="Y137" s="149"/>
+      <c r="Z137" s="149"/>
+      <c r="AA137" s="149"/>
+      <c r="AB137" s="149"/>
+      <c r="AC137" s="149"/>
+      <c r="AD137" s="149"/>
+      <c r="AE137" s="149"/>
+      <c r="AF137" s="149"/>
     </row>
     <row r="138" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A138" s="141"/>
@@ -9780,33 +9784,33 @@
       <c r="C138" s="141"/>
       <c r="D138" s="141"/>
       <c r="E138" s="141"/>
-      <c r="F138" s="141"/>
-      <c r="G138" s="141"/>
-      <c r="H138" s="142"/>
-      <c r="I138" s="142"/>
-      <c r="J138" s="153"/>
-      <c r="K138" s="141"/>
+      <c r="F138" s="142"/>
+      <c r="G138" s="142"/>
+      <c r="H138" s="143"/>
+      <c r="I138" s="143"/>
+      <c r="J138" s="154"/>
+      <c r="K138" s="142"/>
       <c r="L138" s="141"/>
       <c r="M138" s="141"/>
       <c r="N138" s="141"/>
-      <c r="O138" s="148"/>
-      <c r="P138" s="148"/>
-      <c r="Q138" s="148"/>
-      <c r="R138" s="148"/>
-      <c r="S138" s="148"/>
-      <c r="T138" s="148"/>
-      <c r="U138" s="148"/>
-      <c r="V138" s="148"/>
-      <c r="W138" s="148"/>
-      <c r="X138" s="148"/>
-      <c r="Y138" s="148"/>
-      <c r="Z138" s="148"/>
-      <c r="AA138" s="148"/>
-      <c r="AB138" s="148"/>
-      <c r="AC138" s="148"/>
-      <c r="AD138" s="148"/>
-      <c r="AE138" s="148"/>
-      <c r="AF138" s="148"/>
+      <c r="O138" s="149"/>
+      <c r="P138" s="149"/>
+      <c r="Q138" s="149"/>
+      <c r="R138" s="149"/>
+      <c r="S138" s="149"/>
+      <c r="T138" s="149"/>
+      <c r="U138" s="149"/>
+      <c r="V138" s="149"/>
+      <c r="W138" s="149"/>
+      <c r="X138" s="149"/>
+      <c r="Y138" s="149"/>
+      <c r="Z138" s="149"/>
+      <c r="AA138" s="149"/>
+      <c r="AB138" s="149"/>
+      <c r="AC138" s="149"/>
+      <c r="AD138" s="149"/>
+      <c r="AE138" s="149"/>
+      <c r="AF138" s="149"/>
     </row>
     <row r="139" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A139" s="141"/>
@@ -9814,33 +9818,33 @@
       <c r="C139" s="141"/>
       <c r="D139" s="141"/>
       <c r="E139" s="141"/>
-      <c r="F139" s="141"/>
-      <c r="G139" s="141"/>
-      <c r="H139" s="142"/>
-      <c r="I139" s="142"/>
-      <c r="J139" s="153"/>
-      <c r="K139" s="141"/>
+      <c r="F139" s="142"/>
+      <c r="G139" s="142"/>
+      <c r="H139" s="143"/>
+      <c r="I139" s="143"/>
+      <c r="J139" s="154"/>
+      <c r="K139" s="142"/>
       <c r="L139" s="141"/>
       <c r="M139" s="141"/>
       <c r="N139" s="141"/>
-      <c r="O139" s="148"/>
-      <c r="P139" s="148"/>
-      <c r="Q139" s="148"/>
-      <c r="R139" s="148"/>
-      <c r="S139" s="148"/>
-      <c r="T139" s="148"/>
-      <c r="U139" s="148"/>
-      <c r="V139" s="148"/>
-      <c r="W139" s="148"/>
-      <c r="X139" s="148"/>
-      <c r="Y139" s="148"/>
-      <c r="Z139" s="148"/>
-      <c r="AA139" s="148"/>
-      <c r="AB139" s="148"/>
-      <c r="AC139" s="148"/>
-      <c r="AD139" s="148"/>
-      <c r="AE139" s="148"/>
-      <c r="AF139" s="148"/>
+      <c r="O139" s="149"/>
+      <c r="P139" s="149"/>
+      <c r="Q139" s="149"/>
+      <c r="R139" s="149"/>
+      <c r="S139" s="149"/>
+      <c r="T139" s="149"/>
+      <c r="U139" s="149"/>
+      <c r="V139" s="149"/>
+      <c r="W139" s="149"/>
+      <c r="X139" s="149"/>
+      <c r="Y139" s="149"/>
+      <c r="Z139" s="149"/>
+      <c r="AA139" s="149"/>
+      <c r="AB139" s="149"/>
+      <c r="AC139" s="149"/>
+      <c r="AD139" s="149"/>
+      <c r="AE139" s="149"/>
+      <c r="AF139" s="149"/>
     </row>
     <row r="140" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A140" s="141"/>
@@ -9852,43 +9856,43 @@
       </c>
       <c r="D140" s="141"/>
       <c r="E140" s="141"/>
-      <c r="F140" s="141">
+      <c r="F140" s="142">
         <f>E140/2500</f>
         <v>0</v>
       </c>
-      <c r="G140" s="141"/>
-      <c r="H140" s="142" t="s">
+      <c r="G140" s="142"/>
+      <c r="H140" s="143" t="s">
         <v>194</v>
       </c>
-      <c r="I140" s="142" t="s">
+      <c r="I140" s="143" t="s">
         <v>359</v>
       </c>
       <c r="J140" s="141"/>
-      <c r="K140" s="141">
+      <c r="K140" s="142">
         <f>J140/400</f>
         <v>0</v>
       </c>
       <c r="L140" s="141"/>
       <c r="M140" s="141"/>
       <c r="N140" s="141"/>
-      <c r="O140" s="148"/>
-      <c r="P140" s="148"/>
-      <c r="Q140" s="148"/>
-      <c r="R140" s="148"/>
-      <c r="S140" s="148"/>
-      <c r="T140" s="148"/>
-      <c r="U140" s="148"/>
-      <c r="V140" s="148"/>
-      <c r="W140" s="148"/>
-      <c r="X140" s="148"/>
-      <c r="Y140" s="148"/>
-      <c r="Z140" s="148"/>
-      <c r="AA140" s="148"/>
-      <c r="AB140" s="148"/>
-      <c r="AC140" s="148"/>
-      <c r="AD140" s="148"/>
-      <c r="AE140" s="148"/>
-      <c r="AF140" s="148"/>
+      <c r="O140" s="149"/>
+      <c r="P140" s="149"/>
+      <c r="Q140" s="149"/>
+      <c r="R140" s="149"/>
+      <c r="S140" s="149"/>
+      <c r="T140" s="149"/>
+      <c r="U140" s="149"/>
+      <c r="V140" s="149"/>
+      <c r="W140" s="149"/>
+      <c r="X140" s="149"/>
+      <c r="Y140" s="149"/>
+      <c r="Z140" s="149"/>
+      <c r="AA140" s="149"/>
+      <c r="AB140" s="149"/>
+      <c r="AC140" s="149"/>
+      <c r="AD140" s="149"/>
+      <c r="AE140" s="149"/>
+      <c r="AF140" s="149"/>
     </row>
     <row r="141" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A141" s="141"/>
@@ -9896,33 +9900,33 @@
       <c r="C141" s="141"/>
       <c r="D141" s="141"/>
       <c r="E141" s="141"/>
-      <c r="F141" s="141"/>
-      <c r="G141" s="141"/>
-      <c r="H141" s="142"/>
-      <c r="I141" s="142"/>
+      <c r="F141" s="142"/>
+      <c r="G141" s="142"/>
+      <c r="H141" s="143"/>
+      <c r="I141" s="143"/>
       <c r="J141" s="141"/>
-      <c r="K141" s="141"/>
+      <c r="K141" s="142"/>
       <c r="L141" s="141"/>
       <c r="M141" s="141"/>
       <c r="N141" s="141"/>
-      <c r="O141" s="148"/>
-      <c r="P141" s="148"/>
-      <c r="Q141" s="148"/>
-      <c r="R141" s="148"/>
-      <c r="S141" s="148"/>
-      <c r="T141" s="148"/>
-      <c r="U141" s="148"/>
-      <c r="V141" s="148"/>
-      <c r="W141" s="148"/>
-      <c r="X141" s="148"/>
-      <c r="Y141" s="148"/>
-      <c r="Z141" s="148"/>
-      <c r="AA141" s="148"/>
-      <c r="AB141" s="148"/>
-      <c r="AC141" s="148"/>
-      <c r="AD141" s="148"/>
-      <c r="AE141" s="148"/>
-      <c r="AF141" s="148"/>
+      <c r="O141" s="149"/>
+      <c r="P141" s="149"/>
+      <c r="Q141" s="149"/>
+      <c r="R141" s="149"/>
+      <c r="S141" s="149"/>
+      <c r="T141" s="149"/>
+      <c r="U141" s="149"/>
+      <c r="V141" s="149"/>
+      <c r="W141" s="149"/>
+      <c r="X141" s="149"/>
+      <c r="Y141" s="149"/>
+      <c r="Z141" s="149"/>
+      <c r="AA141" s="149"/>
+      <c r="AB141" s="149"/>
+      <c r="AC141" s="149"/>
+      <c r="AD141" s="149"/>
+      <c r="AE141" s="149"/>
+      <c r="AF141" s="149"/>
     </row>
     <row r="142" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A142" s="141"/>
@@ -9930,33 +9934,33 @@
       <c r="C142" s="141"/>
       <c r="D142" s="141"/>
       <c r="E142" s="141"/>
-      <c r="F142" s="141"/>
-      <c r="G142" s="141"/>
-      <c r="H142" s="142"/>
-      <c r="I142" s="142"/>
+      <c r="F142" s="142"/>
+      <c r="G142" s="142"/>
+      <c r="H142" s="143"/>
+      <c r="I142" s="143"/>
       <c r="J142" s="141"/>
-      <c r="K142" s="141"/>
+      <c r="K142" s="142"/>
       <c r="L142" s="141"/>
       <c r="M142" s="141"/>
       <c r="N142" s="141"/>
-      <c r="O142" s="148"/>
-      <c r="P142" s="148"/>
-      <c r="Q142" s="148"/>
-      <c r="R142" s="148"/>
-      <c r="S142" s="148"/>
-      <c r="T142" s="148"/>
-      <c r="U142" s="148"/>
-      <c r="V142" s="148"/>
-      <c r="W142" s="148"/>
-      <c r="X142" s="148"/>
-      <c r="Y142" s="148"/>
-      <c r="Z142" s="148"/>
-      <c r="AA142" s="148"/>
-      <c r="AB142" s="148"/>
-      <c r="AC142" s="148"/>
-      <c r="AD142" s="148"/>
-      <c r="AE142" s="148"/>
-      <c r="AF142" s="148"/>
+      <c r="O142" s="149"/>
+      <c r="P142" s="149"/>
+      <c r="Q142" s="149"/>
+      <c r="R142" s="149"/>
+      <c r="S142" s="149"/>
+      <c r="T142" s="149"/>
+      <c r="U142" s="149"/>
+      <c r="V142" s="149"/>
+      <c r="W142" s="149"/>
+      <c r="X142" s="149"/>
+      <c r="Y142" s="149"/>
+      <c r="Z142" s="149"/>
+      <c r="AA142" s="149"/>
+      <c r="AB142" s="149"/>
+      <c r="AC142" s="149"/>
+      <c r="AD142" s="149"/>
+      <c r="AE142" s="149"/>
+      <c r="AF142" s="149"/>
     </row>
     <row r="143" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A143" s="141"/>
@@ -9964,33 +9968,33 @@
       <c r="C143" s="141"/>
       <c r="D143" s="141"/>
       <c r="E143" s="141"/>
-      <c r="F143" s="141"/>
-      <c r="G143" s="141"/>
-      <c r="H143" s="142"/>
-      <c r="I143" s="142"/>
+      <c r="F143" s="142"/>
+      <c r="G143" s="142"/>
+      <c r="H143" s="143"/>
+      <c r="I143" s="143"/>
       <c r="J143" s="141"/>
-      <c r="K143" s="141"/>
+      <c r="K143" s="142"/>
       <c r="L143" s="141"/>
       <c r="M143" s="141"/>
       <c r="N143" s="141"/>
-      <c r="O143" s="148"/>
-      <c r="P143" s="148"/>
-      <c r="Q143" s="148"/>
-      <c r="R143" s="148"/>
-      <c r="S143" s="148"/>
-      <c r="T143" s="148"/>
-      <c r="U143" s="148"/>
-      <c r="V143" s="148"/>
-      <c r="W143" s="148"/>
-      <c r="X143" s="148"/>
-      <c r="Y143" s="148"/>
-      <c r="Z143" s="148"/>
-      <c r="AA143" s="148"/>
-      <c r="AB143" s="148"/>
-      <c r="AC143" s="148"/>
-      <c r="AD143" s="148"/>
-      <c r="AE143" s="148"/>
-      <c r="AF143" s="148"/>
+      <c r="O143" s="149"/>
+      <c r="P143" s="149"/>
+      <c r="Q143" s="149"/>
+      <c r="R143" s="149"/>
+      <c r="S143" s="149"/>
+      <c r="T143" s="149"/>
+      <c r="U143" s="149"/>
+      <c r="V143" s="149"/>
+      <c r="W143" s="149"/>
+      <c r="X143" s="149"/>
+      <c r="Y143" s="149"/>
+      <c r="Z143" s="149"/>
+      <c r="AA143" s="149"/>
+      <c r="AB143" s="149"/>
+      <c r="AC143" s="149"/>
+      <c r="AD143" s="149"/>
+      <c r="AE143" s="149"/>
+      <c r="AF143" s="149"/>
     </row>
     <row r="144" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A144" s="141"/>
@@ -9998,33 +10002,33 @@
       <c r="C144" s="141"/>
       <c r="D144" s="141"/>
       <c r="E144" s="141"/>
-      <c r="F144" s="141"/>
-      <c r="G144" s="141"/>
-      <c r="H144" s="142"/>
-      <c r="I144" s="142"/>
+      <c r="F144" s="142"/>
+      <c r="G144" s="142"/>
+      <c r="H144" s="143"/>
+      <c r="I144" s="143"/>
       <c r="J144" s="141"/>
-      <c r="K144" s="141"/>
+      <c r="K144" s="142"/>
       <c r="L144" s="141"/>
       <c r="M144" s="141"/>
       <c r="N144" s="141"/>
-      <c r="O144" s="148"/>
-      <c r="P144" s="148"/>
-      <c r="Q144" s="148"/>
-      <c r="R144" s="148"/>
-      <c r="S144" s="148"/>
-      <c r="T144" s="148"/>
-      <c r="U144" s="148"/>
-      <c r="V144" s="148"/>
-      <c r="W144" s="148"/>
-      <c r="X144" s="148"/>
-      <c r="Y144" s="148"/>
-      <c r="Z144" s="148"/>
-      <c r="AA144" s="148"/>
-      <c r="AB144" s="148"/>
-      <c r="AC144" s="148"/>
-      <c r="AD144" s="148"/>
-      <c r="AE144" s="148"/>
-      <c r="AF144" s="148"/>
+      <c r="O144" s="149"/>
+      <c r="P144" s="149"/>
+      <c r="Q144" s="149"/>
+      <c r="R144" s="149"/>
+      <c r="S144" s="149"/>
+      <c r="T144" s="149"/>
+      <c r="U144" s="149"/>
+      <c r="V144" s="149"/>
+      <c r="W144" s="149"/>
+      <c r="X144" s="149"/>
+      <c r="Y144" s="149"/>
+      <c r="Z144" s="149"/>
+      <c r="AA144" s="149"/>
+      <c r="AB144" s="149"/>
+      <c r="AC144" s="149"/>
+      <c r="AD144" s="149"/>
+      <c r="AE144" s="149"/>
+      <c r="AF144" s="149"/>
     </row>
     <row r="145" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A145" s="141" t="s">
@@ -10038,19 +10042,19 @@
       </c>
       <c r="D145" s="141"/>
       <c r="E145" s="141"/>
-      <c r="F145" s="141">
+      <c r="F145" s="142">
         <f>E145/2500</f>
         <v>0</v>
       </c>
-      <c r="G145" s="141"/>
-      <c r="H145" s="142" t="s">
+      <c r="G145" s="142"/>
+      <c r="H145" s="143" t="s">
         <v>194</v>
       </c>
-      <c r="I145" s="142" t="s">
+      <c r="I145" s="143" t="s">
         <v>362</v>
       </c>
       <c r="J145" s="141"/>
-      <c r="K145" s="141">
+      <c r="K145" s="142">
         <f>J145/300</f>
         <v>0</v>
       </c>
@@ -10059,24 +10063,24 @@
       </c>
       <c r="M145" s="141"/>
       <c r="N145" s="141"/>
-      <c r="O145" s="148"/>
-      <c r="P145" s="148"/>
-      <c r="Q145" s="148"/>
-      <c r="R145" s="148"/>
-      <c r="S145" s="148"/>
-      <c r="T145" s="148"/>
-      <c r="U145" s="148"/>
-      <c r="V145" s="148"/>
-      <c r="W145" s="148"/>
-      <c r="X145" s="148"/>
-      <c r="Y145" s="148"/>
-      <c r="Z145" s="148"/>
-      <c r="AA145" s="148"/>
-      <c r="AB145" s="148"/>
-      <c r="AC145" s="148"/>
-      <c r="AD145" s="148"/>
-      <c r="AE145" s="148"/>
-      <c r="AF145" s="148"/>
+      <c r="O145" s="149"/>
+      <c r="P145" s="149"/>
+      <c r="Q145" s="149"/>
+      <c r="R145" s="149"/>
+      <c r="S145" s="149"/>
+      <c r="T145" s="149"/>
+      <c r="U145" s="149"/>
+      <c r="V145" s="149"/>
+      <c r="W145" s="149"/>
+      <c r="X145" s="149"/>
+      <c r="Y145" s="149"/>
+      <c r="Z145" s="149"/>
+      <c r="AA145" s="149"/>
+      <c r="AB145" s="149"/>
+      <c r="AC145" s="149"/>
+      <c r="AD145" s="149"/>
+      <c r="AE145" s="149"/>
+      <c r="AF145" s="149"/>
     </row>
     <row r="146" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A146" s="141"/>
@@ -10084,33 +10088,33 @@
       <c r="C146" s="141"/>
       <c r="D146" s="141"/>
       <c r="E146" s="141"/>
-      <c r="F146" s="141"/>
-      <c r="G146" s="141"/>
-      <c r="H146" s="142"/>
-      <c r="I146" s="142"/>
+      <c r="F146" s="142"/>
+      <c r="G146" s="142"/>
+      <c r="H146" s="143"/>
+      <c r="I146" s="143"/>
       <c r="J146" s="141"/>
-      <c r="K146" s="141"/>
+      <c r="K146" s="142"/>
       <c r="L146" s="141"/>
       <c r="M146" s="141"/>
       <c r="N146" s="141"/>
-      <c r="O146" s="148"/>
-      <c r="P146" s="148"/>
-      <c r="Q146" s="148"/>
-      <c r="R146" s="148"/>
-      <c r="S146" s="148"/>
-      <c r="T146" s="148"/>
-      <c r="U146" s="148"/>
-      <c r="V146" s="148"/>
-      <c r="W146" s="148"/>
-      <c r="X146" s="148"/>
-      <c r="Y146" s="148"/>
-      <c r="Z146" s="148"/>
-      <c r="AA146" s="148"/>
-      <c r="AB146" s="148"/>
-      <c r="AC146" s="148"/>
-      <c r="AD146" s="148"/>
-      <c r="AE146" s="148"/>
-      <c r="AF146" s="148"/>
+      <c r="O146" s="149"/>
+      <c r="P146" s="149"/>
+      <c r="Q146" s="149"/>
+      <c r="R146" s="149"/>
+      <c r="S146" s="149"/>
+      <c r="T146" s="149"/>
+      <c r="U146" s="149"/>
+      <c r="V146" s="149"/>
+      <c r="W146" s="149"/>
+      <c r="X146" s="149"/>
+      <c r="Y146" s="149"/>
+      <c r="Z146" s="149"/>
+      <c r="AA146" s="149"/>
+      <c r="AB146" s="149"/>
+      <c r="AC146" s="149"/>
+      <c r="AD146" s="149"/>
+      <c r="AE146" s="149"/>
+      <c r="AF146" s="149"/>
     </row>
     <row r="147" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A147" s="141"/>
@@ -10118,33 +10122,33 @@
       <c r="C147" s="141"/>
       <c r="D147" s="141"/>
       <c r="E147" s="141"/>
-      <c r="F147" s="141"/>
-      <c r="G147" s="141"/>
-      <c r="H147" s="142"/>
-      <c r="I147" s="142"/>
+      <c r="F147" s="142"/>
+      <c r="G147" s="142"/>
+      <c r="H147" s="143"/>
+      <c r="I147" s="143"/>
       <c r="J147" s="141"/>
-      <c r="K147" s="141"/>
+      <c r="K147" s="142"/>
       <c r="L147" s="141"/>
       <c r="M147" s="141"/>
       <c r="N147" s="141"/>
-      <c r="O147" s="148"/>
-      <c r="P147" s="148"/>
-      <c r="Q147" s="148"/>
-      <c r="R147" s="148"/>
-      <c r="S147" s="148"/>
-      <c r="T147" s="148"/>
-      <c r="U147" s="148"/>
-      <c r="V147" s="148"/>
-      <c r="W147" s="148"/>
-      <c r="X147" s="148"/>
-      <c r="Y147" s="148"/>
-      <c r="Z147" s="148"/>
-      <c r="AA147" s="148"/>
-      <c r="AB147" s="148"/>
-      <c r="AC147" s="148"/>
-      <c r="AD147" s="148"/>
-      <c r="AE147" s="148"/>
-      <c r="AF147" s="148"/>
+      <c r="O147" s="149"/>
+      <c r="P147" s="149"/>
+      <c r="Q147" s="149"/>
+      <c r="R147" s="149"/>
+      <c r="S147" s="149"/>
+      <c r="T147" s="149"/>
+      <c r="U147" s="149"/>
+      <c r="V147" s="149"/>
+      <c r="W147" s="149"/>
+      <c r="X147" s="149"/>
+      <c r="Y147" s="149"/>
+      <c r="Z147" s="149"/>
+      <c r="AA147" s="149"/>
+      <c r="AB147" s="149"/>
+      <c r="AC147" s="149"/>
+      <c r="AD147" s="149"/>
+      <c r="AE147" s="149"/>
+      <c r="AF147" s="149"/>
     </row>
     <row r="148" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A148" s="141"/>
@@ -10152,33 +10156,33 @@
       <c r="C148" s="141"/>
       <c r="D148" s="141"/>
       <c r="E148" s="141"/>
-      <c r="F148" s="141"/>
-      <c r="G148" s="141"/>
-      <c r="H148" s="142"/>
-      <c r="I148" s="142"/>
+      <c r="F148" s="142"/>
+      <c r="G148" s="142"/>
+      <c r="H148" s="143"/>
+      <c r="I148" s="143"/>
       <c r="J148" s="141"/>
-      <c r="K148" s="141"/>
+      <c r="K148" s="142"/>
       <c r="L148" s="141"/>
       <c r="M148" s="141"/>
       <c r="N148" s="141"/>
-      <c r="O148" s="148"/>
-      <c r="P148" s="148"/>
-      <c r="Q148" s="148"/>
-      <c r="R148" s="148"/>
-      <c r="S148" s="148"/>
-      <c r="T148" s="148"/>
-      <c r="U148" s="148"/>
-      <c r="V148" s="148"/>
-      <c r="W148" s="148"/>
-      <c r="X148" s="148"/>
-      <c r="Y148" s="148"/>
-      <c r="Z148" s="148"/>
-      <c r="AA148" s="148"/>
-      <c r="AB148" s="148"/>
-      <c r="AC148" s="148"/>
-      <c r="AD148" s="148"/>
-      <c r="AE148" s="148"/>
-      <c r="AF148" s="148"/>
+      <c r="O148" s="149"/>
+      <c r="P148" s="149"/>
+      <c r="Q148" s="149"/>
+      <c r="R148" s="149"/>
+      <c r="S148" s="149"/>
+      <c r="T148" s="149"/>
+      <c r="U148" s="149"/>
+      <c r="V148" s="149"/>
+      <c r="W148" s="149"/>
+      <c r="X148" s="149"/>
+      <c r="Y148" s="149"/>
+      <c r="Z148" s="149"/>
+      <c r="AA148" s="149"/>
+      <c r="AB148" s="149"/>
+      <c r="AC148" s="149"/>
+      <c r="AD148" s="149"/>
+      <c r="AE148" s="149"/>
+      <c r="AF148" s="149"/>
     </row>
     <row r="149" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A149" s="141"/>
@@ -10186,33 +10190,33 @@
       <c r="C149" s="141"/>
       <c r="D149" s="141"/>
       <c r="E149" s="141"/>
-      <c r="F149" s="141"/>
-      <c r="G149" s="141"/>
-      <c r="H149" s="142"/>
-      <c r="I149" s="142"/>
+      <c r="F149" s="142"/>
+      <c r="G149" s="142"/>
+      <c r="H149" s="143"/>
+      <c r="I149" s="143"/>
       <c r="J149" s="141"/>
-      <c r="K149" s="141"/>
+      <c r="K149" s="142"/>
       <c r="L149" s="141"/>
       <c r="M149" s="141"/>
       <c r="N149" s="141"/>
-      <c r="O149" s="148"/>
-      <c r="P149" s="148"/>
-      <c r="Q149" s="148"/>
-      <c r="R149" s="148"/>
-      <c r="S149" s="148"/>
-      <c r="T149" s="148"/>
-      <c r="U149" s="148"/>
-      <c r="V149" s="148"/>
-      <c r="W149" s="148"/>
-      <c r="X149" s="148"/>
-      <c r="Y149" s="148"/>
-      <c r="Z149" s="148"/>
-      <c r="AA149" s="148"/>
-      <c r="AB149" s="148"/>
-      <c r="AC149" s="148"/>
-      <c r="AD149" s="148"/>
-      <c r="AE149" s="148"/>
-      <c r="AF149" s="148"/>
+      <c r="O149" s="149"/>
+      <c r="P149" s="149"/>
+      <c r="Q149" s="149"/>
+      <c r="R149" s="149"/>
+      <c r="S149" s="149"/>
+      <c r="T149" s="149"/>
+      <c r="U149" s="149"/>
+      <c r="V149" s="149"/>
+      <c r="W149" s="149"/>
+      <c r="X149" s="149"/>
+      <c r="Y149" s="149"/>
+      <c r="Z149" s="149"/>
+      <c r="AA149" s="149"/>
+      <c r="AB149" s="149"/>
+      <c r="AC149" s="149"/>
+      <c r="AD149" s="149"/>
+      <c r="AE149" s="149"/>
+      <c r="AF149" s="149"/>
     </row>
     <row r="150" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A150" s="141"/>
@@ -10224,43 +10228,43 @@
       </c>
       <c r="D150" s="141"/>
       <c r="E150" s="141"/>
-      <c r="F150" s="141">
+      <c r="F150" s="142">
         <f>E150/2500</f>
         <v>0</v>
       </c>
-      <c r="G150" s="141"/>
-      <c r="H150" s="142" t="s">
+      <c r="G150" s="142"/>
+      <c r="H150" s="143" t="s">
         <v>194</v>
       </c>
-      <c r="I150" s="142" t="s">
+      <c r="I150" s="143" t="s">
         <v>364</v>
       </c>
       <c r="J150" s="141"/>
-      <c r="K150" s="141">
+      <c r="K150" s="142">
         <f>J150/400</f>
         <v>0</v>
       </c>
       <c r="L150" s="141"/>
       <c r="M150" s="141"/>
       <c r="N150" s="141"/>
-      <c r="O150" s="148"/>
-      <c r="P150" s="148"/>
-      <c r="Q150" s="148"/>
-      <c r="R150" s="148"/>
-      <c r="S150" s="148"/>
-      <c r="T150" s="148"/>
-      <c r="U150" s="148"/>
-      <c r="V150" s="148"/>
-      <c r="W150" s="148"/>
-      <c r="X150" s="148"/>
-      <c r="Y150" s="148"/>
-      <c r="Z150" s="148"/>
-      <c r="AA150" s="148"/>
-      <c r="AB150" s="148"/>
-      <c r="AC150" s="148"/>
-      <c r="AD150" s="148"/>
-      <c r="AE150" s="148"/>
-      <c r="AF150" s="148"/>
+      <c r="O150" s="149"/>
+      <c r="P150" s="149"/>
+      <c r="Q150" s="149"/>
+      <c r="R150" s="149"/>
+      <c r="S150" s="149"/>
+      <c r="T150" s="149"/>
+      <c r="U150" s="149"/>
+      <c r="V150" s="149"/>
+      <c r="W150" s="149"/>
+      <c r="X150" s="149"/>
+      <c r="Y150" s="149"/>
+      <c r="Z150" s="149"/>
+      <c r="AA150" s="149"/>
+      <c r="AB150" s="149"/>
+      <c r="AC150" s="149"/>
+      <c r="AD150" s="149"/>
+      <c r="AE150" s="149"/>
+      <c r="AF150" s="149"/>
     </row>
     <row r="151" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A151" s="141"/>
@@ -10268,33 +10272,33 @@
       <c r="C151" s="141"/>
       <c r="D151" s="141"/>
       <c r="E151" s="141"/>
-      <c r="F151" s="141"/>
-      <c r="G151" s="141"/>
-      <c r="H151" s="142"/>
-      <c r="I151" s="142"/>
+      <c r="F151" s="142"/>
+      <c r="G151" s="142"/>
+      <c r="H151" s="143"/>
+      <c r="I151" s="143"/>
       <c r="J151" s="141"/>
-      <c r="K151" s="141"/>
+      <c r="K151" s="142"/>
       <c r="L151" s="141"/>
       <c r="M151" s="141"/>
       <c r="N151" s="141"/>
-      <c r="O151" s="148"/>
-      <c r="P151" s="148"/>
-      <c r="Q151" s="148"/>
-      <c r="R151" s="148"/>
-      <c r="S151" s="148"/>
-      <c r="T151" s="148"/>
-      <c r="U151" s="148"/>
-      <c r="V151" s="148"/>
-      <c r="W151" s="148"/>
-      <c r="X151" s="148"/>
-      <c r="Y151" s="148"/>
-      <c r="Z151" s="148"/>
-      <c r="AA151" s="148"/>
-      <c r="AB151" s="148"/>
-      <c r="AC151" s="148"/>
-      <c r="AD151" s="148"/>
-      <c r="AE151" s="148"/>
-      <c r="AF151" s="148"/>
+      <c r="O151" s="149"/>
+      <c r="P151" s="149"/>
+      <c r="Q151" s="149"/>
+      <c r="R151" s="149"/>
+      <c r="S151" s="149"/>
+      <c r="T151" s="149"/>
+      <c r="U151" s="149"/>
+      <c r="V151" s="149"/>
+      <c r="W151" s="149"/>
+      <c r="X151" s="149"/>
+      <c r="Y151" s="149"/>
+      <c r="Z151" s="149"/>
+      <c r="AA151" s="149"/>
+      <c r="AB151" s="149"/>
+      <c r="AC151" s="149"/>
+      <c r="AD151" s="149"/>
+      <c r="AE151" s="149"/>
+      <c r="AF151" s="149"/>
     </row>
     <row r="152" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A152" s="141"/>
@@ -10302,33 +10306,33 @@
       <c r="C152" s="141"/>
       <c r="D152" s="141"/>
       <c r="E152" s="141"/>
-      <c r="F152" s="141"/>
-      <c r="G152" s="141"/>
-      <c r="H152" s="142"/>
-      <c r="I152" s="142"/>
+      <c r="F152" s="142"/>
+      <c r="G152" s="142"/>
+      <c r="H152" s="143"/>
+      <c r="I152" s="143"/>
       <c r="J152" s="141"/>
-      <c r="K152" s="141"/>
+      <c r="K152" s="142"/>
       <c r="L152" s="141"/>
       <c r="M152" s="141"/>
       <c r="N152" s="141"/>
-      <c r="O152" s="148"/>
-      <c r="P152" s="148"/>
-      <c r="Q152" s="148"/>
-      <c r="R152" s="148"/>
-      <c r="S152" s="148"/>
-      <c r="T152" s="148"/>
-      <c r="U152" s="148"/>
-      <c r="V152" s="148"/>
-      <c r="W152" s="148"/>
-      <c r="X152" s="148"/>
-      <c r="Y152" s="148"/>
-      <c r="Z152" s="148"/>
-      <c r="AA152" s="148"/>
-      <c r="AB152" s="148"/>
-      <c r="AC152" s="148"/>
-      <c r="AD152" s="148"/>
-      <c r="AE152" s="148"/>
-      <c r="AF152" s="148"/>
+      <c r="O152" s="149"/>
+      <c r="P152" s="149"/>
+      <c r="Q152" s="149"/>
+      <c r="R152" s="149"/>
+      <c r="S152" s="149"/>
+      <c r="T152" s="149"/>
+      <c r="U152" s="149"/>
+      <c r="V152" s="149"/>
+      <c r="W152" s="149"/>
+      <c r="X152" s="149"/>
+      <c r="Y152" s="149"/>
+      <c r="Z152" s="149"/>
+      <c r="AA152" s="149"/>
+      <c r="AB152" s="149"/>
+      <c r="AC152" s="149"/>
+      <c r="AD152" s="149"/>
+      <c r="AE152" s="149"/>
+      <c r="AF152" s="149"/>
     </row>
     <row r="153" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A153" s="141"/>
@@ -10336,33 +10340,33 @@
       <c r="C153" s="141"/>
       <c r="D153" s="141"/>
       <c r="E153" s="141"/>
-      <c r="F153" s="141"/>
-      <c r="G153" s="141"/>
-      <c r="H153" s="142"/>
-      <c r="I153" s="142"/>
+      <c r="F153" s="142"/>
+      <c r="G153" s="142"/>
+      <c r="H153" s="143"/>
+      <c r="I153" s="143"/>
       <c r="J153" s="141"/>
-      <c r="K153" s="141"/>
+      <c r="K153" s="142"/>
       <c r="L153" s="141"/>
       <c r="M153" s="141"/>
       <c r="N153" s="141"/>
-      <c r="O153" s="148"/>
-      <c r="P153" s="148"/>
-      <c r="Q153" s="148"/>
-      <c r="R153" s="148"/>
-      <c r="S153" s="148"/>
-      <c r="T153" s="148"/>
-      <c r="U153" s="148"/>
-      <c r="V153" s="148"/>
-      <c r="W153" s="148"/>
-      <c r="X153" s="148"/>
-      <c r="Y153" s="148"/>
-      <c r="Z153" s="148"/>
-      <c r="AA153" s="148"/>
-      <c r="AB153" s="148"/>
-      <c r="AC153" s="148"/>
-      <c r="AD153" s="148"/>
-      <c r="AE153" s="148"/>
-      <c r="AF153" s="148"/>
+      <c r="O153" s="149"/>
+      <c r="P153" s="149"/>
+      <c r="Q153" s="149"/>
+      <c r="R153" s="149"/>
+      <c r="S153" s="149"/>
+      <c r="T153" s="149"/>
+      <c r="U153" s="149"/>
+      <c r="V153" s="149"/>
+      <c r="W153" s="149"/>
+      <c r="X153" s="149"/>
+      <c r="Y153" s="149"/>
+      <c r="Z153" s="149"/>
+      <c r="AA153" s="149"/>
+      <c r="AB153" s="149"/>
+      <c r="AC153" s="149"/>
+      <c r="AD153" s="149"/>
+      <c r="AE153" s="149"/>
+      <c r="AF153" s="149"/>
     </row>
     <row r="154" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A154" s="141"/>
@@ -10370,33 +10374,33 @@
       <c r="C154" s="141"/>
       <c r="D154" s="141"/>
       <c r="E154" s="141"/>
-      <c r="F154" s="141"/>
-      <c r="G154" s="141"/>
-      <c r="H154" s="142"/>
-      <c r="I154" s="142"/>
+      <c r="F154" s="142"/>
+      <c r="G154" s="142"/>
+      <c r="H154" s="143"/>
+      <c r="I154" s="143"/>
       <c r="J154" s="141"/>
-      <c r="K154" s="141"/>
+      <c r="K154" s="142"/>
       <c r="L154" s="141"/>
       <c r="M154" s="141"/>
       <c r="N154" s="141"/>
-      <c r="O154" s="148"/>
-      <c r="P154" s="148"/>
-      <c r="Q154" s="148"/>
-      <c r="R154" s="148"/>
-      <c r="S154" s="148"/>
-      <c r="T154" s="148"/>
-      <c r="U154" s="148"/>
-      <c r="V154" s="148"/>
-      <c r="W154" s="148"/>
-      <c r="X154" s="148"/>
-      <c r="Y154" s="148"/>
-      <c r="Z154" s="148"/>
-      <c r="AA154" s="148"/>
-      <c r="AB154" s="148"/>
-      <c r="AC154" s="148"/>
-      <c r="AD154" s="148"/>
-      <c r="AE154" s="148"/>
-      <c r="AF154" s="148"/>
+      <c r="O154" s="149"/>
+      <c r="P154" s="149"/>
+      <c r="Q154" s="149"/>
+      <c r="R154" s="149"/>
+      <c r="S154" s="149"/>
+      <c r="T154" s="149"/>
+      <c r="U154" s="149"/>
+      <c r="V154" s="149"/>
+      <c r="W154" s="149"/>
+      <c r="X154" s="149"/>
+      <c r="Y154" s="149"/>
+      <c r="Z154" s="149"/>
+      <c r="AA154" s="149"/>
+      <c r="AB154" s="149"/>
+      <c r="AC154" s="149"/>
+      <c r="AD154" s="149"/>
+      <c r="AE154" s="149"/>
+      <c r="AF154" s="149"/>
     </row>
   </sheetData>
   <protectedRanges>
@@ -11086,7 +11090,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b5bdb37c-304d-45b0-9ead-82cf4b1e18ba}</x14:id>
+          <x14:id>{d26b6506-af02-4c3e-abd8-c960452e00fd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11098,7 +11102,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{70cac10c-c36d-4e1d-a2c5-c516e8f5755e}</x14:id>
+          <x14:id>{6f9b6945-1b12-42cc-a358-15fccc908496}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11110,7 +11114,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b6af8c4e-13f2-4703-88dc-cfed550de9c5}</x14:id>
+          <x14:id>{fbdf3d43-7e43-46d8-ba48-dfc08066ee32}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11122,7 +11126,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bee170fd-42b7-40df-9112-0529c3e8af7d}</x14:id>
+          <x14:id>{0a25df39-72f8-4de8-8b8e-aa779181855d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11134,7 +11138,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c5a833c9-4ce5-4980-ae7e-c11d14bbdc15}</x14:id>
+          <x14:id>{59f2dfec-c076-4ea3-b927-f22bf00d43fe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11146,7 +11150,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0553788b-7da1-45bd-a985-958155d938e9}</x14:id>
+          <x14:id>{eaff4522-b194-4d35-9268-cc6e8157ea8d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11158,7 +11162,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{114fcd61-28dc-4a3d-8bf2-4982fdfb1546}</x14:id>
+          <x14:id>{7d77bee7-6fd5-4381-acaf-738800090c26}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11170,7 +11174,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2f292e0e-71a0-4d17-8db6-3ac6c57e5318}</x14:id>
+          <x14:id>{4023263c-9333-4063-83f5-5b92623fd4b7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11184,7 +11188,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f06b5711-00b8-49b1-b0c4-77c1220dd65f}</x14:id>
+          <x14:id>{d1905c29-40d3-4efd-94f7-aa65a257254f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11196,7 +11200,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{965cd7c9-04c7-4320-8637-ec70834fa997}</x14:id>
+          <x14:id>{dc608717-f066-4f78-a5a9-64a41b662072}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11208,7 +11212,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1aa03129-594d-4d1c-b29b-cbe46ad0f321}</x14:id>
+          <x14:id>{d6490629-fcbe-471b-956e-835d02956a98}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11220,7 +11224,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2f8f479c-fff7-4087-8ec2-684807409923}</x14:id>
+          <x14:id>{33e11453-3ca0-4b2d-9011-82d65491cc7f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11232,7 +11236,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{78278cfb-ca23-4344-b895-291410e6af17}</x14:id>
+          <x14:id>{03343b28-50d7-405b-8ef2-4a52868d50ba}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11244,7 +11248,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d01c4d01-5569-4c75-8d97-2c31d5f0cf4e}</x14:id>
+          <x14:id>{88e41178-ac57-4290-9e47-ead19d391199}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11256,7 +11260,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c7b218de-9a6b-44e5-b631-73ec483f30c2}</x14:id>
+          <x14:id>{10f13032-784c-4f6c-bc1c-efe1a061a361}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11268,7 +11272,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8d693668-89f8-4e19-a75d-dd2b62168fc4}</x14:id>
+          <x14:id>{36c63486-18e3-449a-a7b5-cf052a5709bc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11282,7 +11286,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0f6f1cfa-4622-4714-af9e-864554cb04fc}</x14:id>
+          <x14:id>{81d13e68-642e-4bb1-a82f-f9364374467b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11294,7 +11298,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a9913723-1643-4861-a19a-cec77ddaccfe}</x14:id>
+          <x14:id>{fbd366fb-f6fc-4190-9490-00fa288a2ef2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11306,7 +11310,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bea9e6f5-ba8b-4f43-af62-21b318bab6e7}</x14:id>
+          <x14:id>{e721645b-c6dc-44a7-a543-64432da7b5a9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11318,7 +11322,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a4abb4c2-a7e7-41a6-8d65-f07f8b857fae}</x14:id>
+          <x14:id>{f3b60a87-cc09-4ff8-91bd-c716b92a6c12}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11330,7 +11334,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0458a306-f0a9-4df4-a133-ac43f3ad062b}</x14:id>
+          <x14:id>{b31ce8c0-c208-4033-af3f-49da25cbf5b5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11342,7 +11346,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eb4ea31a-4a31-4d6a-ac71-e23e06fb8e35}</x14:id>
+          <x14:id>{019968d7-b214-449c-99d1-32d466b3193b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11354,7 +11358,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{285d110c-58bc-456b-824f-edb20d1032d6}</x14:id>
+          <x14:id>{e72f0bc5-84bf-43ea-80d8-59a15d55da42}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11366,7 +11370,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{219751a3-2ce5-4831-ab37-ff5e15317496}</x14:id>
+          <x14:id>{26daa55e-941b-4a21-9fa2-f3ff9d61a6fe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11380,7 +11384,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5dfc36d9-ee4e-4022-8ef2-020b9c63c61d}</x14:id>
+          <x14:id>{3a3f25c4-cd4f-4c7b-ac97-3410b455c670}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11392,7 +11396,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4700a69f-9f02-419e-abac-bfd92861ca4d}</x14:id>
+          <x14:id>{768107ad-ece9-4d66-9141-266d37f91bfd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11404,7 +11408,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a2fba1b3-9157-40d6-a81a-0028feb684e4}</x14:id>
+          <x14:id>{6292edcd-73c9-4d4b-baa1-65b91ea82f9e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11416,7 +11420,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{94817ea8-8a5b-4010-9977-c022e014e003}</x14:id>
+          <x14:id>{a1bd7b84-4b14-426e-857d-8719c72c37d8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11428,7 +11432,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e57d1a90-9aaa-4c70-8e30-106d55c09713}</x14:id>
+          <x14:id>{c0532312-1b08-47e2-9a09-963ee3f2f64e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11440,7 +11444,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{12179ac9-f647-4d9c-b9ae-4a1be66bf126}</x14:id>
+          <x14:id>{c48d18f7-ad5d-4787-93e0-57a82c6cae51}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11452,7 +11456,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{de4caa06-4609-4439-9130-509dfe5a9dc5}</x14:id>
+          <x14:id>{711097c7-3b0c-4aab-99d9-866ad7f7c87e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11464,7 +11468,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{765bddd9-3192-437e-9afb-27933e53a3f8}</x14:id>
+          <x14:id>{4136dfb6-56c9-4c42-9acb-caa2d2077048}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11478,7 +11482,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b291811a-dcea-4d64-b241-5d85a2500b9c}</x14:id>
+          <x14:id>{dd0213ae-263a-41d6-8dd2-0a992ccf8cb7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11490,7 +11494,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5df749e9-95a0-42d9-976c-ab5571580b11}</x14:id>
+          <x14:id>{787283b6-cb39-492e-9021-686202451be5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11502,7 +11506,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9a431776-b765-4fc1-9f80-9fe681b7e805}</x14:id>
+          <x14:id>{90a758bf-4932-4b37-a21d-927a773edcda}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11514,7 +11518,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a1fd002b-7e0a-4e52-9539-06961645664a}</x14:id>
+          <x14:id>{9855e2a8-8456-4661-81fd-6915e4559f21}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11526,7 +11530,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7207f772-8522-4531-824a-e67beb258a74}</x14:id>
+          <x14:id>{80468915-385f-4356-b03a-be4dbd243f8e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11538,7 +11542,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e475a319-fd6c-4759-8851-334b36e00a75}</x14:id>
+          <x14:id>{0e4c1bf7-7a26-40f7-93b0-a6cbc43089f5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11550,7 +11554,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ae775541-37ab-4200-87c7-76f0ea39bb1f}</x14:id>
+          <x14:id>{fc66b491-9ab6-4864-9842-b40335ef73e7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11562,7 +11566,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{28aea0bf-fcca-4cc0-8df3-9e74ea5f36ee}</x14:id>
+          <x14:id>{b22569c0-bfb5-455c-a1a0-334788c0fbb4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11576,7 +11580,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{17dce266-3284-4cb8-94c1-f36d85374b28}</x14:id>
+          <x14:id>{99b76234-da35-4554-94be-443acc709c39}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11588,7 +11592,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{34c6179b-6b7f-42dc-8b61-49591e1fc02c}</x14:id>
+          <x14:id>{fa4ae5be-e494-43ac-add9-6e6dfeb7368b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11600,7 +11604,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{37418d0b-11ad-4b43-89cc-9c372b3c1143}</x14:id>
+          <x14:id>{b2e24994-7c4f-4dbb-8867-8c0f1170739e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11612,7 +11616,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{075dbdca-8b4d-4d31-8253-2482efffd198}</x14:id>
+          <x14:id>{51b5e3da-e479-4ce0-938e-993fef1494f2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11624,7 +11628,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{14335229-59b5-4440-9262-849cabff99ec}</x14:id>
+          <x14:id>{c45da89a-5892-4b98-8630-22fb1ba3be8d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11636,7 +11640,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dadabee5-68bb-4c30-af48-157a83eff0f2}</x14:id>
+          <x14:id>{036682b9-389d-488e-a322-46985c5f882e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11648,7 +11652,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e56e7f9a-caf4-477b-9d1f-8b9f411e3563}</x14:id>
+          <x14:id>{0028203e-c5a8-44a2-968f-d2948b8f702d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11660,7 +11664,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5cd39489-b0d7-4c27-bd74-55e9f86d60b0}</x14:id>
+          <x14:id>{d72c2497-ec79-49c9-b0ef-313233bcdec5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11674,7 +11678,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{adcea6f6-a63f-438f-a7d5-06c178a3e3cf}</x14:id>
+          <x14:id>{1b4d543e-b4d4-4ec3-bc96-4b162b66afcd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11686,7 +11690,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{25a027e5-9b5e-4eef-9bed-e86368ecd880}</x14:id>
+          <x14:id>{8088920a-74bd-4e07-94c7-9d32fd898f8c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11698,7 +11702,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6b0a2beb-4643-4d8b-bbd2-13dd2d781aca}</x14:id>
+          <x14:id>{ad9239a5-280c-46d2-a105-879b4fdf1949}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11712,7 +11716,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ee7d6c52-3640-46e1-a24d-d40fbf16e8d9}</x14:id>
+          <x14:id>{67b43be6-050b-46f0-8488-a79cc66e77f2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11724,7 +11728,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4fad6bbd-e805-446d-ac9e-06593a0f925b}</x14:id>
+          <x14:id>{4cf57c99-0a12-479a-9906-640199b7a00d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11736,7 +11740,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{56127cfd-c848-448f-9036-4cb856e63eee}</x14:id>
+          <x14:id>{ced816e7-654f-4b78-8360-8e82f0b04ecc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11750,7 +11754,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f1198962-2654-4c94-8476-6e3b45cd451c}</x14:id>
+          <x14:id>{678575e2-b5fc-4c02-9722-25beb2733a4d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11762,7 +11766,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b0e3e4d8-9fea-4b16-bf73-a9b23d92ad38}</x14:id>
+          <x14:id>{cda19f44-8c33-4ae0-97f7-b7c0447e794a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11776,7 +11780,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{66b29c32-8cf3-4277-82d6-ba95161c5981}</x14:id>
+          <x14:id>{16a9e5b0-f7ab-4fbc-a6a4-766d03e3fc89}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11788,7 +11792,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f506ca46-8425-4c07-a8da-13727ef585c8}</x14:id>
+          <x14:id>{4ff3fb55-3fa4-45a3-a2aa-91fd74b24072}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11800,7 +11804,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{30ef224e-fe6c-4b32-b953-937fb224c6f2}</x14:id>
+          <x14:id>{0a81fc6a-d45c-48a8-a144-e4fa2c45b1ee}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11814,7 +11818,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ea6cb50c-aac6-4be2-8eb0-196601b5940a}</x14:id>
+          <x14:id>{7da44644-4e47-4b84-b907-4dd47e99ef14}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11826,7 +11830,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c34ba798-a809-4db0-aa17-fa446710e270}</x14:id>
+          <x14:id>{7ece2329-754c-4dda-ba1b-fa1a8bd18872}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11838,7 +11842,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4bd76677-8845-4c64-acfb-b6a557ead14e}</x14:id>
+          <x14:id>{9d508d61-1fe4-4ab7-9ecd-1b60b9cfd4b8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11852,7 +11856,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8fe7ba6b-37bd-4793-9560-3f7fb8fef8a7}</x14:id>
+          <x14:id>{246b0ca9-687d-4e4e-a4e1-c559ddc91d10}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11864,7 +11868,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{152d7522-c7ca-49a0-b114-a5b724a1f774}</x14:id>
+          <x14:id>{f1b60e70-98a0-4a9f-bd53-0d23933f2cbd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11876,7 +11880,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{130ca20e-fec8-4d00-8c53-292224148420}</x14:id>
+          <x14:id>{155e4ad8-fdf1-4432-bed0-fc7c1ed53cc1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11890,7 +11894,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d6931269-8022-4805-a10b-f685ee134c25}</x14:id>
+          <x14:id>{dfa17ede-82bb-4ec6-9600-af1a10ad9335}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11902,7 +11906,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c6989c46-adfc-4013-b430-805b1c371b96}</x14:id>
+          <x14:id>{c3e83820-e30d-44e7-96ef-94d364d554e5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11914,7 +11918,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8ac1dcf1-5a08-4401-907d-98676ac0adc6}</x14:id>
+          <x14:id>{e7f1ce64-5ef1-4ce0-a38d-96f2ca81580d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11928,7 +11932,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c914cfa2-4f39-449f-b9fe-931802c70420}</x14:id>
+          <x14:id>{db7a0dd9-e644-40a2-aa14-fdf44c7e0bcf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11940,7 +11944,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b32f1855-e93c-44f4-9a79-e6b80394f85c}</x14:id>
+          <x14:id>{e8ba5cac-1e98-4939-bf97-ca099f30975f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11952,7 +11956,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b78adf73-c8f4-487a-8e7d-bcff748e7667}</x14:id>
+          <x14:id>{e3cf83b7-6496-488c-8825-b2c6bf81f58f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11966,7 +11970,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{86dd25d1-7c19-4d66-b61b-9852ae60cbf0}</x14:id>
+          <x14:id>{3ba01fad-1012-44aa-95df-d0cf55e2013e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11978,7 +11982,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{adfd9c4f-6b88-44a4-b255-16336ff6d4f6}</x14:id>
+          <x14:id>{2110f27d-bee4-40cd-8ffe-06bb1a300495}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11990,7 +11994,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ab6efa9f-6f94-4293-8f44-388673ea190d}</x14:id>
+          <x14:id>{bfc6bf5c-1d96-4745-9d0b-d5c3da782014}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12002,7 +12006,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{62e892dc-3651-4ea0-9ebf-4e11e1936ed2}</x14:id>
+          <x14:id>{c7a10603-5394-4560-a078-1f8cde127f69}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12014,7 +12018,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dadba715-1311-4b2c-81a9-1a0e0cc11ac7}</x14:id>
+          <x14:id>{dfbe3c9e-4bcd-4d83-ad7b-00efffb492f6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12026,7 +12030,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{67bc41c7-064d-4f54-8835-8b4bbcab6d95}</x14:id>
+          <x14:id>{ea6a31f5-73c7-4647-a8bf-875b8310af6d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12038,7 +12042,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{edb8592f-6483-4caa-8b83-d9c2ac690782}</x14:id>
+          <x14:id>{69d466d0-abfb-4d61-acf8-b5adea56189b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12050,7 +12054,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d043a9cb-21e5-4ec2-b058-a4ea811c027e}</x14:id>
+          <x14:id>{793ea7f4-f361-4baa-b8c2-7657028d4894}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12064,7 +12068,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c9313cad-6624-4e0f-ae7d-7f037f9f250f}</x14:id>
+          <x14:id>{4785fce1-05c1-4eff-8ae3-8ff7c1bd1ea9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12076,7 +12080,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{68fa76f4-0799-4cbc-8303-65ed6c0ca6d9}</x14:id>
+          <x14:id>{9f86a527-c07f-47ec-b872-80c8aff57e1f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12090,7 +12094,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5b7c410c-f518-4d51-9341-9efd74373b22}</x14:id>
+          <x14:id>{888fa92c-8112-4f96-857d-00159d71c86e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12104,7 +12108,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{899b5e31-c46a-49b8-95f6-2baf42f6a076}</x14:id>
+          <x14:id>{57747a2d-c3ca-49bd-b778-9e19d4db0e15}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12118,7 +12122,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f1a4b3e3-fef8-49a8-8bc7-2e173d78582e}</x14:id>
+          <x14:id>{15b31294-f99e-4183-830c-dd322fd307a8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12132,7 +12136,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8362e5b2-406f-470b-9f71-6247ab730169}</x14:id>
+          <x14:id>{9c2570c8-1a17-4430-9067-a150c811964d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12146,7 +12150,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{03f8dc56-1d28-40fd-9ea3-a61cdeef71e8}</x14:id>
+          <x14:id>{26c58f1c-0796-4e14-ae7c-fc4088105c24}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12158,7 +12162,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5d7c33c2-0703-4e16-8173-894538552e82}</x14:id>
+          <x14:id>{786036a2-343a-4a2a-aced-2913f439c017}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12170,7 +12174,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a876de58-0e26-4b09-b6ed-bb9db6bd7eb5}</x14:id>
+          <x14:id>{652d0d30-241a-48ed-b98e-638d0045db9d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12184,7 +12188,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7a74caab-7c50-49c3-b25c-0be646ed47b7}</x14:id>
+          <x14:id>{4890317d-7792-4a65-b2e0-fee8cf5e878a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12196,7 +12200,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3f2352c3-6ec6-4fc9-9b24-f41eadfbc60f}</x14:id>
+          <x14:id>{97c430b1-f1b4-4b9f-a8ab-3b6ec963945c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12208,7 +12212,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5f8b9665-7e50-4bb3-9c94-e00344d7b40f}</x14:id>
+          <x14:id>{1f9ae181-fa63-4e77-a2a8-236f68bf084f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12222,7 +12226,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{67e86ebc-2a6d-41a6-aa7a-48a719c20d65}</x14:id>
+          <x14:id>{42bf44fa-a319-4fde-a6c2-5c8a4df39b12}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12234,7 +12238,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c3b5085b-5262-45b8-90e4-b5b4fab31cbc}</x14:id>
+          <x14:id>{05b6d790-7f3e-4b15-9d16-6526f9bbddf6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12246,7 +12250,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{be17578d-f265-4070-a364-1ba6ef976da4}</x14:id>
+          <x14:id>{3faffba6-6106-41fa-a4b5-bbb58564c9cf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12260,7 +12264,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a2c91264-2f52-467c-95b1-3b0d15e451da}</x14:id>
+          <x14:id>{bf767043-9723-40d3-89c1-4f0237d63cdb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12272,7 +12276,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f7f8b401-6248-419b-b500-eaf3502d38d5}</x14:id>
+          <x14:id>{e73aae7c-0db7-4549-addd-c779c1ac5c67}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12284,7 +12288,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{49416b94-fd26-4d9d-994f-6df1882ca6e9}</x14:id>
+          <x14:id>{807f2e68-6300-4ffb-971a-128c023b4064}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12298,7 +12302,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b15f3b6d-6758-45ff-abbc-36130e6136a0}</x14:id>
+          <x14:id>{bcb33bf1-acf1-485f-84d9-60f81cce47fc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12310,7 +12314,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{37d9cf3b-6aa4-468e-a81f-876467b1e332}</x14:id>
+          <x14:id>{158ee51e-7592-4f23-98a6-4b2b489f3150}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12324,7 +12328,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e249975f-305c-4e94-9257-91fd1a6d53e8}</x14:id>
+          <x14:id>{a3752975-14d5-462d-a711-737ec2cd7922}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12336,7 +12340,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b240a561-ec3e-406b-8750-8614b86aed19}</x14:id>
+          <x14:id>{aa6f49fd-7b36-4e3e-aed3-fed86d85bd90}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12348,7 +12352,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b27629ea-eb70-4edc-8f10-b9a81b9d8624}</x14:id>
+          <x14:id>{5e6721e5-b970-44fe-89c8-36dadc575889}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12362,7 +12366,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4fd8c3ad-57f4-4b82-9b33-3d148fd0137e}</x14:id>
+          <x14:id>{e05244d8-0e67-41f4-b329-31e24ba61ec8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12374,7 +12378,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5433f30b-40b0-4f97-80a1-b3af0999a273}</x14:id>
+          <x14:id>{db6b9fc7-9eb0-4d66-98f5-f700afd0fe8c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12386,7 +12390,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ed943de3-3d56-464c-856a-33d969cf3a04}</x14:id>
+          <x14:id>{f5d30e62-89c8-49a1-9c0c-b6e80ee77963}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12400,7 +12404,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{55abfbfa-66ed-4cfd-a1a3-2b07625cfb9d}</x14:id>
+          <x14:id>{d19732fd-2033-474d-be69-60e4354ac7c7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12412,7 +12416,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e9de3cd7-e3ff-4b26-8af4-d46824f7900e}</x14:id>
+          <x14:id>{b6072a33-a097-49b6-801f-b68f2bfd9993}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12446,7 +12450,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b5bdb37c-304d-45b0-9ead-82cf4b1e18ba}">
+          <x14:cfRule type="dataBar" id="{d26b6506-af02-4c3e-abd8-c960452e00fd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12457,7 +12461,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{70cac10c-c36d-4e1d-a2c5-c516e8f5755e}">
+          <x14:cfRule type="dataBar" id="{6f9b6945-1b12-42cc-a358-15fccc908496}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12468,14 +12472,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b6af8c4e-13f2-4703-88dc-cfed550de9c5}">
+          <x14:cfRule type="dataBar" id="{fbdf3d43-7e43-46d8-ba48-dfc08066ee32}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{bee170fd-42b7-40df-9112-0529c3e8af7d}">
+          <x14:cfRule type="dataBar" id="{0a25df39-72f8-4de8-8b8e-aa779181855d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12486,7 +12490,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c5a833c9-4ce5-4980-ae7e-c11d14bbdc15}">
+          <x14:cfRule type="dataBar" id="{59f2dfec-c076-4ea3-b927-f22bf00d43fe}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12497,7 +12501,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0553788b-7da1-45bd-a985-958155d938e9}">
+          <x14:cfRule type="dataBar" id="{eaff4522-b194-4d35-9268-cc6e8157ea8d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12508,7 +12512,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{114fcd61-28dc-4a3d-8bf2-4982fdfb1546}">
+          <x14:cfRule type="dataBar" id="{7d77bee7-6fd5-4381-acaf-738800090c26}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12517,7 +12521,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2f292e0e-71a0-4d17-8db6-3ac6c57e5318}">
+          <x14:cfRule type="dataBar" id="{4023263c-9333-4063-83f5-5b92623fd4b7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12529,7 +12533,7 @@
           <xm:sqref>AD56</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f06b5711-00b8-49b1-b0c4-77c1220dd65f}">
+          <x14:cfRule type="dataBar" id="{d1905c29-40d3-4efd-94f7-aa65a257254f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12540,7 +12544,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{965cd7c9-04c7-4320-8637-ec70834fa997}">
+          <x14:cfRule type="dataBar" id="{dc608717-f066-4f78-a5a9-64a41b662072}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12551,14 +12555,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1aa03129-594d-4d1c-b29b-cbe46ad0f321}">
+          <x14:cfRule type="dataBar" id="{d6490629-fcbe-471b-956e-835d02956a98}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2f8f479c-fff7-4087-8ec2-684807409923}">
+          <x14:cfRule type="dataBar" id="{33e11453-3ca0-4b2d-9011-82d65491cc7f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12569,7 +12573,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{78278cfb-ca23-4344-b895-291410e6af17}">
+          <x14:cfRule type="dataBar" id="{03343b28-50d7-405b-8ef2-4a52868d50ba}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12580,7 +12584,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d01c4d01-5569-4c75-8d97-2c31d5f0cf4e}">
+          <x14:cfRule type="dataBar" id="{88e41178-ac57-4290-9e47-ead19d391199}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12591,7 +12595,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c7b218de-9a6b-44e5-b631-73ec483f30c2}">
+          <x14:cfRule type="dataBar" id="{10f13032-784c-4f6c-bc1c-efe1a061a361}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12600,7 +12604,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8d693668-89f8-4e19-a75d-dd2b62168fc4}">
+          <x14:cfRule type="dataBar" id="{36c63486-18e3-449a-a7b5-cf052a5709bc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12612,7 +12616,7 @@
           <xm:sqref>K60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0f6f1cfa-4622-4714-af9e-864554cb04fc}">
+          <x14:cfRule type="dataBar" id="{81d13e68-642e-4bb1-a82f-f9364374467b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12623,7 +12627,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a9913723-1643-4861-a19a-cec77ddaccfe}">
+          <x14:cfRule type="dataBar" id="{fbd366fb-f6fc-4190-9490-00fa288a2ef2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12634,14 +12638,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{bea9e6f5-ba8b-4f43-af62-21b318bab6e7}">
+          <x14:cfRule type="dataBar" id="{e721645b-c6dc-44a7-a543-64432da7b5a9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a4abb4c2-a7e7-41a6-8d65-f07f8b857fae}">
+          <x14:cfRule type="dataBar" id="{f3b60a87-cc09-4ff8-91bd-c716b92a6c12}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12652,7 +12656,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0458a306-f0a9-4df4-a133-ac43f3ad062b}">
+          <x14:cfRule type="dataBar" id="{b31ce8c0-c208-4033-af3f-49da25cbf5b5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12663,7 +12667,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{eb4ea31a-4a31-4d6a-ac71-e23e06fb8e35}">
+          <x14:cfRule type="dataBar" id="{019968d7-b214-449c-99d1-32d466b3193b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12674,7 +12678,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{285d110c-58bc-456b-824f-edb20d1032d6}">
+          <x14:cfRule type="dataBar" id="{e72f0bc5-84bf-43ea-80d8-59a15d55da42}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12683,7 +12687,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{219751a3-2ce5-4831-ab37-ff5e15317496}">
+          <x14:cfRule type="dataBar" id="{26daa55e-941b-4a21-9fa2-f3ff9d61a6fe}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12695,7 +12699,7 @@
           <xm:sqref>AD60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5dfc36d9-ee4e-4022-8ef2-020b9c63c61d}">
+          <x14:cfRule type="dataBar" id="{3a3f25c4-cd4f-4c7b-ac97-3410b455c670}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12706,7 +12710,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4700a69f-9f02-419e-abac-bfd92861ca4d}">
+          <x14:cfRule type="dataBar" id="{768107ad-ece9-4d66-9141-266d37f91bfd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12717,14 +12721,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a2fba1b3-9157-40d6-a81a-0028feb684e4}">
+          <x14:cfRule type="dataBar" id="{6292edcd-73c9-4d4b-baa1-65b91ea82f9e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{94817ea8-8a5b-4010-9977-c022e014e003}">
+          <x14:cfRule type="dataBar" id="{a1bd7b84-4b14-426e-857d-8719c72c37d8}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12735,7 +12739,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e57d1a90-9aaa-4c70-8e30-106d55c09713}">
+          <x14:cfRule type="dataBar" id="{c0532312-1b08-47e2-9a09-963ee3f2f64e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12746,7 +12750,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{12179ac9-f647-4d9c-b9ae-4a1be66bf126}">
+          <x14:cfRule type="dataBar" id="{c48d18f7-ad5d-4787-93e0-57a82c6cae51}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12757,7 +12761,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{de4caa06-4609-4439-9130-509dfe5a9dc5}">
+          <x14:cfRule type="dataBar" id="{711097c7-3b0c-4aab-99d9-866ad7f7c87e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12766,7 +12770,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{765bddd9-3192-437e-9afb-27933e53a3f8}">
+          <x14:cfRule type="dataBar" id="{4136dfb6-56c9-4c42-9acb-caa2d2077048}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12778,7 +12782,7 @@
           <xm:sqref>K61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b291811a-dcea-4d64-b241-5d85a2500b9c}">
+          <x14:cfRule type="dataBar" id="{dd0213ae-263a-41d6-8dd2-0a992ccf8cb7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12789,7 +12793,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5df749e9-95a0-42d9-976c-ab5571580b11}">
+          <x14:cfRule type="dataBar" id="{787283b6-cb39-492e-9021-686202451be5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12800,14 +12804,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9a431776-b765-4fc1-9f80-9fe681b7e805}">
+          <x14:cfRule type="dataBar" id="{90a758bf-4932-4b37-a21d-927a773edcda}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a1fd002b-7e0a-4e52-9539-06961645664a}">
+          <x14:cfRule type="dataBar" id="{9855e2a8-8456-4661-81fd-6915e4559f21}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12818,7 +12822,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7207f772-8522-4531-824a-e67beb258a74}">
+          <x14:cfRule type="dataBar" id="{80468915-385f-4356-b03a-be4dbd243f8e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12829,7 +12833,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e475a319-fd6c-4759-8851-334b36e00a75}">
+          <x14:cfRule type="dataBar" id="{0e4c1bf7-7a26-40f7-93b0-a6cbc43089f5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12840,7 +12844,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ae775541-37ab-4200-87c7-76f0ea39bb1f}">
+          <x14:cfRule type="dataBar" id="{fc66b491-9ab6-4864-9842-b40335ef73e7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12849,7 +12853,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{28aea0bf-fcca-4cc0-8df3-9e74ea5f36ee}">
+          <x14:cfRule type="dataBar" id="{b22569c0-bfb5-455c-a1a0-334788c0fbb4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12861,7 +12865,7 @@
           <xm:sqref>K62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{17dce266-3284-4cb8-94c1-f36d85374b28}">
+          <x14:cfRule type="dataBar" id="{99b76234-da35-4554-94be-443acc709c39}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12872,7 +12876,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{34c6179b-6b7f-42dc-8b61-49591e1fc02c}">
+          <x14:cfRule type="dataBar" id="{fa4ae5be-e494-43ac-add9-6e6dfeb7368b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12883,14 +12887,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{37418d0b-11ad-4b43-89cc-9c372b3c1143}">
+          <x14:cfRule type="dataBar" id="{b2e24994-7c4f-4dbb-8867-8c0f1170739e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{075dbdca-8b4d-4d31-8253-2482efffd198}">
+          <x14:cfRule type="dataBar" id="{51b5e3da-e479-4ce0-938e-993fef1494f2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12901,7 +12905,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{14335229-59b5-4440-9262-849cabff99ec}">
+          <x14:cfRule type="dataBar" id="{c45da89a-5892-4b98-8630-22fb1ba3be8d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12912,7 +12916,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{dadabee5-68bb-4c30-af48-157a83eff0f2}">
+          <x14:cfRule type="dataBar" id="{036682b9-389d-488e-a322-46985c5f882e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12923,7 +12927,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e56e7f9a-caf4-477b-9d1f-8b9f411e3563}">
+          <x14:cfRule type="dataBar" id="{0028203e-c5a8-44a2-968f-d2948b8f702d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12932,7 +12936,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5cd39489-b0d7-4c27-bd74-55e9f86d60b0}">
+          <x14:cfRule type="dataBar" id="{d72c2497-ec79-49c9-b0ef-313233bcdec5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12944,7 +12948,7 @@
           <xm:sqref>K63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{adcea6f6-a63f-438f-a7d5-06c178a3e3cf}">
+          <x14:cfRule type="dataBar" id="{1b4d543e-b4d4-4ec3-bc96-4b162b66afcd}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12953,7 +12957,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{25a027e5-9b5e-4eef-9bed-e86368ecd880}">
+          <x14:cfRule type="dataBar" id="{8088920a-74bd-4e07-94c7-9d32fd898f8c}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12962,7 +12966,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6b0a2beb-4643-4d8b-bbd2-13dd2d781aca}">
+          <x14:cfRule type="dataBar" id="{ad9239a5-280c-46d2-a105-879b4fdf1949}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -12975,7 +12979,7 @@
           <xm:sqref>AB67</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ee7d6c52-3640-46e1-a24d-d40fbf16e8d9}">
+          <x14:cfRule type="dataBar" id="{67b43be6-050b-46f0-8488-a79cc66e77f2}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12984,7 +12988,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4fad6bbd-e805-446d-ac9e-06593a0f925b}">
+          <x14:cfRule type="dataBar" id="{4cf57c99-0a12-479a-9906-640199b7a00d}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12993,7 +12997,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{56127cfd-c848-448f-9036-4cb856e63eee}">
+          <x14:cfRule type="dataBar" id="{ced816e7-654f-4b78-8360-8e82f0b04ecc}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13006,7 +13010,7 @@
           <xm:sqref>AB101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f1198962-2654-4c94-8476-6e3b45cd451c}">
+          <x14:cfRule type="dataBar" id="{678575e2-b5fc-4c02-9722-25beb2733a4d}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13015,7 +13019,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b0e3e4d8-9fea-4b16-bf73-a9b23d92ad38}">
+          <x14:cfRule type="dataBar" id="{cda19f44-8c33-4ae0-97f7-b7c0447e794a}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13027,7 +13031,7 @@
           <xm:sqref>AB115</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{66b29c32-8cf3-4277-82d6-ba95161c5981}">
+          <x14:cfRule type="dataBar" id="{16a9e5b0-f7ab-4fbc-a6a4-766d03e3fc89}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13036,7 +13040,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f506ca46-8425-4c07-a8da-13727ef585c8}">
+          <x14:cfRule type="dataBar" id="{4ff3fb55-3fa4-45a3-a2aa-91fd74b24072}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13045,7 +13049,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{30ef224e-fe6c-4b32-b953-937fb224c6f2}">
+          <x14:cfRule type="dataBar" id="{0a81fc6a-d45c-48a8-a144-e4fa2c45b1ee}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13058,7 +13062,7 @@
           <xm:sqref>AB125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ea6cb50c-aac6-4be2-8eb0-196601b5940a}">
+          <x14:cfRule type="dataBar" id="{7da44644-4e47-4b84-b907-4dd47e99ef14}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13067,7 +13071,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c34ba798-a809-4db0-aa17-fa446710e270}">
+          <x14:cfRule type="dataBar" id="{7ece2329-754c-4dda-ba1b-fa1a8bd18872}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13076,7 +13080,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4bd76677-8845-4c64-acfb-b6a557ead14e}">
+          <x14:cfRule type="dataBar" id="{9d508d61-1fe4-4ab7-9ecd-1b60b9cfd4b8}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13089,7 +13093,7 @@
           <xm:sqref>K135</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8fe7ba6b-37bd-4793-9560-3f7fb8fef8a7}">
+          <x14:cfRule type="dataBar" id="{246b0ca9-687d-4e4e-a4e1-c559ddc91d10}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13098,7 +13102,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{152d7522-c7ca-49a0-b114-a5b724a1f774}">
+          <x14:cfRule type="dataBar" id="{f1b60e70-98a0-4a9f-bd53-0d23933f2cbd}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13107,7 +13111,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{130ca20e-fec8-4d00-8c53-292224148420}">
+          <x14:cfRule type="dataBar" id="{155e4ad8-fdf1-4432-bed0-fc7c1ed53cc1}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13120,7 +13124,7 @@
           <xm:sqref>K140</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d6931269-8022-4805-a10b-f685ee134c25}">
+          <x14:cfRule type="dataBar" id="{dfa17ede-82bb-4ec6-9600-af1a10ad9335}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13129,7 +13133,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c6989c46-adfc-4013-b430-805b1c371b96}">
+          <x14:cfRule type="dataBar" id="{c3e83820-e30d-44e7-96ef-94d364d554e5}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13138,7 +13142,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8ac1dcf1-5a08-4401-907d-98676ac0adc6}">
+          <x14:cfRule type="dataBar" id="{e7f1ce64-5ef1-4ce0-a38d-96f2ca81580d}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13151,7 +13155,7 @@
           <xm:sqref>K145</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c914cfa2-4f39-449f-b9fe-931802c70420}">
+          <x14:cfRule type="dataBar" id="{db7a0dd9-e644-40a2-aa14-fdf44c7e0bcf}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13160,7 +13164,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b32f1855-e93c-44f4-9a79-e6b80394f85c}">
+          <x14:cfRule type="dataBar" id="{e8ba5cac-1e98-4939-bf97-ca099f30975f}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13169,7 +13173,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b78adf73-c8f4-487a-8e7d-bcff748e7667}">
+          <x14:cfRule type="dataBar" id="{e3cf83b7-6496-488c-8825-b2c6bf81f58f}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13182,7 +13186,7 @@
           <xm:sqref>K150</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{86dd25d1-7c19-4d66-b61b-9852ae60cbf0}">
+          <x14:cfRule type="dataBar" id="{3ba01fad-1012-44aa-95df-d0cf55e2013e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -13193,7 +13197,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{adfd9c4f-6b88-44a4-b255-16336ff6d4f6}">
+          <x14:cfRule type="dataBar" id="{2110f27d-bee4-40cd-8ffe-06bb1a300495}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13204,14 +13208,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ab6efa9f-6f94-4293-8f44-388673ea190d}">
+          <x14:cfRule type="dataBar" id="{bfc6bf5c-1d96-4745-9d0b-d5c3da782014}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{62e892dc-3651-4ea0-9ebf-4e11e1936ed2}">
+          <x14:cfRule type="dataBar" id="{c7a10603-5394-4560-a078-1f8cde127f69}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -13222,7 +13226,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{dadba715-1311-4b2c-81a9-1a0e0cc11ac7}">
+          <x14:cfRule type="dataBar" id="{dfbe3c9e-4bcd-4d83-ad7b-00efffb492f6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -13233,7 +13237,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{67bc41c7-064d-4f54-8835-8b4bbcab6d95}">
+          <x14:cfRule type="dataBar" id="{ea6a31f5-73c7-4647-a8bf-875b8310af6d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13244,7 +13248,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{edb8592f-6483-4caa-8b83-d9c2ac690782}">
+          <x14:cfRule type="dataBar" id="{69d466d0-abfb-4d61-acf8-b5adea56189b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13253,7 +13257,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d043a9cb-21e5-4ec2-b058-a4ea811c027e}">
+          <x14:cfRule type="dataBar" id="{793ea7f4-f361-4baa-b8c2-7657028d4894}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13265,7 +13269,7 @@
           <xm:sqref>K57:K58</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c9313cad-6624-4e0f-ae7d-7f037f9f250f}">
+          <x14:cfRule type="dataBar" id="{4785fce1-05c1-4eff-8ae3-8ff7c1bd1ea9}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13274,7 +13278,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{68fa76f4-0799-4cbc-8303-65ed6c0ca6d9}">
+          <x14:cfRule type="dataBar" id="{9f86a527-c07f-47ec-b872-80c8aff57e1f}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13287,7 +13291,7 @@
           <xm:sqref>Y67:Y86</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5b7c410c-f518-4d51-9341-9efd74373b22}">
+          <x14:cfRule type="dataBar" id="{888fa92c-8112-4f96-857d-00159d71c86e}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13300,7 +13304,7 @@
           <xm:sqref>Y77:Y86</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{899b5e31-c46a-49b8-95f6-2baf42f6a076}">
+          <x14:cfRule type="dataBar" id="{57747a2d-c3ca-49bd-b778-9e19d4db0e15}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13313,7 +13317,7 @@
           <xm:sqref>AB115:AB124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f1a4b3e3-fef8-49a8-8bc7-2e173d78582e}">
+          <x14:cfRule type="dataBar" id="{15b31294-f99e-4183-830c-dd322fd307a8}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13325,7 +13329,7 @@
           <xm:sqref>AD56:AE57</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8362e5b2-406f-470b-9f71-6247ab730169}">
+          <x14:cfRule type="dataBar" id="{9c2570c8-1a17-4430-9067-a150c811964d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13337,7 +13341,7 @@
           <xm:sqref>AD60:AE63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{03f8dc56-1d28-40fd-9ea3-a61cdeef71e8}">
+          <x14:cfRule type="dataBar" id="{26c58f1c-0796-4e14-ae7c-fc4088105c24}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13346,7 +13350,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5d7c33c2-0703-4e16-8173-894538552e82}">
+          <x14:cfRule type="dataBar" id="{786036a2-343a-4a2a-aced-2913f439c017}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13355,7 +13359,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a876de58-0e26-4b09-b6ed-bb9db6bd7eb5}">
+          <x14:cfRule type="dataBar" id="{652d0d30-241a-48ed-b98e-638d0045db9d}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13368,7 +13372,7 @@
           <xm:sqref>F67 F72 F77 F82</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7a74caab-7c50-49c3-b25c-0be646ed47b7}">
+          <x14:cfRule type="dataBar" id="{4890317d-7792-4a65-b2e0-fee8cf5e878a}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13377,7 +13381,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3f2352c3-6ec6-4fc9-9b24-f41eadfbc60f}">
+          <x14:cfRule type="dataBar" id="{97c430b1-f1b4-4b9f-a8ab-3b6ec963945c}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13386,7 +13390,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5f8b9665-7e50-4bb3-9c94-e00344d7b40f}">
+          <x14:cfRule type="dataBar" id="{1f9ae181-fa63-4e77-a2a8-236f68bf084f}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13399,7 +13403,7 @@
           <xm:sqref>K67 K77 K87 K101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{67e86ebc-2a6d-41a6-aa7a-48a719c20d65}">
+          <x14:cfRule type="dataBar" id="{42bf44fa-a319-4fde-a6c2-5c8a4df39b12}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13408,7 +13412,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c3b5085b-5262-45b8-90e4-b5b4fab31cbc}">
+          <x14:cfRule type="dataBar" id="{05b6d790-7f3e-4b15-9d16-6526f9bbddf6}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13417,7 +13421,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{be17578d-f265-4070-a364-1ba6ef976da4}">
+          <x14:cfRule type="dataBar" id="{3faffba6-6106-41fa-a4b5-bbb58564c9cf}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13430,7 +13434,7 @@
           <xm:sqref>AB77 AB87</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a2c91264-2f52-467c-95b1-3b0d15e451da}">
+          <x14:cfRule type="dataBar" id="{bf767043-9723-40d3-89c1-4f0237d63cdb}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13439,7 +13443,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f7f8b401-6248-419b-b500-eaf3502d38d5}">
+          <x14:cfRule type="dataBar" id="{e73aae7c-0db7-4549-addd-c779c1ac5c67}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13448,7 +13452,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{49416b94-fd26-4d9d-994f-6df1882ca6e9}">
+          <x14:cfRule type="dataBar" id="{807f2e68-6300-4ffb-971a-128c023b4064}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13461,7 +13465,7 @@
           <xm:sqref>F87 F94 F101 F108</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b15f3b6d-6758-45ff-abbc-36130e6136a0}">
+          <x14:cfRule type="dataBar" id="{bcb33bf1-acf1-485f-84d9-60f81cce47fc}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13470,7 +13474,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{37d9cf3b-6aa4-468e-a81f-876467b1e332}">
+          <x14:cfRule type="dataBar" id="{158ee51e-7592-4f23-98a6-4b2b489f3150}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13483,7 +13487,7 @@
           <xm:sqref>Y87 Y101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e249975f-305c-4e94-9257-91fd1a6d53e8}">
+          <x14:cfRule type="dataBar" id="{a3752975-14d5-462d-a711-737ec2cd7922}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13492,7 +13496,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b240a561-ec3e-406b-8750-8614b86aed19}">
+          <x14:cfRule type="dataBar" id="{aa6f49fd-7b36-4e3e-aed3-fed86d85bd90}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13501,7 +13505,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b27629ea-eb70-4edc-8f10-b9a81b9d8624}">
+          <x14:cfRule type="dataBar" id="{5e6721e5-b970-44fe-89c8-36dadc575889}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13514,7 +13518,7 @@
           <xm:sqref>F115 F120 F125 F130 F135 F140 F145 F150</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4fd8c3ad-57f4-4b82-9b33-3d148fd0137e}">
+          <x14:cfRule type="dataBar" id="{e05244d8-0e67-41f4-b329-31e24ba61ec8}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13523,7 +13527,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5433f30b-40b0-4f97-80a1-b3af0999a273}">
+          <x14:cfRule type="dataBar" id="{db6b9fc7-9eb0-4d66-98f5-f700afd0fe8c}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13532,7 +13536,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ed943de3-3d56-464c-856a-33d969cf3a04}">
+          <x14:cfRule type="dataBar" id="{f5d30e62-89c8-49a1-9c0c-b6e80ee77963}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13545,7 +13549,7 @@
           <xm:sqref>K115 K125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{55abfbfa-66ed-4cfd-a1a3-2b07625cfb9d}">
+          <x14:cfRule type="dataBar" id="{d19732fd-2033-474d-be69-60e4354ac7c7}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13554,7 +13558,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e9de3cd7-e3ff-4b26-8af4-d46824f7900e}">
+          <x14:cfRule type="dataBar" id="{b6072a33-a097-49b6-801f-b68f2bfd9993}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13576,12 +13580,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="26.8818181818182" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.38181818181818" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.21818181818182" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.38181818181818" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.8796296296296" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.37962962962963" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.22222222222222" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9.37962962962963" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">

--- a/其他楼交接班容量报表空模板.xlsx
+++ b/其他楼交接班容量报表空模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="22020"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="本班组" sheetId="1" r:id="rId1"/>
@@ -3193,28 +3193,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AF154"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="18.1851851851852" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.9351851851852" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.9363636363636" style="1" customWidth="1"/>
     <col min="7" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.4074074074074" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.4090909090909" style="1" customWidth="1"/>
     <col min="10" max="11" width="9" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.9351851851852" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.9363636363636" style="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="1" customWidth="1"/>
-    <col min="15" max="15" width="38.1851851851852" style="1" customWidth="1"/>
+    <col min="14" max="14" width="8.75454545454545" style="1" customWidth="1"/>
+    <col min="15" max="15" width="38.1818181818182" style="1" customWidth="1"/>
     <col min="16" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="12.5925925925926" style="1" customWidth="1"/>
-    <col min="20" max="20" width="16.5092592592593" style="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5909090909091" style="1" customWidth="1"/>
+    <col min="20" max="20" width="16.5090909090909" style="1" customWidth="1"/>
     <col min="21" max="21" width="9" style="1" customWidth="1"/>
-    <col min="22" max="22" width="14.1574074074074" style="1" customWidth="1"/>
+    <col min="22" max="22" width="14.1545454545455" style="1" customWidth="1"/>
     <col min="23" max="24" width="9" style="1" customWidth="1"/>
-    <col min="25" max="25" width="10.25" style="1" customWidth="1"/>
+    <col min="25" max="25" width="10.2545454545455" style="1" customWidth="1"/>
     <col min="26" max="27" width="9" style="1" customWidth="1"/>
-    <col min="28" max="28" width="17.4166666666667" style="1" customWidth="1"/>
+    <col min="28" max="28" width="17.4181818181818" style="1" customWidth="1"/>
     <col min="31" max="31" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3689,7 +3689,10 @@
       <c r="I12" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="J12" s="51"/>
+      <c r="J12" s="51">
+        <f>G12/10000</f>
+        <v>0</v>
+      </c>
       <c r="K12" s="14"/>
       <c r="L12" s="15"/>
       <c r="M12" s="52">
@@ -3732,7 +3735,10 @@
       <c r="I13" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="J13" s="51"/>
+      <c r="J13" s="51">
+        <f>G13/10000</f>
+        <v>0</v>
+      </c>
       <c r="K13" s="14"/>
       <c r="L13" s="15"/>
       <c r="M13" s="52">
@@ -3772,7 +3778,10 @@
       <c r="I14" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="J14" s="51"/>
+      <c r="J14" s="51">
+        <f>G14/10000</f>
+        <v>0</v>
+      </c>
       <c r="K14" s="14"/>
       <c r="L14" s="15"/>
       <c r="M14" s="52">
@@ -3813,7 +3822,10 @@
       <c r="I15" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="J15" s="51"/>
+      <c r="J15" s="51">
+        <f>G15/10000</f>
+        <v>0</v>
+      </c>
       <c r="K15" s="14"/>
       <c r="L15" s="15"/>
       <c r="M15" s="52">
@@ -5001,6 +5013,7 @@
         <v>89</v>
       </c>
       <c r="N38" s="103" t="e">
+        <f>N35-N36</f>
         <v>#VALUE!</v>
       </c>
       <c r="O38" s="53"/>
@@ -5036,6 +5049,7 @@
         <v>89</v>
       </c>
       <c r="AA38" s="102" t="e">
+        <f>AA35-AA36</f>
         <v>#VALUE!</v>
       </c>
       <c r="AB38" s="85" t="s">
@@ -5155,6 +5169,7 @@
         <v>100</v>
       </c>
       <c r="L40" s="102" t="e">
+        <f>L39-L35</f>
         <v>#VALUE!</v>
       </c>
       <c r="M40" s="100" t="s">
@@ -5188,6 +5203,7 @@
         <v>100</v>
       </c>
       <c r="Y40" s="102" t="e">
+        <f>Y39-Y35</f>
         <v>#VALUE!</v>
       </c>
       <c r="Z40" s="100" t="s">
@@ -5230,6 +5246,7 @@
         <v>105</v>
       </c>
       <c r="N41" s="103" t="e">
+        <f>N39-N40</f>
         <v>#VALUE!</v>
       </c>
       <c r="O41" s="53"/>
@@ -5255,6 +5272,7 @@
         <v>105</v>
       </c>
       <c r="AA41" s="102" t="e">
+        <f>AA39-AA40</f>
         <v>#VALUE!</v>
       </c>
       <c r="AB41" s="77"/>
@@ -6242,7 +6260,7 @@
       <c r="AD64" s="62"/>
       <c r="AE64" s="62"/>
     </row>
-    <row r="65" s="10" customFormat="1" ht="17.4" spans="1:32">
+    <row r="65" s="10" customFormat="1" ht="17.5" spans="1:32">
       <c r="A65" s="134"/>
       <c r="B65" s="135"/>
       <c r="C65" s="135"/>
@@ -11090,7 +11108,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d26b6506-af02-4c3e-abd8-c960452e00fd}</x14:id>
+          <x14:id>{aa9873e0-b3ee-4b61-97ca-60ebe8490711}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11102,7 +11120,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6f9b6945-1b12-42cc-a358-15fccc908496}</x14:id>
+          <x14:id>{fa04ff7d-e7b6-4f75-97c5-547db3ff1338}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11114,7 +11132,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fbdf3d43-7e43-46d8-ba48-dfc08066ee32}</x14:id>
+          <x14:id>{a0f9c72e-9472-48c2-a3b7-d75ed7029e82}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11126,7 +11144,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0a25df39-72f8-4de8-8b8e-aa779181855d}</x14:id>
+          <x14:id>{eaf28077-1c70-4a53-bbd7-f15b73e61db5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11138,7 +11156,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{59f2dfec-c076-4ea3-b927-f22bf00d43fe}</x14:id>
+          <x14:id>{41712525-6ece-4b08-b8d3-9d3845852a53}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11150,7 +11168,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eaff4522-b194-4d35-9268-cc6e8157ea8d}</x14:id>
+          <x14:id>{0d2887e9-c6ae-429c-9c5c-9dbd0477bbac}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11162,7 +11180,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7d77bee7-6fd5-4381-acaf-738800090c26}</x14:id>
+          <x14:id>{f46084ea-dcb6-42bd-a0d6-64db48718725}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11174,7 +11192,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4023263c-9333-4063-83f5-5b92623fd4b7}</x14:id>
+          <x14:id>{94f15dda-0d0a-4769-a449-4211f61782dc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11188,7 +11206,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d1905c29-40d3-4efd-94f7-aa65a257254f}</x14:id>
+          <x14:id>{43429ba3-2e5b-495d-9b71-3f834820802f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11200,7 +11218,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dc608717-f066-4f78-a5a9-64a41b662072}</x14:id>
+          <x14:id>{86537bc5-7ab9-409d-80ae-cbe4ffdbd11a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11212,7 +11230,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d6490629-fcbe-471b-956e-835d02956a98}</x14:id>
+          <x14:id>{d0cffe50-db3a-4e75-a937-5859344b2671}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11224,7 +11242,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{33e11453-3ca0-4b2d-9011-82d65491cc7f}</x14:id>
+          <x14:id>{42992f20-2b34-4e69-8927-84297e40cb77}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11236,7 +11254,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{03343b28-50d7-405b-8ef2-4a52868d50ba}</x14:id>
+          <x14:id>{b5c2efb9-731c-47e2-8e75-2defb76932bb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11248,7 +11266,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{88e41178-ac57-4290-9e47-ead19d391199}</x14:id>
+          <x14:id>{734a5852-7e0d-4a73-9323-84faf665d4c1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11260,7 +11278,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{10f13032-784c-4f6c-bc1c-efe1a061a361}</x14:id>
+          <x14:id>{a6eae9c2-528e-4110-b8cc-3e34c44ed3dd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11272,7 +11290,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{36c63486-18e3-449a-a7b5-cf052a5709bc}</x14:id>
+          <x14:id>{fc5b1b1f-c9a2-42da-b741-794cc7353231}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11286,7 +11304,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{81d13e68-642e-4bb1-a82f-f9364374467b}</x14:id>
+          <x14:id>{f449423e-64ed-4e39-8f50-125d20a5238b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11298,7 +11316,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fbd366fb-f6fc-4190-9490-00fa288a2ef2}</x14:id>
+          <x14:id>{4751ce9e-4308-4980-9db3-cf29778b08aa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11310,7 +11328,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e721645b-c6dc-44a7-a543-64432da7b5a9}</x14:id>
+          <x14:id>{ae1bf825-491f-4627-b0b8-3911cc05c530}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11322,7 +11340,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f3b60a87-cc09-4ff8-91bd-c716b92a6c12}</x14:id>
+          <x14:id>{d08897cd-e5a6-448c-8e36-068e0a304cec}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11334,7 +11352,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b31ce8c0-c208-4033-af3f-49da25cbf5b5}</x14:id>
+          <x14:id>{d22b0a3a-d663-4bd0-b96c-2fde01c1819e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11346,7 +11364,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{019968d7-b214-449c-99d1-32d466b3193b}</x14:id>
+          <x14:id>{2d570da1-cff8-4be1-8e3b-f00775dd52f1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11358,7 +11376,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e72f0bc5-84bf-43ea-80d8-59a15d55da42}</x14:id>
+          <x14:id>{2a0d7a0d-9b48-41dd-b9fe-cb47c71e7694}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11370,7 +11388,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{26daa55e-941b-4a21-9fa2-f3ff9d61a6fe}</x14:id>
+          <x14:id>{ab7611f9-cda9-4f81-9fdb-20d3244ceed6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11384,7 +11402,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3a3f25c4-cd4f-4c7b-ac97-3410b455c670}</x14:id>
+          <x14:id>{5bd36edc-4e10-443f-92bb-f4a3f3a6c6b8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11396,7 +11414,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{768107ad-ece9-4d66-9141-266d37f91bfd}</x14:id>
+          <x14:id>{19560f1c-6f5a-4b5d-9846-e73233382076}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11408,7 +11426,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6292edcd-73c9-4d4b-baa1-65b91ea82f9e}</x14:id>
+          <x14:id>{373cf832-e1ea-463a-874e-ca0321128e27}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11420,7 +11438,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a1bd7b84-4b14-426e-857d-8719c72c37d8}</x14:id>
+          <x14:id>{f15d0d51-e8d1-4437-8d11-a82576c10b52}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11432,7 +11450,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c0532312-1b08-47e2-9a09-963ee3f2f64e}</x14:id>
+          <x14:id>{9fc9a93b-9763-48d5-a058-9dffaf6af6da}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11444,7 +11462,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c48d18f7-ad5d-4787-93e0-57a82c6cae51}</x14:id>
+          <x14:id>{94610865-7687-4172-98c0-0d604837e404}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11456,7 +11474,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{711097c7-3b0c-4aab-99d9-866ad7f7c87e}</x14:id>
+          <x14:id>{89e566b9-e737-46db-a25a-32faf312eb2d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11468,7 +11486,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4136dfb6-56c9-4c42-9acb-caa2d2077048}</x14:id>
+          <x14:id>{cbd8b374-90b1-419d-b36f-78d9b0f07af3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11482,7 +11500,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dd0213ae-263a-41d6-8dd2-0a992ccf8cb7}</x14:id>
+          <x14:id>{15d2dd97-a8fc-42fc-acd9-328a716cbb5c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11494,7 +11512,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{787283b6-cb39-492e-9021-686202451be5}</x14:id>
+          <x14:id>{8604edfc-4b0d-4e02-9cd3-8e7f21a63ba7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11506,7 +11524,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{90a758bf-4932-4b37-a21d-927a773edcda}</x14:id>
+          <x14:id>{fe7d76b5-851c-4d38-bf9e-0adc3087bc04}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11518,7 +11536,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9855e2a8-8456-4661-81fd-6915e4559f21}</x14:id>
+          <x14:id>{8227ced0-21d7-4e63-90ea-8c85c2172c7b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11530,7 +11548,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{80468915-385f-4356-b03a-be4dbd243f8e}</x14:id>
+          <x14:id>{ec50bacd-7c22-41ff-be62-be0492650e28}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11542,7 +11560,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0e4c1bf7-7a26-40f7-93b0-a6cbc43089f5}</x14:id>
+          <x14:id>{7e15e1d2-ffbf-4cb5-9377-b01c38800de0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11554,7 +11572,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fc66b491-9ab6-4864-9842-b40335ef73e7}</x14:id>
+          <x14:id>{562e4acf-06a4-4331-b013-a9381983f7e9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11566,7 +11584,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b22569c0-bfb5-455c-a1a0-334788c0fbb4}</x14:id>
+          <x14:id>{2679b03f-c717-496d-a47f-0fb1759ea747}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11580,7 +11598,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{99b76234-da35-4554-94be-443acc709c39}</x14:id>
+          <x14:id>{e051c854-f424-4f97-9cf3-74130ff478e7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11592,7 +11610,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fa4ae5be-e494-43ac-add9-6e6dfeb7368b}</x14:id>
+          <x14:id>{54065d80-b0a0-4403-aad4-108e903cfdc2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11604,7 +11622,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b2e24994-7c4f-4dbb-8867-8c0f1170739e}</x14:id>
+          <x14:id>{5b160a84-3c34-42fb-9640-4740da21719e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11616,7 +11634,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{51b5e3da-e479-4ce0-938e-993fef1494f2}</x14:id>
+          <x14:id>{5fe7beb5-de89-4c39-9413-1498f2504de9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11628,7 +11646,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c45da89a-5892-4b98-8630-22fb1ba3be8d}</x14:id>
+          <x14:id>{67617d65-03a4-4695-9dbb-cd4698732438}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11640,7 +11658,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{036682b9-389d-488e-a322-46985c5f882e}</x14:id>
+          <x14:id>{0b1fe81b-1579-475e-815d-14f279a89b42}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11652,7 +11670,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0028203e-c5a8-44a2-968f-d2948b8f702d}</x14:id>
+          <x14:id>{4343cd32-0abe-4f91-b033-0ef48f5d0940}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11664,7 +11682,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d72c2497-ec79-49c9-b0ef-313233bcdec5}</x14:id>
+          <x14:id>{2dbf4edc-b4f6-4128-8b18-62befc47b7e3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11678,7 +11696,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1b4d543e-b4d4-4ec3-bc96-4b162b66afcd}</x14:id>
+          <x14:id>{10e25e35-da01-4b05-81ff-8af5b5c142b6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11690,7 +11708,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8088920a-74bd-4e07-94c7-9d32fd898f8c}</x14:id>
+          <x14:id>{330d7808-ae3e-4709-b691-9ecf468a5cd8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11702,7 +11720,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ad9239a5-280c-46d2-a105-879b4fdf1949}</x14:id>
+          <x14:id>{9987c89f-18a5-4525-9bb9-45ff1fd0b546}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11716,7 +11734,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{67b43be6-050b-46f0-8488-a79cc66e77f2}</x14:id>
+          <x14:id>{f45eb2a8-00d7-4eac-8b1b-60cfc1e42934}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11728,7 +11746,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4cf57c99-0a12-479a-9906-640199b7a00d}</x14:id>
+          <x14:id>{d0e9c784-2d31-46e3-bc70-7e459884b3a5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11740,7 +11758,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ced816e7-654f-4b78-8360-8e82f0b04ecc}</x14:id>
+          <x14:id>{b082b7ee-05fd-401c-9117-c15e7e7bc1d0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11754,7 +11772,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{678575e2-b5fc-4c02-9722-25beb2733a4d}</x14:id>
+          <x14:id>{c46fbf50-fa2e-48d8-8d06-c6539c6c779c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11766,7 +11784,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cda19f44-8c33-4ae0-97f7-b7c0447e794a}</x14:id>
+          <x14:id>{431e3765-6590-4641-9f0e-d68b8f2c6c5d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11780,7 +11798,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{16a9e5b0-f7ab-4fbc-a6a4-766d03e3fc89}</x14:id>
+          <x14:id>{1dcdcc10-7594-4f7d-812a-1f3c2ba38a84}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11792,7 +11810,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4ff3fb55-3fa4-45a3-a2aa-91fd74b24072}</x14:id>
+          <x14:id>{3dcd5b39-fdbf-49b8-9353-676c7c3590bc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11804,7 +11822,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0a81fc6a-d45c-48a8-a144-e4fa2c45b1ee}</x14:id>
+          <x14:id>{7ddd7afa-ed6c-4d19-91ee-06002d8d1b7f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11818,7 +11836,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7da44644-4e47-4b84-b907-4dd47e99ef14}</x14:id>
+          <x14:id>{5c07b905-349e-4a2d-b430-bb4d7ac85860}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11830,7 +11848,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7ece2329-754c-4dda-ba1b-fa1a8bd18872}</x14:id>
+          <x14:id>{c8c9d9aa-ee45-4d66-b2b2-58be51c524a9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11842,7 +11860,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9d508d61-1fe4-4ab7-9ecd-1b60b9cfd4b8}</x14:id>
+          <x14:id>{7839ab6e-e2be-4312-b833-66fa3e4c9f07}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11856,7 +11874,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{246b0ca9-687d-4e4e-a4e1-c559ddc91d10}</x14:id>
+          <x14:id>{8930ba59-95c8-4f05-a69f-7820ffb64b68}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11868,7 +11886,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f1b60e70-98a0-4a9f-bd53-0d23933f2cbd}</x14:id>
+          <x14:id>{d44c1848-0434-4f9d-83ed-7650589ec994}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11880,7 +11898,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{155e4ad8-fdf1-4432-bed0-fc7c1ed53cc1}</x14:id>
+          <x14:id>{0d16a92c-f53f-4955-b841-4b77a61cb245}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11894,7 +11912,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dfa17ede-82bb-4ec6-9600-af1a10ad9335}</x14:id>
+          <x14:id>{7a8cd518-76f9-49f5-b401-2ad8cefde44a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11906,7 +11924,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c3e83820-e30d-44e7-96ef-94d364d554e5}</x14:id>
+          <x14:id>{b4209c88-a67e-4b4f-baa7-1fe8c88a0cb6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11918,7 +11936,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e7f1ce64-5ef1-4ce0-a38d-96f2ca81580d}</x14:id>
+          <x14:id>{38c467a4-5e44-46d3-9559-9692b46dd54d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11932,7 +11950,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{db7a0dd9-e644-40a2-aa14-fdf44c7e0bcf}</x14:id>
+          <x14:id>{339a5f35-080a-46b4-bccb-8bacd2c5240f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11944,7 +11962,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e8ba5cac-1e98-4939-bf97-ca099f30975f}</x14:id>
+          <x14:id>{887ef401-7856-47a5-b305-ffef768b610a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11956,7 +11974,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e3cf83b7-6496-488c-8825-b2c6bf81f58f}</x14:id>
+          <x14:id>{e9325cde-0ad4-43da-a2a1-136c2ec9199a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11970,7 +11988,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3ba01fad-1012-44aa-95df-d0cf55e2013e}</x14:id>
+          <x14:id>{07175fa1-5f89-4f51-af95-401a62e1a2d4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11982,7 +12000,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2110f27d-bee4-40cd-8ffe-06bb1a300495}</x14:id>
+          <x14:id>{aa2b516a-a20e-42b8-9c7f-2ed77ae61ebf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11994,7 +12012,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bfc6bf5c-1d96-4745-9d0b-d5c3da782014}</x14:id>
+          <x14:id>{b8701955-4a16-479c-8f2b-d2a224e0c0d2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12006,7 +12024,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c7a10603-5394-4560-a078-1f8cde127f69}</x14:id>
+          <x14:id>{a6c7ff95-17a3-4537-a599-2235dd00a17e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12018,7 +12036,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dfbe3c9e-4bcd-4d83-ad7b-00efffb492f6}</x14:id>
+          <x14:id>{e437c70f-aa76-441c-b4f0-bb738a1f6d16}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12030,7 +12048,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ea6a31f5-73c7-4647-a8bf-875b8310af6d}</x14:id>
+          <x14:id>{6468aa35-73cf-4e3c-9996-d0d30839b2f7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12042,7 +12060,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{69d466d0-abfb-4d61-acf8-b5adea56189b}</x14:id>
+          <x14:id>{432bc915-a0d9-4dcb-b56f-647b516ba97d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12054,7 +12072,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{793ea7f4-f361-4baa-b8c2-7657028d4894}</x14:id>
+          <x14:id>{c0736e08-d1c7-4b9f-b863-65c2c7377b59}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12068,7 +12086,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4785fce1-05c1-4eff-8ae3-8ff7c1bd1ea9}</x14:id>
+          <x14:id>{1f470d2a-f298-4423-bba1-4584d6e6041a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12080,7 +12098,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9f86a527-c07f-47ec-b872-80c8aff57e1f}</x14:id>
+          <x14:id>{9cd0397c-243b-4064-a845-d5ab2251b5c4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12094,7 +12112,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{888fa92c-8112-4f96-857d-00159d71c86e}</x14:id>
+          <x14:id>{81c785b6-d9ec-4e50-be20-ba1828fc7b08}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12108,7 +12126,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{57747a2d-c3ca-49bd-b778-9e19d4db0e15}</x14:id>
+          <x14:id>{79b6edcb-0864-4815-9590-d441def8ecc5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12122,7 +12140,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{15b31294-f99e-4183-830c-dd322fd307a8}</x14:id>
+          <x14:id>{e2f097f9-60e2-41d7-ac88-952fb112f193}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12136,7 +12154,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9c2570c8-1a17-4430-9067-a150c811964d}</x14:id>
+          <x14:id>{848b3bdf-5226-43db-a571-6d78ab541026}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12150,7 +12168,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{26c58f1c-0796-4e14-ae7c-fc4088105c24}</x14:id>
+          <x14:id>{d1af849e-6cfa-447b-9666-60a64f0a3c6c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12162,7 +12180,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{786036a2-343a-4a2a-aced-2913f439c017}</x14:id>
+          <x14:id>{88a765bc-ceaf-43f2-b1ac-254c53d9f821}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12174,7 +12192,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{652d0d30-241a-48ed-b98e-638d0045db9d}</x14:id>
+          <x14:id>{b880d4d5-90b6-4164-a1f9-f61498a22dec}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12188,7 +12206,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4890317d-7792-4a65-b2e0-fee8cf5e878a}</x14:id>
+          <x14:id>{252c3fb7-85dd-4309-bf47-a7f7445ad33d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12200,7 +12218,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{97c430b1-f1b4-4b9f-a8ab-3b6ec963945c}</x14:id>
+          <x14:id>{ed2ae304-a059-424f-ab1a-6738c2dfbbb5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12212,7 +12230,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1f9ae181-fa63-4e77-a2a8-236f68bf084f}</x14:id>
+          <x14:id>{06a91191-f7ee-41af-96c4-9098481de723}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12226,7 +12244,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{42bf44fa-a319-4fde-a6c2-5c8a4df39b12}</x14:id>
+          <x14:id>{5240afe0-1a4e-4a62-858b-4dbc14260841}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12238,7 +12256,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{05b6d790-7f3e-4b15-9d16-6526f9bbddf6}</x14:id>
+          <x14:id>{a8207689-0771-43bd-be70-2bac451b8a04}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12250,7 +12268,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3faffba6-6106-41fa-a4b5-bbb58564c9cf}</x14:id>
+          <x14:id>{5afbf0a8-23db-4b75-a432-eb4c5cab17c7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12264,7 +12282,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bf767043-9723-40d3-89c1-4f0237d63cdb}</x14:id>
+          <x14:id>{d79459d6-884c-4a3c-b21c-ed4b9dd6430d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12276,7 +12294,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e73aae7c-0db7-4549-addd-c779c1ac5c67}</x14:id>
+          <x14:id>{107698f6-313c-498b-9b8b-f8c72165b31a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12288,7 +12306,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{807f2e68-6300-4ffb-971a-128c023b4064}</x14:id>
+          <x14:id>{d27e7a6f-c0c3-4597-93ba-dbd4e1ace09f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12302,7 +12320,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bcb33bf1-acf1-485f-84d9-60f81cce47fc}</x14:id>
+          <x14:id>{911f05c4-d337-4296-bd10-b2f788f7ea15}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12314,7 +12332,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{158ee51e-7592-4f23-98a6-4b2b489f3150}</x14:id>
+          <x14:id>{d1190f8f-cfbf-402f-a563-1b754a8cfb86}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12328,7 +12346,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a3752975-14d5-462d-a711-737ec2cd7922}</x14:id>
+          <x14:id>{4016564b-8f81-4817-ad31-55622271c777}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12340,7 +12358,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aa6f49fd-7b36-4e3e-aed3-fed86d85bd90}</x14:id>
+          <x14:id>{63bc00e1-4b5e-48dd-ada2-f422fffef014}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12352,7 +12370,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5e6721e5-b970-44fe-89c8-36dadc575889}</x14:id>
+          <x14:id>{25b4dfa6-6b69-48fb-bb36-8124ba70281d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12366,7 +12384,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e05244d8-0e67-41f4-b329-31e24ba61ec8}</x14:id>
+          <x14:id>{999bc4c6-b06a-4795-9a2b-728ae4c09929}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12378,7 +12396,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{db6b9fc7-9eb0-4d66-98f5-f700afd0fe8c}</x14:id>
+          <x14:id>{91514c5a-78c8-4267-9557-de51ffedf53a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12390,7 +12408,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f5d30e62-89c8-49a1-9c0c-b6e80ee77963}</x14:id>
+          <x14:id>{d6549bd5-9cc0-4af3-8f63-7a52b5128f2a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12404,7 +12422,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d19732fd-2033-474d-be69-60e4354ac7c7}</x14:id>
+          <x14:id>{0d2a7e42-b164-4b3b-8686-4c60f3a77136}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12416,7 +12434,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b6072a33-a097-49b6-801f-b68f2bfd9993}</x14:id>
+          <x14:id>{31cced82-ae48-4a8c-a610-5d558d082985}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12450,7 +12468,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d26b6506-af02-4c3e-abd8-c960452e00fd}">
+          <x14:cfRule type="dataBar" id="{aa9873e0-b3ee-4b61-97ca-60ebe8490711}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12461,7 +12479,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6f9b6945-1b12-42cc-a358-15fccc908496}">
+          <x14:cfRule type="dataBar" id="{fa04ff7d-e7b6-4f75-97c5-547db3ff1338}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12472,14 +12490,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fbdf3d43-7e43-46d8-ba48-dfc08066ee32}">
+          <x14:cfRule type="dataBar" id="{a0f9c72e-9472-48c2-a3b7-d75ed7029e82}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0a25df39-72f8-4de8-8b8e-aa779181855d}">
+          <x14:cfRule type="dataBar" id="{eaf28077-1c70-4a53-bbd7-f15b73e61db5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12490,7 +12508,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{59f2dfec-c076-4ea3-b927-f22bf00d43fe}">
+          <x14:cfRule type="dataBar" id="{41712525-6ece-4b08-b8d3-9d3845852a53}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12501,7 +12519,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{eaff4522-b194-4d35-9268-cc6e8157ea8d}">
+          <x14:cfRule type="dataBar" id="{0d2887e9-c6ae-429c-9c5c-9dbd0477bbac}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12512,7 +12530,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7d77bee7-6fd5-4381-acaf-738800090c26}">
+          <x14:cfRule type="dataBar" id="{f46084ea-dcb6-42bd-a0d6-64db48718725}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12521,7 +12539,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4023263c-9333-4063-83f5-5b92623fd4b7}">
+          <x14:cfRule type="dataBar" id="{94f15dda-0d0a-4769-a449-4211f61782dc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12533,7 +12551,7 @@
           <xm:sqref>AD56</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d1905c29-40d3-4efd-94f7-aa65a257254f}">
+          <x14:cfRule type="dataBar" id="{43429ba3-2e5b-495d-9b71-3f834820802f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12544,7 +12562,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{dc608717-f066-4f78-a5a9-64a41b662072}">
+          <x14:cfRule type="dataBar" id="{86537bc5-7ab9-409d-80ae-cbe4ffdbd11a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12555,14 +12573,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d6490629-fcbe-471b-956e-835d02956a98}">
+          <x14:cfRule type="dataBar" id="{d0cffe50-db3a-4e75-a937-5859344b2671}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{33e11453-3ca0-4b2d-9011-82d65491cc7f}">
+          <x14:cfRule type="dataBar" id="{42992f20-2b34-4e69-8927-84297e40cb77}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12573,7 +12591,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{03343b28-50d7-405b-8ef2-4a52868d50ba}">
+          <x14:cfRule type="dataBar" id="{b5c2efb9-731c-47e2-8e75-2defb76932bb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12584,7 +12602,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{88e41178-ac57-4290-9e47-ead19d391199}">
+          <x14:cfRule type="dataBar" id="{734a5852-7e0d-4a73-9323-84faf665d4c1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12595,7 +12613,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{10f13032-784c-4f6c-bc1c-efe1a061a361}">
+          <x14:cfRule type="dataBar" id="{a6eae9c2-528e-4110-b8cc-3e34c44ed3dd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12604,7 +12622,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{36c63486-18e3-449a-a7b5-cf052a5709bc}">
+          <x14:cfRule type="dataBar" id="{fc5b1b1f-c9a2-42da-b741-794cc7353231}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12616,7 +12634,7 @@
           <xm:sqref>K60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{81d13e68-642e-4bb1-a82f-f9364374467b}">
+          <x14:cfRule type="dataBar" id="{f449423e-64ed-4e39-8f50-125d20a5238b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12627,7 +12645,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fbd366fb-f6fc-4190-9490-00fa288a2ef2}">
+          <x14:cfRule type="dataBar" id="{4751ce9e-4308-4980-9db3-cf29778b08aa}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12638,14 +12656,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e721645b-c6dc-44a7-a543-64432da7b5a9}">
+          <x14:cfRule type="dataBar" id="{ae1bf825-491f-4627-b0b8-3911cc05c530}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f3b60a87-cc09-4ff8-91bd-c716b92a6c12}">
+          <x14:cfRule type="dataBar" id="{d08897cd-e5a6-448c-8e36-068e0a304cec}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12656,7 +12674,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b31ce8c0-c208-4033-af3f-49da25cbf5b5}">
+          <x14:cfRule type="dataBar" id="{d22b0a3a-d663-4bd0-b96c-2fde01c1819e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12667,7 +12685,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{019968d7-b214-449c-99d1-32d466b3193b}">
+          <x14:cfRule type="dataBar" id="{2d570da1-cff8-4be1-8e3b-f00775dd52f1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12678,7 +12696,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e72f0bc5-84bf-43ea-80d8-59a15d55da42}">
+          <x14:cfRule type="dataBar" id="{2a0d7a0d-9b48-41dd-b9fe-cb47c71e7694}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12687,7 +12705,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{26daa55e-941b-4a21-9fa2-f3ff9d61a6fe}">
+          <x14:cfRule type="dataBar" id="{ab7611f9-cda9-4f81-9fdb-20d3244ceed6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12699,7 +12717,7 @@
           <xm:sqref>AD60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3a3f25c4-cd4f-4c7b-ac97-3410b455c670}">
+          <x14:cfRule type="dataBar" id="{5bd36edc-4e10-443f-92bb-f4a3f3a6c6b8}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12710,7 +12728,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{768107ad-ece9-4d66-9141-266d37f91bfd}">
+          <x14:cfRule type="dataBar" id="{19560f1c-6f5a-4b5d-9846-e73233382076}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12721,14 +12739,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6292edcd-73c9-4d4b-baa1-65b91ea82f9e}">
+          <x14:cfRule type="dataBar" id="{373cf832-e1ea-463a-874e-ca0321128e27}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a1bd7b84-4b14-426e-857d-8719c72c37d8}">
+          <x14:cfRule type="dataBar" id="{f15d0d51-e8d1-4437-8d11-a82576c10b52}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12739,7 +12757,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c0532312-1b08-47e2-9a09-963ee3f2f64e}">
+          <x14:cfRule type="dataBar" id="{9fc9a93b-9763-48d5-a058-9dffaf6af6da}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12750,7 +12768,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c48d18f7-ad5d-4787-93e0-57a82c6cae51}">
+          <x14:cfRule type="dataBar" id="{94610865-7687-4172-98c0-0d604837e404}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12761,7 +12779,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{711097c7-3b0c-4aab-99d9-866ad7f7c87e}">
+          <x14:cfRule type="dataBar" id="{89e566b9-e737-46db-a25a-32faf312eb2d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12770,7 +12788,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4136dfb6-56c9-4c42-9acb-caa2d2077048}">
+          <x14:cfRule type="dataBar" id="{cbd8b374-90b1-419d-b36f-78d9b0f07af3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12782,7 +12800,7 @@
           <xm:sqref>K61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dd0213ae-263a-41d6-8dd2-0a992ccf8cb7}">
+          <x14:cfRule type="dataBar" id="{15d2dd97-a8fc-42fc-acd9-328a716cbb5c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12793,7 +12811,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{787283b6-cb39-492e-9021-686202451be5}">
+          <x14:cfRule type="dataBar" id="{8604edfc-4b0d-4e02-9cd3-8e7f21a63ba7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12804,14 +12822,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{90a758bf-4932-4b37-a21d-927a773edcda}">
+          <x14:cfRule type="dataBar" id="{fe7d76b5-851c-4d38-bf9e-0adc3087bc04}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9855e2a8-8456-4661-81fd-6915e4559f21}">
+          <x14:cfRule type="dataBar" id="{8227ced0-21d7-4e63-90ea-8c85c2172c7b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12822,7 +12840,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{80468915-385f-4356-b03a-be4dbd243f8e}">
+          <x14:cfRule type="dataBar" id="{ec50bacd-7c22-41ff-be62-be0492650e28}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12833,7 +12851,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0e4c1bf7-7a26-40f7-93b0-a6cbc43089f5}">
+          <x14:cfRule type="dataBar" id="{7e15e1d2-ffbf-4cb5-9377-b01c38800de0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12844,7 +12862,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fc66b491-9ab6-4864-9842-b40335ef73e7}">
+          <x14:cfRule type="dataBar" id="{562e4acf-06a4-4331-b013-a9381983f7e9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12853,7 +12871,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b22569c0-bfb5-455c-a1a0-334788c0fbb4}">
+          <x14:cfRule type="dataBar" id="{2679b03f-c717-496d-a47f-0fb1759ea747}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12865,7 +12883,7 @@
           <xm:sqref>K62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{99b76234-da35-4554-94be-443acc709c39}">
+          <x14:cfRule type="dataBar" id="{e051c854-f424-4f97-9cf3-74130ff478e7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12876,7 +12894,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fa4ae5be-e494-43ac-add9-6e6dfeb7368b}">
+          <x14:cfRule type="dataBar" id="{54065d80-b0a0-4403-aad4-108e903cfdc2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12887,14 +12905,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b2e24994-7c4f-4dbb-8867-8c0f1170739e}">
+          <x14:cfRule type="dataBar" id="{5b160a84-3c34-42fb-9640-4740da21719e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{51b5e3da-e479-4ce0-938e-993fef1494f2}">
+          <x14:cfRule type="dataBar" id="{5fe7beb5-de89-4c39-9413-1498f2504de9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12905,7 +12923,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c45da89a-5892-4b98-8630-22fb1ba3be8d}">
+          <x14:cfRule type="dataBar" id="{67617d65-03a4-4695-9dbb-cd4698732438}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12916,7 +12934,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{036682b9-389d-488e-a322-46985c5f882e}">
+          <x14:cfRule type="dataBar" id="{0b1fe81b-1579-475e-815d-14f279a89b42}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12927,7 +12945,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0028203e-c5a8-44a2-968f-d2948b8f702d}">
+          <x14:cfRule type="dataBar" id="{4343cd32-0abe-4f91-b033-0ef48f5d0940}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12936,7 +12954,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d72c2497-ec79-49c9-b0ef-313233bcdec5}">
+          <x14:cfRule type="dataBar" id="{2dbf4edc-b4f6-4128-8b18-62befc47b7e3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12948,7 +12966,7 @@
           <xm:sqref>K63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1b4d543e-b4d4-4ec3-bc96-4b162b66afcd}">
+          <x14:cfRule type="dataBar" id="{10e25e35-da01-4b05-81ff-8af5b5c142b6}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12957,7 +12975,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8088920a-74bd-4e07-94c7-9d32fd898f8c}">
+          <x14:cfRule type="dataBar" id="{330d7808-ae3e-4709-b691-9ecf468a5cd8}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12966,7 +12984,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ad9239a5-280c-46d2-a105-879b4fdf1949}">
+          <x14:cfRule type="dataBar" id="{9987c89f-18a5-4525-9bb9-45ff1fd0b546}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -12979,7 +12997,7 @@
           <xm:sqref>AB67</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{67b43be6-050b-46f0-8488-a79cc66e77f2}">
+          <x14:cfRule type="dataBar" id="{f45eb2a8-00d7-4eac-8b1b-60cfc1e42934}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12988,7 +13006,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4cf57c99-0a12-479a-9906-640199b7a00d}">
+          <x14:cfRule type="dataBar" id="{d0e9c784-2d31-46e3-bc70-7e459884b3a5}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12997,7 +13015,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ced816e7-654f-4b78-8360-8e82f0b04ecc}">
+          <x14:cfRule type="dataBar" id="{b082b7ee-05fd-401c-9117-c15e7e7bc1d0}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13010,7 +13028,7 @@
           <xm:sqref>AB101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{678575e2-b5fc-4c02-9722-25beb2733a4d}">
+          <x14:cfRule type="dataBar" id="{c46fbf50-fa2e-48d8-8d06-c6539c6c779c}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13019,7 +13037,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{cda19f44-8c33-4ae0-97f7-b7c0447e794a}">
+          <x14:cfRule type="dataBar" id="{431e3765-6590-4641-9f0e-d68b8f2c6c5d}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13031,7 +13049,7 @@
           <xm:sqref>AB115</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{16a9e5b0-f7ab-4fbc-a6a4-766d03e3fc89}">
+          <x14:cfRule type="dataBar" id="{1dcdcc10-7594-4f7d-812a-1f3c2ba38a84}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13040,7 +13058,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4ff3fb55-3fa4-45a3-a2aa-91fd74b24072}">
+          <x14:cfRule type="dataBar" id="{3dcd5b39-fdbf-49b8-9353-676c7c3590bc}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13049,7 +13067,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0a81fc6a-d45c-48a8-a144-e4fa2c45b1ee}">
+          <x14:cfRule type="dataBar" id="{7ddd7afa-ed6c-4d19-91ee-06002d8d1b7f}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13062,7 +13080,7 @@
           <xm:sqref>AB125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7da44644-4e47-4b84-b907-4dd47e99ef14}">
+          <x14:cfRule type="dataBar" id="{5c07b905-349e-4a2d-b430-bb4d7ac85860}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13071,7 +13089,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7ece2329-754c-4dda-ba1b-fa1a8bd18872}">
+          <x14:cfRule type="dataBar" id="{c8c9d9aa-ee45-4d66-b2b2-58be51c524a9}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13080,7 +13098,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9d508d61-1fe4-4ab7-9ecd-1b60b9cfd4b8}">
+          <x14:cfRule type="dataBar" id="{7839ab6e-e2be-4312-b833-66fa3e4c9f07}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13093,7 +13111,7 @@
           <xm:sqref>K135</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{246b0ca9-687d-4e4e-a4e1-c559ddc91d10}">
+          <x14:cfRule type="dataBar" id="{8930ba59-95c8-4f05-a69f-7820ffb64b68}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13102,7 +13120,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f1b60e70-98a0-4a9f-bd53-0d23933f2cbd}">
+          <x14:cfRule type="dataBar" id="{d44c1848-0434-4f9d-83ed-7650589ec994}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13111,7 +13129,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{155e4ad8-fdf1-4432-bed0-fc7c1ed53cc1}">
+          <x14:cfRule type="dataBar" id="{0d16a92c-f53f-4955-b841-4b77a61cb245}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13124,7 +13142,7 @@
           <xm:sqref>K140</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dfa17ede-82bb-4ec6-9600-af1a10ad9335}">
+          <x14:cfRule type="dataBar" id="{7a8cd518-76f9-49f5-b401-2ad8cefde44a}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13133,7 +13151,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c3e83820-e30d-44e7-96ef-94d364d554e5}">
+          <x14:cfRule type="dataBar" id="{b4209c88-a67e-4b4f-baa7-1fe8c88a0cb6}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13142,7 +13160,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e7f1ce64-5ef1-4ce0-a38d-96f2ca81580d}">
+          <x14:cfRule type="dataBar" id="{38c467a4-5e44-46d3-9559-9692b46dd54d}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13155,7 +13173,7 @@
           <xm:sqref>K145</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{db7a0dd9-e644-40a2-aa14-fdf44c7e0bcf}">
+          <x14:cfRule type="dataBar" id="{339a5f35-080a-46b4-bccb-8bacd2c5240f}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13164,7 +13182,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e8ba5cac-1e98-4939-bf97-ca099f30975f}">
+          <x14:cfRule type="dataBar" id="{887ef401-7856-47a5-b305-ffef768b610a}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13173,7 +13191,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e3cf83b7-6496-488c-8825-b2c6bf81f58f}">
+          <x14:cfRule type="dataBar" id="{e9325cde-0ad4-43da-a2a1-136c2ec9199a}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13186,7 +13204,7 @@
           <xm:sqref>K150</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3ba01fad-1012-44aa-95df-d0cf55e2013e}">
+          <x14:cfRule type="dataBar" id="{07175fa1-5f89-4f51-af95-401a62e1a2d4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -13197,7 +13215,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2110f27d-bee4-40cd-8ffe-06bb1a300495}">
+          <x14:cfRule type="dataBar" id="{aa2b516a-a20e-42b8-9c7f-2ed77ae61ebf}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13208,14 +13226,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{bfc6bf5c-1d96-4745-9d0b-d5c3da782014}">
+          <x14:cfRule type="dataBar" id="{b8701955-4a16-479c-8f2b-d2a224e0c0d2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c7a10603-5394-4560-a078-1f8cde127f69}">
+          <x14:cfRule type="dataBar" id="{a6c7ff95-17a3-4537-a599-2235dd00a17e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -13226,7 +13244,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{dfbe3c9e-4bcd-4d83-ad7b-00efffb492f6}">
+          <x14:cfRule type="dataBar" id="{e437c70f-aa76-441c-b4f0-bb738a1f6d16}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -13237,7 +13255,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ea6a31f5-73c7-4647-a8bf-875b8310af6d}">
+          <x14:cfRule type="dataBar" id="{6468aa35-73cf-4e3c-9996-d0d30839b2f7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13248,7 +13266,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{69d466d0-abfb-4d61-acf8-b5adea56189b}">
+          <x14:cfRule type="dataBar" id="{432bc915-a0d9-4dcb-b56f-647b516ba97d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13257,7 +13275,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{793ea7f4-f361-4baa-b8c2-7657028d4894}">
+          <x14:cfRule type="dataBar" id="{c0736e08-d1c7-4b9f-b863-65c2c7377b59}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13269,7 +13287,7 @@
           <xm:sqref>K57:K58</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4785fce1-05c1-4eff-8ae3-8ff7c1bd1ea9}">
+          <x14:cfRule type="dataBar" id="{1f470d2a-f298-4423-bba1-4584d6e6041a}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13278,7 +13296,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9f86a527-c07f-47ec-b872-80c8aff57e1f}">
+          <x14:cfRule type="dataBar" id="{9cd0397c-243b-4064-a845-d5ab2251b5c4}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13291,7 +13309,7 @@
           <xm:sqref>Y67:Y86</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{888fa92c-8112-4f96-857d-00159d71c86e}">
+          <x14:cfRule type="dataBar" id="{81c785b6-d9ec-4e50-be20-ba1828fc7b08}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13304,7 +13322,7 @@
           <xm:sqref>Y77:Y86</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{57747a2d-c3ca-49bd-b778-9e19d4db0e15}">
+          <x14:cfRule type="dataBar" id="{79b6edcb-0864-4815-9590-d441def8ecc5}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13317,7 +13335,7 @@
           <xm:sqref>AB115:AB124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{15b31294-f99e-4183-830c-dd322fd307a8}">
+          <x14:cfRule type="dataBar" id="{e2f097f9-60e2-41d7-ac88-952fb112f193}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13329,7 +13347,7 @@
           <xm:sqref>AD56:AE57</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9c2570c8-1a17-4430-9067-a150c811964d}">
+          <x14:cfRule type="dataBar" id="{848b3bdf-5226-43db-a571-6d78ab541026}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13341,7 +13359,7 @@
           <xm:sqref>AD60:AE63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{26c58f1c-0796-4e14-ae7c-fc4088105c24}">
+          <x14:cfRule type="dataBar" id="{d1af849e-6cfa-447b-9666-60a64f0a3c6c}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13350,7 +13368,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{786036a2-343a-4a2a-aced-2913f439c017}">
+          <x14:cfRule type="dataBar" id="{88a765bc-ceaf-43f2-b1ac-254c53d9f821}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13359,7 +13377,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{652d0d30-241a-48ed-b98e-638d0045db9d}">
+          <x14:cfRule type="dataBar" id="{b880d4d5-90b6-4164-a1f9-f61498a22dec}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13372,7 +13390,7 @@
           <xm:sqref>F67 F72 F77 F82</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4890317d-7792-4a65-b2e0-fee8cf5e878a}">
+          <x14:cfRule type="dataBar" id="{252c3fb7-85dd-4309-bf47-a7f7445ad33d}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13381,7 +13399,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{97c430b1-f1b4-4b9f-a8ab-3b6ec963945c}">
+          <x14:cfRule type="dataBar" id="{ed2ae304-a059-424f-ab1a-6738c2dfbbb5}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13390,7 +13408,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1f9ae181-fa63-4e77-a2a8-236f68bf084f}">
+          <x14:cfRule type="dataBar" id="{06a91191-f7ee-41af-96c4-9098481de723}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13403,7 +13421,7 @@
           <xm:sqref>K67 K77 K87 K101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{42bf44fa-a319-4fde-a6c2-5c8a4df39b12}">
+          <x14:cfRule type="dataBar" id="{5240afe0-1a4e-4a62-858b-4dbc14260841}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13412,7 +13430,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{05b6d790-7f3e-4b15-9d16-6526f9bbddf6}">
+          <x14:cfRule type="dataBar" id="{a8207689-0771-43bd-be70-2bac451b8a04}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13421,7 +13439,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3faffba6-6106-41fa-a4b5-bbb58564c9cf}">
+          <x14:cfRule type="dataBar" id="{5afbf0a8-23db-4b75-a432-eb4c5cab17c7}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13434,7 +13452,7 @@
           <xm:sqref>AB77 AB87</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bf767043-9723-40d3-89c1-4f0237d63cdb}">
+          <x14:cfRule type="dataBar" id="{d79459d6-884c-4a3c-b21c-ed4b9dd6430d}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13443,7 +13461,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e73aae7c-0db7-4549-addd-c779c1ac5c67}">
+          <x14:cfRule type="dataBar" id="{107698f6-313c-498b-9b8b-f8c72165b31a}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13452,7 +13470,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{807f2e68-6300-4ffb-971a-128c023b4064}">
+          <x14:cfRule type="dataBar" id="{d27e7a6f-c0c3-4597-93ba-dbd4e1ace09f}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13465,7 +13483,7 @@
           <xm:sqref>F87 F94 F101 F108</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bcb33bf1-acf1-485f-84d9-60f81cce47fc}">
+          <x14:cfRule type="dataBar" id="{911f05c4-d337-4296-bd10-b2f788f7ea15}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13474,7 +13492,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{158ee51e-7592-4f23-98a6-4b2b489f3150}">
+          <x14:cfRule type="dataBar" id="{d1190f8f-cfbf-402f-a563-1b754a8cfb86}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13487,7 +13505,7 @@
           <xm:sqref>Y87 Y101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a3752975-14d5-462d-a711-737ec2cd7922}">
+          <x14:cfRule type="dataBar" id="{4016564b-8f81-4817-ad31-55622271c777}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13496,7 +13514,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{aa6f49fd-7b36-4e3e-aed3-fed86d85bd90}">
+          <x14:cfRule type="dataBar" id="{63bc00e1-4b5e-48dd-ada2-f422fffef014}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13505,7 +13523,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5e6721e5-b970-44fe-89c8-36dadc575889}">
+          <x14:cfRule type="dataBar" id="{25b4dfa6-6b69-48fb-bb36-8124ba70281d}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13518,7 +13536,7 @@
           <xm:sqref>F115 F120 F125 F130 F135 F140 F145 F150</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e05244d8-0e67-41f4-b329-31e24ba61ec8}">
+          <x14:cfRule type="dataBar" id="{999bc4c6-b06a-4795-9a2b-728ae4c09929}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13527,7 +13545,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{db6b9fc7-9eb0-4d66-98f5-f700afd0fe8c}">
+          <x14:cfRule type="dataBar" id="{91514c5a-78c8-4267-9557-de51ffedf53a}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13536,7 +13554,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f5d30e62-89c8-49a1-9c0c-b6e80ee77963}">
+          <x14:cfRule type="dataBar" id="{d6549bd5-9cc0-4af3-8f63-7a52b5128f2a}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13549,7 +13567,7 @@
           <xm:sqref>K115 K125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d19732fd-2033-474d-be69-60e4354ac7c7}">
+          <x14:cfRule type="dataBar" id="{0d2a7e42-b164-4b3b-8686-4c60f3a77136}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13558,7 +13576,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b6072a33-a097-49b6-801f-b68f2bfd9993}">
+          <x14:cfRule type="dataBar" id="{31cced82-ae48-4a8c-a610-5d558d082985}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13580,12 +13598,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="26.8796296296296" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.37962962962963" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.22222222222222" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.37962962962963" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.8818181818182" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.38181818181818" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.21818181818182" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9.38181818181818" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
